--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="YDJJpdDsIoyDjKKXdtnMIC/RnJWBqnb+29MuVWVl0WQ="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="YVyT860PVjy1j1GorqR2dylNg14PuGH2VgNk0fkAIZc="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="293">
   <si>
     <t>County</t>
   </si>
@@ -179,12 +179,69 @@
     <t>Select Fire Rescue</t>
   </si>
   <si>
+    <t>Wellington</t>
+  </si>
+  <si>
+    <t>Town of Wellington Planning Department</t>
+  </si>
+  <si>
+    <t>publicrecords@wellingtonfl.gov</t>
+  </si>
+  <si>
+    <t>https://www.wellingtonfl.gov/FormCenter/Public-Information-Request-Form-4/Public-Information-Request-Form-46</t>
+  </si>
+  <si>
+    <t>Just email</t>
+  </si>
+  <si>
+    <t>Has portal but prob just email</t>
+  </si>
+  <si>
+    <t>Town of Wellington Building Department</t>
+  </si>
+  <si>
+    <t>Town of Wellington Environmental Department</t>
+  </si>
+  <si>
+    <t>Town of Wellington Fire Department</t>
+  </si>
+  <si>
+    <t>unincorporated</t>
+  </si>
+  <si>
+    <t>Palm Beach County Building Department</t>
+  </si>
+  <si>
+    <t>PZBPublicRecords@pbcgov.org</t>
+  </si>
+  <si>
+    <t>https://pbcgov.com/eprr/pzb</t>
+  </si>
+  <si>
+    <t>Portal or email</t>
+  </si>
+  <si>
+    <t>Palm Beach County Planning Department</t>
+  </si>
+  <si>
+    <t>Palm Beach County Environmental Department</t>
+  </si>
+  <si>
+    <t>PublicRecordsRequest@flhealth.gov</t>
+  </si>
+  <si>
+    <t>Palm Beach County Fire Department</t>
+  </si>
+  <si>
+    <t>https://pbcfr.justfoia.com/Forms/Launch/a3770868-033f-442c-b6d0-a11d3493c386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portal </t>
+  </si>
+  <si>
     <t>Lee</t>
   </si>
   <si>
-    <t>unincorporated</t>
-  </si>
-  <si>
     <t>Lee County Community Development – Permits</t>
   </si>
   <si>
@@ -234,6 +291,36 @@
   </si>
   <si>
     <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>Bonita Springs</t>
+  </si>
+  <si>
+    <t>City of Bonita Springs Building Department</t>
+  </si>
+  <si>
+    <t>recordsrequest@cityofbonitasprings.org</t>
+  </si>
+  <si>
+    <t>https://egweb1.cityofbonitasprings.org/energov/selfservice#/home</t>
+  </si>
+  <si>
+    <t>Lookup + Email</t>
+  </si>
+  <si>
+    <t>Can try to lookup permits, otherwise email</t>
+  </si>
+  <si>
+    <t>City of Bonita Springs Planning Department</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email </t>
+  </si>
+  <si>
+    <t>City of Bonita Springs Environmental Department</t>
+  </si>
+  <si>
+    <t>City of Bonita Springs Fire Department</t>
   </si>
   <si>
     <t>Fort Myers</t>
@@ -352,6 +439,9 @@
     <t>Use self lookup with FOLIO</t>
   </si>
   <si>
+    <t>*</t>
+  </si>
+  <si>
     <t>Department of Environmental Resources Management</t>
   </si>
   <si>
@@ -361,7 +451,10 @@
     <t>DermRecords@miamidade.gov</t>
   </si>
   <si>
-    <t>Regulatory and Economic Resources</t>
+    <t>https://ecmrer.miamidade.gov/home</t>
+  </si>
+  <si>
+    <t>Use folio to lookup</t>
   </si>
   <si>
     <t>Miami Gardens</t>
@@ -397,9 +490,6 @@
     <t>Public records portal; City Clerk is custodian</t>
   </si>
   <si>
-    <t>*</t>
-  </si>
-  <si>
     <t>Miami-Dade Fire Rescue — Public Records</t>
   </si>
   <si>
@@ -505,12 +595,51 @@
     <t>City of Miami Planning Department</t>
   </si>
   <si>
+    <t>https://www.miami.gov/My-Government/Government-Services/Request-Public-Records</t>
+  </si>
+  <si>
     <t>Send email to email</t>
   </si>
   <si>
     <t>City of Miami Fire Department</t>
   </si>
   <si>
+    <t>fire@miamigov.com</t>
+  </si>
+  <si>
+    <t>Cutler Bay</t>
+  </si>
+  <si>
+    <t>City of Cutler Bay Building Department</t>
+  </si>
+  <si>
+    <t>MMelinu@cutlerbay-fl.gov</t>
+  </si>
+  <si>
+    <t>https://www.cutlerbay-fl.gov/townclerk/webform/public-records-request</t>
+  </si>
+  <si>
+    <t>Email or Portal</t>
+  </si>
+  <si>
+    <t>City of Cutler Bay Planning Department</t>
+  </si>
+  <si>
+    <t>Opa Locka</t>
+  </si>
+  <si>
+    <t>City of Opa Locka Building Department</t>
+  </si>
+  <si>
+    <t>jflores@opalockafl.gov</t>
+  </si>
+  <si>
+    <t>https://opalockafl.justfoia.com/Forms/Launch/d705cbd6-1396-49b7-939e-8d86c5a87deb</t>
+  </si>
+  <si>
+    <t>City of Opa Locka Planning Department</t>
+  </si>
+  <si>
     <t>Broward</t>
   </si>
   <si>
@@ -661,6 +790,9 @@
     <t>City of Miramar Building Department</t>
   </si>
   <si>
+    <t>clerksoffice@miramarfl.gov</t>
+  </si>
+  <si>
     <t>https://miramarfl.justfoia.com/Forms/Launch/d705cbd6-1396-49b7-939e-8d86c5a87deb</t>
   </si>
   <si>
@@ -676,6 +808,51 @@
     <t>City of Miramar Fire Department</t>
   </si>
   <si>
+    <t>Pembroke Pines</t>
+  </si>
+  <si>
+    <t>City of Pembroke Pines Building Department</t>
+  </si>
+  <si>
+    <t>gfernandez@ppines.com</t>
+  </si>
+  <si>
+    <t>https://crm-pembrokepinesfl.mycusthelp.com/WEBAPP/_rs/(S(xlkwufcy0yplyl4kwki35vmy))/SupportHome.aspx?sSessionID=999416543XJBLEPSSYVC[QTFHGNWNFKNRDRMHJGH</t>
+  </si>
+  <si>
+    <t>Email Clerk or Use Portal</t>
+  </si>
+  <si>
+    <t>City of Pembroke Pines Planning Department</t>
+  </si>
+  <si>
+    <t>City of Pembroke Pines Environmental Department</t>
+  </si>
+  <si>
+    <t>City of Pembroke Pines Fire Department</t>
+  </si>
+  <si>
+    <t>Plantation</t>
+  </si>
+  <si>
+    <t>City of Plantation Building Department</t>
+  </si>
+  <si>
+    <t>CityClerk@plantation.org</t>
+  </si>
+  <si>
+    <t>https://plantationfl.mycusthelp.com/webapp/_rs/(S(rypd5ubcdranmyztd0c50ajb))/SupportHome.aspx?sSessionID=999416543LTBNOGSPZOEEPCFTLIATHNQAMSSBJZF&amp;lp=2</t>
+  </si>
+  <si>
+    <t>City of Plantation Planning Department</t>
+  </si>
+  <si>
+    <t>City of Plantation Environmental Department</t>
+  </si>
+  <si>
+    <t>City of Plantation Fire Department</t>
+  </si>
+  <si>
     <t>Collier</t>
   </si>
   <si>
@@ -731,9 +908,6 @@
   </si>
   <si>
     <t>Orange County Fire Department</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email </t>
   </si>
   <si>
     <t>Highlands</t>
@@ -816,12 +990,12 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <u/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <u/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
@@ -887,23 +1061,23 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -1412,772 +1586,692 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="E10" s="2"/>
+      <c r="F10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="9"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="G11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="H11" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="I11" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I10" s="2" t="s">
+      <c r="J11" s="2"/>
+      <c r="K11" s="9"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
+      <c r="E12" s="2"/>
+      <c r="F12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="9"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="C13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E13" s="2"/>
+      <c r="F13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13" s="2"/>
+      <c r="K13" s="9"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>66</v>
+        <v>55</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>68</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="2"/>
+      <c r="K14" s="9"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>45</v>
+      <c r="A15" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>66</v>
+        <v>59</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>70</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="2"/>
+      <c r="K15" s="9"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>45</v>
+      <c r="A16" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>66</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="10"/>
       <c r="H16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="J16" s="2"/>
+      <c r="K16" s="9"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>45</v>
+      <c r="A17" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="2"/>
+      <c r="K17" s="9"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J17" s="2" t="s">
+      <c r="G21" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K17" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K19" s="9" t="s">
+      <c r="K21" s="9" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>80</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="J22" s="2"/>
+      <c r="K22" s="9"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>79</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23" s="12"/>
       <c r="H23" s="3" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>82</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="J23" s="2"/>
+      <c r="K23" s="9"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>79</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G24" s="12"/>
       <c r="H24" s="3" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>39</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="J24" s="2"/>
+      <c r="K24" s="9"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>79</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G25" s="12"/>
       <c r="H25" s="3" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>85</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="J25" s="2"/>
+      <c r="K25" s="9"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="A26" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>87</v>
+      <c r="D26" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I26" s="11" t="s">
-        <v>91</v>
+      <c r="I26" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K26" s="2" t="s">
-        <v>63</v>
+      <c r="K26" s="9" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="A27" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>92</v>
+      <c r="D27" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>95</v>
       </c>
       <c r="H27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K27" s="2" t="s">
-        <v>63</v>
+      <c r="K27" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>46</v>
+      <c r="A28" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F28" s="3" t="s">
         <v>100</v>
       </c>
+      <c r="E28" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="G28" s="5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K28" s="2" t="s">
-        <v>63</v>
+      <c r="K28" s="9" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B29" s="2" t="s">
+      <c r="A29" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>105</v>
+      <c r="E29" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>107</v>
+        <v>18</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K29" s="2" t="s">
-        <v>63</v>
+      <c r="K29" s="9" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C30" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="G30" s="4" t="s">
+      <c r="D31" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="E31" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K31" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="I31" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="L31" s="13"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
-      <c r="O31" s="13"/>
-      <c r="P31" s="13"/>
-      <c r="Q31" s="13"/>
-      <c r="R31" s="13"/>
-      <c r="S31" s="13"/>
-      <c r="T31" s="13"/>
-      <c r="U31" s="13"/>
-      <c r="V31" s="13"/>
-      <c r="W31" s="13"/>
-      <c r="X31" s="13"/>
-      <c r="Y31" s="13"/>
-      <c r="Z31" s="13"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>13</v>
+        <v>105</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J32" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>29</v>
       </c>
       <c r="K32" s="9" t="s">
@@ -2186,1339 +2280,2093 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>22</v>
+        <v>105</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G33" s="14" t="s">
-        <v>122</v>
+        <v>107</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>108</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="J33" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>29</v>
       </c>
       <c r="K33" s="9" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3" t="s">
-        <v>128</v>
+        <v>106</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>107</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="J34" s="2"/>
-      <c r="K34" s="9"/>
+        <v>96</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3" t="s">
-        <v>128</v>
+        <v>110</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>107</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="J35" s="2"/>
-      <c r="K35" s="9"/>
+        <v>96</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3" t="s">
-        <v>128</v>
+        <v>112</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>107</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J36" s="2"/>
-      <c r="K36" s="9"/>
+        <v>96</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>135</v>
+        <v>54</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3" t="s">
-        <v>137</v>
+        <v>113</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>107</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="J37" s="2"/>
-      <c r="K37" s="9"/>
+        <v>96</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
+        <v>115</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="G38" s="5" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I38" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="J38" s="2"/>
-      <c r="K38" s="9"/>
+      <c r="I38" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="E39" s="3"/>
+        <v>115</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="F39" s="3" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="J39" s="2"/>
-      <c r="K39" s="9"/>
+        <v>126</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E40" s="3"/>
+        <v>128</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="F40" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="G40" s="15"/>
+        <v>130</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>131</v>
+      </c>
       <c r="H40" s="3" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="J40" s="2"/>
-      <c r="K40" s="9"/>
+        <v>132</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B41" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I42" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="J42" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D43" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="J43" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="L43" s="15"/>
+      <c r="M43" s="15"/>
+      <c r="N43" s="15"/>
+      <c r="O43" s="15"/>
+      <c r="P43" s="15"/>
+      <c r="Q43" s="15"/>
+      <c r="R43" s="15"/>
+      <c r="S43" s="15"/>
+      <c r="T43" s="15"/>
+      <c r="U43" s="15"/>
+      <c r="V43" s="15"/>
+      <c r="W43" s="15"/>
+      <c r="X43" s="15"/>
+      <c r="Y43" s="15"/>
+      <c r="Z43" s="15"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="G41" s="15"/>
-      <c r="H41" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="J41" s="2"/>
-      <c r="K41" s="9"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="s">
+      <c r="F44" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="G44" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="H44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K44" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K45" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="I42" s="6" t="s">
+      <c r="D46" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J46" s="2"/>
+      <c r="K46" s="9"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="C43" s="6" t="s">
+      <c r="C47" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="I43" s="6" t="s">
+      <c r="D47" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J47" s="2"/>
+      <c r="K47" s="9"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D44" s="6" t="s">
+      <c r="C48" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="F44" s="6"/>
-      <c r="G44" s="7" t="s">
+      <c r="G48" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H44" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="C45" s="6" t="s">
+      <c r="H48" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="J48" s="2"/>
+      <c r="K48" s="9"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J49" s="2"/>
+      <c r="K49" s="9"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J50" s="2"/>
+      <c r="K50" s="9"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J51" s="2"/>
+      <c r="K51" s="9"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J52" s="2"/>
+      <c r="K52" s="9"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D45" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="C46" s="6" t="s">
+      <c r="D53" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J53" s="2"/>
+      <c r="K53" s="9"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="C47" s="6" t="s">
+      <c r="D54" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J54" s="2"/>
+      <c r="K54" s="9"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="F48" s="6"/>
-      <c r="G48" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="H49" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I49" s="6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="C50" s="6" t="s">
+      <c r="D55" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J55" s="2"/>
+      <c r="K55" s="9"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D50" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="C51" s="6" t="s">
+      <c r="D56" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="2"/>
+      <c r="K56" s="9"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D51" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="F52" s="6"/>
-      <c r="G52" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I55" s="6" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="F56" s="6"/>
-      <c r="G56" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
+      <c r="D57" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J57" s="2"/>
+      <c r="K57" s="9"/>
+    </row>
+    <row r="58">
       <c r="A58" s="6" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="59">
       <c r="A59" s="6" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="6" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="F60" s="6"/>
       <c r="G60" s="7" t="s">
-        <v>159</v>
+        <v>202</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="61">
       <c r="A61" s="6" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="6" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>18</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>166</v>
+        <v>209</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="6" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>18</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>166</v>
+        <v>209</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="6" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="F64" s="6"/>
       <c r="G64" s="7" t="s">
-        <v>159</v>
+        <v>202</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>161</v>
+        <v>204</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="6" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>18</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>166</v>
+        <v>209</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="6" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="F66" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="G66" s="16"/>
+        <v>213</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>214</v>
+      </c>
       <c r="H66" s="6" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="6" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="F67" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="G67" s="16"/>
+        <v>215</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>214</v>
+      </c>
       <c r="H67" s="6" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="6" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="F68" s="6"/>
       <c r="G68" s="7" t="s">
-        <v>159</v>
+        <v>202</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>161</v>
+        <v>204</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="6" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="F69" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="G69" s="16"/>
+        <v>216</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>214</v>
+      </c>
       <c r="H69" s="6" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="6" t="s">
-        <v>151</v>
+        <v>217</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="F70" s="6"/>
+        <v>219</v>
+      </c>
       <c r="G70" s="7" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>18</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="6" t="s">
-        <v>151</v>
+        <v>217</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="F71" s="6"/>
+        <v>222</v>
+      </c>
       <c r="G71" s="7" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>18</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="6" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F72" s="6"/>
       <c r="G72" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="6" t="s">
-        <v>151</v>
+        <v>217</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="F73" s="6"/>
+        <v>223</v>
+      </c>
       <c r="G73" s="7" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>18</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="6" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>18</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="J74" s="6" t="s">
-        <v>29</v>
+        <v>221</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="6" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>18</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="J75" s="6" t="s">
-        <v>29</v>
+        <v>221</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="6" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>212</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="F76" s="6"/>
       <c r="G76" s="7" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="J76" s="6" t="s">
-        <v>29</v>
+        <v>204</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="6" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>18</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="J77" s="6" t="s">
-        <v>29</v>
+        <v>221</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="6" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>46</v>
+        <v>229</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>216</v>
+        <v>230</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>231</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>217</v>
+        <v>18</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="6" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>46</v>
+        <v>229</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="F79" s="6" t="s">
-        <v>216</v>
+        <v>232</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>231</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>217</v>
+        <v>18</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>5</v>
+        <v>209</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="6" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>46</v>
+        <v>229</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>221</v>
+        <v>201</v>
+      </c>
+      <c r="F80" s="6"/>
+      <c r="G80" s="7" t="s">
+        <v>202</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="6" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>46</v>
+        <v>229</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="F81" s="6" t="s">
-        <v>216</v>
+        <v>233</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>231</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>217</v>
+        <v>18</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="6" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>230</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="G82" s="10"/>
       <c r="H82" s="6" t="s">
-        <v>217</v>
+        <v>5</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="6" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>230</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="G83" s="10"/>
       <c r="H83" s="6" t="s">
-        <v>217</v>
+        <v>5</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="6" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="F84" s="6" t="s">
-        <v>230</v>
+        <v>201</v>
+      </c>
+      <c r="F84" s="6"/>
+      <c r="G84" s="7" t="s">
+        <v>202</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>231</v>
+        <v>204</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="6" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="E85" s="6" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>230</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="G85" s="10"/>
       <c r="H85" s="6" t="s">
-        <v>217</v>
+        <v>5</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
+        <v>241</v>
+      </c>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I86" s="6" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="G88" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="G91" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="G93" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I94" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I95" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="A96" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I96" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="A97" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="G97" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I97" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="J98" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="A99" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I99" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="J99" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="A100" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I100" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="J100" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="A101" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="G101" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I101" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="J101" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="A102" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="I102" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="A103" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="I103" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="A104" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="I104" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="A105" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="I105" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="A106" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="E106" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="I106" s="6" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="A107" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="H107" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="I107" s="6" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="A108" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="I108" s="6" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="A109" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="H109" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="I109" s="6" t="s">
+        <v>289</v>
+      </c>
+    </row>
     <row r="110" ht="15.75" customHeight="1"/>
     <row r="111" ht="15.75" customHeight="1"/>
     <row r="112" ht="15.75" customHeight="1"/>
@@ -4459,6 +5307,30 @@
     <row r="1047" ht="15.75" customHeight="1"/>
     <row r="1048" ht="15.75" customHeight="1"/>
     <row r="1049" ht="15.75" customHeight="1"/>
+    <row r="1050" ht="15.75" customHeight="1"/>
+    <row r="1051" ht="15.75" customHeight="1"/>
+    <row r="1052" ht="15.75" customHeight="1"/>
+    <row r="1053" ht="15.75" customHeight="1"/>
+    <row r="1054" ht="15.75" customHeight="1"/>
+    <row r="1055" ht="15.75" customHeight="1"/>
+    <row r="1056" ht="15.75" customHeight="1"/>
+    <row r="1057" ht="15.75" customHeight="1"/>
+    <row r="1058" ht="15.75" customHeight="1"/>
+    <row r="1059" ht="15.75" customHeight="1"/>
+    <row r="1060" ht="15.75" customHeight="1"/>
+    <row r="1061" ht="15.75" customHeight="1"/>
+    <row r="1062" ht="15.75" customHeight="1"/>
+    <row r="1063" ht="15.75" customHeight="1"/>
+    <row r="1064" ht="15.75" customHeight="1"/>
+    <row r="1065" ht="15.75" customHeight="1"/>
+    <row r="1066" ht="15.75" customHeight="1"/>
+    <row r="1067" ht="15.75" customHeight="1"/>
+    <row r="1068" ht="15.75" customHeight="1"/>
+    <row r="1069" ht="15.75" customHeight="1"/>
+    <row r="1070" ht="15.75" customHeight="1"/>
+    <row r="1071" ht="15.75" customHeight="1"/>
+    <row r="1072" ht="15.75" customHeight="1"/>
+    <row r="1073" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="G2"/>
@@ -4474,67 +5346,89 @@
     <hyperlink r:id="rId11" ref="G13"/>
     <hyperlink r:id="rId12" ref="G14"/>
     <hyperlink r:id="rId13" ref="G15"/>
-    <hyperlink r:id="rId14" ref="G16"/>
-    <hyperlink r:id="rId15" ref="G17"/>
-    <hyperlink r:id="rId16" ref="G18"/>
-    <hyperlink r:id="rId17" ref="G19"/>
-    <hyperlink r:id="rId18" ref="G20"/>
-    <hyperlink r:id="rId19" ref="G21"/>
-    <hyperlink r:id="rId20" ref="G22"/>
-    <hyperlink r:id="rId21" ref="G23"/>
-    <hyperlink r:id="rId22" ref="G24"/>
-    <hyperlink r:id="rId23" ref="G25"/>
-    <hyperlink r:id="rId24" ref="G26"/>
-    <hyperlink r:id="rId25" ref="I26"/>
-    <hyperlink r:id="rId26" ref="G27"/>
-    <hyperlink r:id="rId27" ref="G28"/>
-    <hyperlink r:id="rId28" ref="G29"/>
-    <hyperlink r:id="rId29" ref="G30"/>
-    <hyperlink r:id="rId30" ref="G32"/>
-    <hyperlink r:id="rId31" ref="G33"/>
-    <hyperlink r:id="rId32" ref="G34"/>
-    <hyperlink r:id="rId33" ref="G35"/>
-    <hyperlink r:id="rId34" ref="G36"/>
-    <hyperlink r:id="rId35" location="/home" ref="G37"/>
-    <hyperlink r:id="rId36" ref="G38"/>
-    <hyperlink r:id="rId37" ref="G39"/>
-    <hyperlink r:id="rId38" ref="G42"/>
-    <hyperlink r:id="rId39" ref="G43"/>
-    <hyperlink r:id="rId40" ref="G44"/>
-    <hyperlink r:id="rId41" ref="G45"/>
-    <hyperlink r:id="rId42" ref="G46"/>
-    <hyperlink r:id="rId43" ref="G47"/>
-    <hyperlink r:id="rId44" ref="G48"/>
-    <hyperlink r:id="rId45" ref="G49"/>
-    <hyperlink r:id="rId46" ref="G50"/>
-    <hyperlink r:id="rId47" ref="G51"/>
-    <hyperlink r:id="rId48" ref="G52"/>
-    <hyperlink r:id="rId49" ref="G53"/>
-    <hyperlink r:id="rId50" ref="G54"/>
-    <hyperlink r:id="rId51" ref="G55"/>
-    <hyperlink r:id="rId52" ref="G56"/>
-    <hyperlink r:id="rId53" ref="G57"/>
-    <hyperlink r:id="rId54" ref="G58"/>
-    <hyperlink r:id="rId55" ref="G59"/>
-    <hyperlink r:id="rId56" ref="G60"/>
-    <hyperlink r:id="rId57" ref="G61"/>
-    <hyperlink r:id="rId58" ref="G62"/>
-    <hyperlink r:id="rId59" ref="G63"/>
-    <hyperlink r:id="rId60" ref="G64"/>
-    <hyperlink r:id="rId61" ref="G65"/>
+    <hyperlink r:id="rId14" ref="G17"/>
+    <hyperlink r:id="rId15" ref="G18"/>
+    <hyperlink r:id="rId16" ref="G19"/>
+    <hyperlink r:id="rId17" ref="G20"/>
+    <hyperlink r:id="rId18" ref="G21"/>
+    <hyperlink r:id="rId19" location="/home" ref="G22"/>
+    <hyperlink r:id="rId20" ref="G26"/>
+    <hyperlink r:id="rId21" ref="G27"/>
+    <hyperlink r:id="rId22" ref="G28"/>
+    <hyperlink r:id="rId23" ref="G29"/>
+    <hyperlink r:id="rId24" ref="G30"/>
+    <hyperlink r:id="rId25" ref="G31"/>
+    <hyperlink r:id="rId26" ref="G32"/>
+    <hyperlink r:id="rId27" ref="G33"/>
+    <hyperlink r:id="rId28" ref="G34"/>
+    <hyperlink r:id="rId29" ref="G35"/>
+    <hyperlink r:id="rId30" ref="G36"/>
+    <hyperlink r:id="rId31" ref="G37"/>
+    <hyperlink r:id="rId32" ref="G38"/>
+    <hyperlink r:id="rId33" ref="I38"/>
+    <hyperlink r:id="rId34" ref="G39"/>
+    <hyperlink r:id="rId35" ref="G40"/>
+    <hyperlink r:id="rId36" ref="G41"/>
+    <hyperlink r:id="rId37" ref="G42"/>
+    <hyperlink r:id="rId38" ref="G44"/>
+    <hyperlink r:id="rId39" ref="G45"/>
+    <hyperlink r:id="rId40" ref="G46"/>
+    <hyperlink r:id="rId41" ref="G47"/>
+    <hyperlink r:id="rId42" ref="G48"/>
+    <hyperlink r:id="rId43" location="/home" ref="G49"/>
+    <hyperlink r:id="rId44" ref="G50"/>
+    <hyperlink r:id="rId45" ref="G51"/>
+    <hyperlink r:id="rId46" ref="G52"/>
+    <hyperlink r:id="rId47" ref="G53"/>
+    <hyperlink r:id="rId48" ref="G54"/>
+    <hyperlink r:id="rId49" ref="G55"/>
+    <hyperlink r:id="rId50" ref="G56"/>
+    <hyperlink r:id="rId51" ref="G57"/>
+    <hyperlink r:id="rId52" ref="G58"/>
+    <hyperlink r:id="rId53" ref="G59"/>
+    <hyperlink r:id="rId54" ref="G60"/>
+    <hyperlink r:id="rId55" ref="G61"/>
+    <hyperlink r:id="rId56" ref="G62"/>
+    <hyperlink r:id="rId57" ref="G63"/>
+    <hyperlink r:id="rId58" ref="G64"/>
+    <hyperlink r:id="rId59" ref="G65"/>
+    <hyperlink r:id="rId60" ref="G66"/>
+    <hyperlink r:id="rId61" ref="G67"/>
     <hyperlink r:id="rId62" ref="G68"/>
-    <hyperlink r:id="rId63" ref="G70"/>
-    <hyperlink r:id="rId64" ref="G71"/>
-    <hyperlink r:id="rId65" ref="G72"/>
-    <hyperlink r:id="rId66" ref="G73"/>
-    <hyperlink r:id="rId67" ref="G74"/>
-    <hyperlink r:id="rId68" ref="G75"/>
-    <hyperlink r:id="rId69" ref="G76"/>
-    <hyperlink r:id="rId70" ref="G77"/>
+    <hyperlink r:id="rId63" ref="G69"/>
+    <hyperlink r:id="rId64" ref="G70"/>
+    <hyperlink r:id="rId65" ref="G71"/>
+    <hyperlink r:id="rId66" ref="G72"/>
+    <hyperlink r:id="rId67" ref="G73"/>
+    <hyperlink r:id="rId68" ref="G74"/>
+    <hyperlink r:id="rId69" ref="G75"/>
+    <hyperlink r:id="rId70" ref="G76"/>
+    <hyperlink r:id="rId71" ref="G77"/>
+    <hyperlink r:id="rId72" ref="G78"/>
+    <hyperlink r:id="rId73" ref="G79"/>
+    <hyperlink r:id="rId74" ref="G80"/>
+    <hyperlink r:id="rId75" ref="G81"/>
+    <hyperlink r:id="rId76" ref="G84"/>
+    <hyperlink r:id="rId77" ref="G86"/>
+    <hyperlink r:id="rId78" ref="G87"/>
+    <hyperlink r:id="rId79" ref="G88"/>
+    <hyperlink r:id="rId80" ref="G89"/>
+    <hyperlink r:id="rId81" ref="G90"/>
+    <hyperlink r:id="rId82" ref="G91"/>
+    <hyperlink r:id="rId83" ref="G92"/>
+    <hyperlink r:id="rId84" ref="G93"/>
+    <hyperlink r:id="rId85" ref="G94"/>
+    <hyperlink r:id="rId86" ref="G95"/>
+    <hyperlink r:id="rId87" ref="G96"/>
+    <hyperlink r:id="rId88" ref="G97"/>
+    <hyperlink r:id="rId89" ref="G98"/>
+    <hyperlink r:id="rId90" ref="G99"/>
+    <hyperlink r:id="rId91" ref="G100"/>
+    <hyperlink r:id="rId92" ref="G101"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId71"/>
+  <drawing r:id="rId93"/>
 </worksheet>
 </file>
--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="YVyT860PVjy1j1GorqR2dylNg14PuGH2VgNk0fkAIZc="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="mVYAxCEhvWkd6fsJKxrQ7n6B6HYocaG4rDqhgGyG9KE="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="296">
   <si>
     <t>County</t>
   </si>
@@ -69,16 +69,13 @@
     <t>cityclerk@rivierabeach.org</t>
   </si>
   <si>
-    <t>https://www.rivierabch.com/clerk/records-request</t>
-  </si>
-  <si>
-    <t>Portal</t>
-  </si>
-  <si>
-    <t>Green Next Button -&gt; Standard Public Records</t>
-  </si>
-  <si>
-    <t>No</t>
+    <t>https://rivierabeachfl-energovweb.tylerhost.net/apps/SelfService#/home</t>
+  </si>
+  <si>
+    <t>Self Lookup</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
   <si>
     <t>2025-08-06</t>
@@ -118,9 +115,6 @@
     <t>PBC ERM Portal. If doesn't work, use FDH</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>fire</t>
   </si>
   <si>
@@ -143,6 +137,9 @@
   </si>
   <si>
     <t>https://boyntonbeachfl.mycusthelp.com/WEBAPP/_rs/(S(grztt2kh4fy0zchy4lqoj4oa))/RequestOpen.aspx?rqst=66</t>
+  </si>
+  <si>
+    <t>Portal</t>
   </si>
   <si>
     <t>Select Building Divison</t>
@@ -404,12 +401,15 @@
     <t>https://miamidadecounty.govqa.us/WEBAPP/_rs/(S(vcgebaolranwuuj2uiqutnes))/RequestSelect.aspx?sSessionID=206170212118:35498EAHIOTOEGXZVNDLBQVFUPJ</t>
   </si>
   <si>
+    <t>Portal + Lookup</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <rFont val="Calibri"/>
         <color theme="1"/>
       </rPr>
-      <t xml:space="preserve">Check for permits here: </t>
+      <t xml:space="preserve">Select Regulatory and Economic Resources | Check for permits here: </t>
     </r>
     <r>
       <rPr>
@@ -433,10 +433,7 @@
     <t>https://gisweb.miamidade.gov/landmanagement/</t>
   </si>
   <si>
-    <t>Self Lookup</t>
-  </si>
-  <si>
-    <t>Use self lookup with FOLIO</t>
+    <t>Select Regulatory and Economic Resources | Use self lookup with FOLIO</t>
   </si>
   <si>
     <t>*</t>
@@ -451,10 +448,7 @@
     <t>DermRecords@miamidade.gov</t>
   </si>
   <si>
-    <t>https://ecmrer.miamidade.gov/home</t>
-  </si>
-  <si>
-    <t>Use folio to lookup</t>
+    <t>Use email</t>
   </si>
   <si>
     <t>Miami Gardens</t>
@@ -625,7 +619,7 @@
     <t>City of Cutler Bay Planning Department</t>
   </si>
   <si>
-    <t>Opa Locka</t>
+    <t>Opa-Locka</t>
   </si>
   <si>
     <t>City of Opa Locka Building Department</t>
@@ -640,6 +634,24 @@
     <t>City of Opa Locka Planning Department</t>
   </si>
   <si>
+    <t>Hialeah</t>
+  </si>
+  <si>
+    <t>City of Hialeah Building Department</t>
+  </si>
+  <si>
+    <t>https://cityofhialeahfl.nextrequest.com/requests/new</t>
+  </si>
+  <si>
+    <t>Next Request Portal</t>
+  </si>
+  <si>
+    <t>City of Hialeah Planning Department</t>
+  </si>
+  <si>
+    <t>City of Hialeah Fire Department</t>
+  </si>
+  <si>
     <t>Broward</t>
   </si>
   <si>
@@ -884,9 +896,6 @@
   </si>
   <si>
     <t>PublicRecordRequest@ocfl.net</t>
-  </si>
-  <si>
-    <t>Use email</t>
   </si>
   <si>
     <t>Email + FastTrack lookup if login works</t>
@@ -961,7 +970,7 @@
     <font>
       <u/>
       <sz val="11.0"/>
-      <color theme="10"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1002,7 +1011,7 @@
     <font>
       <u/>
       <sz val="11.0"/>
-      <color rgb="FF0000FF"/>
+      <color theme="10"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1045,7 +1054,9 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -1071,14 +1082,12 @@
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1368,13 +1377,13 @@
         <v>18</v>
       </c>
       <c r="I2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -1385,10 +1394,10 @@
         <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>15</v>
@@ -1403,13 +1412,13 @@
         <v>18</v>
       </c>
       <c r="I3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -1420,24 +1429,24 @@
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="J4" s="6" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -1448,26 +1457,26 @@
         <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -1475,28 +1484,28 @@
         <v>11</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -1504,28 +1513,28 @@
         <v>11</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
@@ -1533,27 +1542,27 @@
         <v>11</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="J8" s="6" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -1561,28 +1570,28 @@
         <v>11</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -1590,26 +1599,26 @@
         <v>11</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="H10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="I10" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="9"/>
@@ -1619,26 +1628,26 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="H11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="I11" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="9"/>
@@ -1648,26 +1657,26 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="H12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="I12" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="9"/>
@@ -1677,26 +1686,26 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="H13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="I13" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="9"/>
@@ -1706,26 +1715,26 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="H14" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="I14" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="9"/>
@@ -1735,26 +1744,26 @@
         <v>11</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="H15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="I15" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="9"/>
@@ -1764,21 +1773,21 @@
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G16" s="10"/>
       <c r="H16" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>5</v>
@@ -1791,697 +1800,697 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3"/>
       <c r="G17" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="I17" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="9"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="H18" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="J18" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>75</v>
-      </c>
       <c r="H19" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="G20" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G21" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I21" s="2" t="s">
+      <c r="J21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K21" s="9" t="s">
         <v>81</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="H22" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="I22" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="9"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G23" s="12"/>
       <c r="H23" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="9"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G24" s="12"/>
       <c r="H24" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="9"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="9"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G26" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K26" s="9" t="s">
         <v>96</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G27" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="J27" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G28" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H28" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="J28" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G29" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="J29" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D30" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="G30" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="H30" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K30" s="9" t="s">
         <v>108</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="C31" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K31" s="9" t="s">
         <v>110</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K31" s="9" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="C32" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E32" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G32" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>108</v>
-      </c>
       <c r="H32" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="C33" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D33" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K33" s="9" t="s">
         <v>113</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="G34" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="H34" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K34" s="9" t="s">
         <v>108</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D35" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K35" s="9" t="s">
         <v>110</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E36" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G36" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G36" s="5" t="s">
-        <v>108</v>
-      </c>
       <c r="H36" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D37" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K37" s="9" t="s">
         <v>113</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D38" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="F38" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="G38" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="H38" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I38" s="13" t="s">
         <v>120</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>121</v>
@@ -2496,1226 +2505,1233 @@
         <v>124</v>
       </c>
       <c r="H39" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="I39" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="J39" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" s="3" t="s">
+      <c r="E40" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="F40" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="G40" s="5"/>
+      <c r="H40" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G40" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="J40" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D41" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="G41" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="H41" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="I41" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="J41" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D42" s="2" t="s">
+      <c r="F42" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G42" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G42" s="4" t="s">
+      <c r="I42" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="J42" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D43" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="I42" s="2" t="s">
+      <c r="E43" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="J42" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D43" s="15" t="s">
+      <c r="F43" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="G43" s="15"/>
+      <c r="H43" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="F43" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="I43" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="J43" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K43" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L43" s="15"/>
-      <c r="M43" s="15"/>
-      <c r="N43" s="15"/>
-      <c r="O43" s="15"/>
-      <c r="P43" s="15"/>
-      <c r="Q43" s="15"/>
-      <c r="R43" s="15"/>
-      <c r="S43" s="15"/>
-      <c r="T43" s="15"/>
-      <c r="U43" s="15"/>
-      <c r="V43" s="15"/>
-      <c r="W43" s="15"/>
-      <c r="X43" s="15"/>
-      <c r="Y43" s="15"/>
-      <c r="Z43" s="15"/>
+      <c r="I43" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="J43" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="L43" s="16"/>
+      <c r="M43" s="16"/>
+      <c r="N43" s="16"/>
+      <c r="O43" s="16"/>
+      <c r="P43" s="16"/>
+      <c r="Q43" s="16"/>
+      <c r="R43" s="16"/>
+      <c r="S43" s="16"/>
+      <c r="T43" s="16"/>
+      <c r="U43" s="16"/>
+      <c r="V43" s="16"/>
+      <c r="W43" s="16"/>
+      <c r="X43" s="16"/>
+      <c r="Y43" s="16"/>
+      <c r="Z43" s="16"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D44" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="G44" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="H44" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G44" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="J44" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K44" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E45" s="3" t="s">
+      <c r="F45" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G45" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G45" s="16" t="s">
-        <v>152</v>
-      </c>
       <c r="H45" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="J46" s="2"/>
       <c r="K46" s="9"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="9"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="9"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="H49" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G49" s="5" t="s">
+      <c r="I49" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="J49" s="2"/>
       <c r="K49" s="9"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J50" s="2"/>
       <c r="K50" s="9"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="J51" s="2"/>
       <c r="K51" s="9"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="9"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="9"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="H54" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="G54" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="I54" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="9"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="H55" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="G55" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="I55" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="9"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="9"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="J57" s="2"/>
       <c r="K57" s="9"/>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="H58" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D58" s="6" t="s">
+      <c r="J58" s="2"/>
+      <c r="K58" s="9"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="G58" s="7" t="s">
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="J59" s="2"/>
+      <c r="K59" s="9"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="H58" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="s">
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="H60" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I60" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="F60" s="6"/>
-      <c r="G60" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>204</v>
-      </c>
+      <c r="J60" s="2"/>
+      <c r="K60" s="9"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="H61" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="I61" s="6" t="s">
+      <c r="B62" s="6" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>206</v>
-      </c>
       <c r="C62" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>18</v>
+        <v>202</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B63" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="F63" s="6"/>
+      <c r="G63" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="C63" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="G63" s="7" t="s">
+      <c r="H63" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="I63" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="H63" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I63" s="6" t="s">
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D64" s="6" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D64" s="6" t="s">
+      <c r="G64" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="F64" s="6"/>
-      <c r="G64" s="7" t="s">
+      <c r="H64" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="H64" s="6" t="s">
+      <c r="I64" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="I64" s="6" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>211</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B66" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G66" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="C66" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D66" s="6" t="s">
+      <c r="H66" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I66" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="G66" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I66" s="6" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>215</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="F67" s="6"/>
       <c r="G67" s="7" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>18</v>
+        <v>207</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B68" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G68" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="C68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="F68" s="6"/>
-      <c r="G68" s="7" t="s">
-        <v>202</v>
-      </c>
       <c r="H68" s="6" t="s">
-        <v>203</v>
+        <v>36</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="6" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>219</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="6" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>222</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="F71" s="6"/>
       <c r="G71" s="7" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>18</v>
+        <v>207</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B72" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="G72" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="F72" s="6"/>
-      <c r="G72" s="7" t="s">
-        <v>202</v>
-      </c>
       <c r="H72" s="6" t="s">
-        <v>203</v>
+        <v>36</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="6" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>223</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="6" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="B74" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="G74" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C74" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D74" s="6" t="s">
+      <c r="H74" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I74" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="G74" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I74" s="6" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>227</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="F75" s="6"/>
       <c r="G75" s="7" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>18</v>
+        <v>207</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="6" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="B76" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="G76" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C76" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="F76" s="6"/>
-      <c r="G76" s="7" t="s">
-        <v>202</v>
-      </c>
       <c r="H76" s="6" t="s">
-        <v>203</v>
+        <v>36</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D78" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="G78" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="G78" s="7" t="s">
-        <v>231</v>
-      </c>
       <c r="H78" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>232</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="F79" s="6"/>
       <c r="G79" s="7" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>18</v>
+        <v>207</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="F80" s="6"/>
+        <v>232</v>
+      </c>
       <c r="G80" s="7" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>203</v>
+        <v>36</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D82" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G82" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="F82" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="G82" s="10"/>
       <c r="H82" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="F83" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="G83" s="10"/>
+        <v>205</v>
+      </c>
+      <c r="F83" s="6"/>
+      <c r="G83" s="7" t="s">
+        <v>206</v>
+      </c>
       <c r="H83" s="6" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>237</v>
+        <v>208</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="F84" s="6"/>
+        <v>237</v>
+      </c>
       <c r="G84" s="7" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>203</v>
+        <v>36</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>239</v>
@@ -3733,233 +3749,218 @@
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B86" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D86" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="C86" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>243</v>
-      </c>
       <c r="F86" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="G86" s="7" t="s">
-        <v>245</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="G86" s="10"/>
       <c r="H86" s="6" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="F87" s="6" t="s">
-        <v>244</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="F87" s="6"/>
       <c r="G87" s="7" t="s">
-        <v>245</v>
+        <v>206</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>18</v>
+        <v>207</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>246</v>
+        <v>208</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="G88" s="7" t="s">
+      <c r="G88" s="10"/>
+      <c r="H88" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I88" s="6" t="s">
         <v>245</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I88" s="6" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D89" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="G89" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="F89" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="G89" s="7" t="s">
-        <v>245</v>
-      </c>
       <c r="H89" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="E90" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="F90" s="6" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B91" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="G91" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I91" s="6" t="s">
         <v>250</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="E91" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="G91" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="H91" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I91" s="6" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B92" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I92" s="6" t="s">
         <v>250</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="E92" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="G92" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I92" s="6" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>259</v>
@@ -3968,408 +3969,492 @@
         <v>15</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E95" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="G98" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="B98" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>268</v>
-      </c>
       <c r="H98" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="J98" s="6" t="s">
-        <v>29</v>
+        <v>258</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="G99" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="B99" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="G99" s="7" t="s">
-        <v>268</v>
-      </c>
       <c r="H99" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="J99" s="6" t="s">
-        <v>29</v>
+        <v>258</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="G100" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="B100" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="G100" s="7" t="s">
-        <v>268</v>
-      </c>
       <c r="H100" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="J100" s="6" t="s">
-        <v>29</v>
+        <v>258</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="6" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D101" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="G101" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="G101" s="7" t="s">
-        <v>268</v>
-      </c>
       <c r="H101" s="6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="6" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>54</v>
+        <v>270</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="F102" s="6" t="s">
-        <v>275</v>
+      <c r="G102" s="7" t="s">
+        <v>272</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>276</v>
+        <v>36</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>277</v>
+        <v>273</v>
+      </c>
+      <c r="J102" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="G103" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I103" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="B103" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="I103" s="6" t="s">
-        <v>5</v>
+      <c r="J103" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I104" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="B104" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="I104" s="6" t="s">
-        <v>282</v>
+      <c r="J104" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="6" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>276</v>
+        <v>130</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>90</v>
+        <v>280</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="6" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>285</v>
+        <v>53</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="E106" s="6" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>276</v>
+        <v>130</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>289</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H107" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="B107" s="6" t="s">
+      <c r="I107" s="6" t="s">
         <v>285</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="E107" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="F107" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="H107" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="I107" s="6" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="6" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>285</v>
+        <v>53</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="E108" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>276</v>
+        <v>130</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>289</v>
+        <v>89</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D109" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="H109" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="I109" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="E109" s="6" t="s">
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="F109" s="6" t="s">
+      <c r="B110" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="H109" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="I109" s="6" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
+      <c r="C110" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="I110" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="A111" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="F111" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="H111" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="I111" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="A112" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="E112" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="I112" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
     <row r="113" ht="15.75" customHeight="1"/>
     <row r="114" ht="15.75" customHeight="1"/>
     <row r="115" ht="15.75" customHeight="1"/>
@@ -5331,10 +5416,13 @@
     <row r="1071" ht="15.75" customHeight="1"/>
     <row r="1072" ht="15.75" customHeight="1"/>
     <row r="1073" ht="15.75" customHeight="1"/>
+    <row r="1074" ht="15.75" customHeight="1"/>
+    <row r="1075" ht="15.75" customHeight="1"/>
+    <row r="1076" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="G2"/>
-    <hyperlink r:id="rId2" ref="G3"/>
+    <hyperlink r:id="rId1" location="/home" ref="G2"/>
+    <hyperlink r:id="rId2" location="/home" ref="G3"/>
     <hyperlink r:id="rId3" ref="G4"/>
     <hyperlink r:id="rId4" ref="G6"/>
     <hyperlink r:id="rId5" ref="G7"/>
@@ -5367,68 +5455,70 @@
     <hyperlink r:id="rId32" ref="G38"/>
     <hyperlink r:id="rId33" ref="I38"/>
     <hyperlink r:id="rId34" ref="G39"/>
-    <hyperlink r:id="rId35" ref="G40"/>
-    <hyperlink r:id="rId36" ref="G41"/>
-    <hyperlink r:id="rId37" ref="G42"/>
-    <hyperlink r:id="rId38" ref="G44"/>
-    <hyperlink r:id="rId39" ref="G45"/>
-    <hyperlink r:id="rId40" ref="G46"/>
-    <hyperlink r:id="rId41" ref="G47"/>
-    <hyperlink r:id="rId42" ref="G48"/>
-    <hyperlink r:id="rId43" location="/home" ref="G49"/>
-    <hyperlink r:id="rId44" ref="G50"/>
-    <hyperlink r:id="rId45" ref="G51"/>
-    <hyperlink r:id="rId46" ref="G52"/>
-    <hyperlink r:id="rId47" ref="G53"/>
-    <hyperlink r:id="rId48" ref="G54"/>
-    <hyperlink r:id="rId49" ref="G55"/>
-    <hyperlink r:id="rId50" ref="G56"/>
-    <hyperlink r:id="rId51" ref="G57"/>
-    <hyperlink r:id="rId52" ref="G58"/>
-    <hyperlink r:id="rId53" ref="G59"/>
-    <hyperlink r:id="rId54" ref="G60"/>
-    <hyperlink r:id="rId55" ref="G61"/>
-    <hyperlink r:id="rId56" ref="G62"/>
-    <hyperlink r:id="rId57" ref="G63"/>
-    <hyperlink r:id="rId58" ref="G64"/>
-    <hyperlink r:id="rId59" ref="G65"/>
-    <hyperlink r:id="rId60" ref="G66"/>
-    <hyperlink r:id="rId61" ref="G67"/>
-    <hyperlink r:id="rId62" ref="G68"/>
-    <hyperlink r:id="rId63" ref="G69"/>
-    <hyperlink r:id="rId64" ref="G70"/>
-    <hyperlink r:id="rId65" ref="G71"/>
-    <hyperlink r:id="rId66" ref="G72"/>
-    <hyperlink r:id="rId67" ref="G73"/>
-    <hyperlink r:id="rId68" ref="G74"/>
-    <hyperlink r:id="rId69" ref="G75"/>
-    <hyperlink r:id="rId70" ref="G76"/>
-    <hyperlink r:id="rId71" ref="G77"/>
-    <hyperlink r:id="rId72" ref="G78"/>
-    <hyperlink r:id="rId73" ref="G79"/>
-    <hyperlink r:id="rId74" ref="G80"/>
-    <hyperlink r:id="rId75" ref="G81"/>
-    <hyperlink r:id="rId76" ref="G84"/>
-    <hyperlink r:id="rId77" ref="G86"/>
+    <hyperlink r:id="rId35" ref="G41"/>
+    <hyperlink r:id="rId36" ref="G42"/>
+    <hyperlink r:id="rId37" ref="G44"/>
+    <hyperlink r:id="rId38" ref="G45"/>
+    <hyperlink r:id="rId39" ref="G46"/>
+    <hyperlink r:id="rId40" ref="G47"/>
+    <hyperlink r:id="rId41" ref="G48"/>
+    <hyperlink r:id="rId42" location="/home" ref="G49"/>
+    <hyperlink r:id="rId43" ref="G50"/>
+    <hyperlink r:id="rId44" ref="G51"/>
+    <hyperlink r:id="rId45" ref="G52"/>
+    <hyperlink r:id="rId46" ref="G53"/>
+    <hyperlink r:id="rId47" ref="G54"/>
+    <hyperlink r:id="rId48" ref="G55"/>
+    <hyperlink r:id="rId49" ref="G56"/>
+    <hyperlink r:id="rId50" ref="G57"/>
+    <hyperlink r:id="rId51" ref="G58"/>
+    <hyperlink r:id="rId52" ref="G59"/>
+    <hyperlink r:id="rId53" ref="G60"/>
+    <hyperlink r:id="rId54" ref="G61"/>
+    <hyperlink r:id="rId55" ref="G62"/>
+    <hyperlink r:id="rId56" ref="G63"/>
+    <hyperlink r:id="rId57" ref="G64"/>
+    <hyperlink r:id="rId58" ref="G65"/>
+    <hyperlink r:id="rId59" ref="G66"/>
+    <hyperlink r:id="rId60" ref="G67"/>
+    <hyperlink r:id="rId61" ref="G68"/>
+    <hyperlink r:id="rId62" ref="G69"/>
+    <hyperlink r:id="rId63" ref="G70"/>
+    <hyperlink r:id="rId64" ref="G71"/>
+    <hyperlink r:id="rId65" ref="G72"/>
+    <hyperlink r:id="rId66" ref="G73"/>
+    <hyperlink r:id="rId67" ref="G74"/>
+    <hyperlink r:id="rId68" ref="G75"/>
+    <hyperlink r:id="rId69" ref="G76"/>
+    <hyperlink r:id="rId70" ref="G77"/>
+    <hyperlink r:id="rId71" ref="G78"/>
+    <hyperlink r:id="rId72" ref="G79"/>
+    <hyperlink r:id="rId73" ref="G80"/>
+    <hyperlink r:id="rId74" ref="G81"/>
+    <hyperlink r:id="rId75" ref="G82"/>
+    <hyperlink r:id="rId76" ref="G83"/>
+    <hyperlink r:id="rId77" ref="G84"/>
     <hyperlink r:id="rId78" ref="G87"/>
-    <hyperlink r:id="rId79" ref="G88"/>
-    <hyperlink r:id="rId80" ref="G89"/>
-    <hyperlink r:id="rId81" ref="G90"/>
-    <hyperlink r:id="rId82" ref="G91"/>
-    <hyperlink r:id="rId83" ref="G92"/>
-    <hyperlink r:id="rId84" ref="G93"/>
-    <hyperlink r:id="rId85" ref="G94"/>
-    <hyperlink r:id="rId86" ref="G95"/>
-    <hyperlink r:id="rId87" ref="G96"/>
-    <hyperlink r:id="rId88" ref="G97"/>
-    <hyperlink r:id="rId89" ref="G98"/>
-    <hyperlink r:id="rId90" ref="G99"/>
-    <hyperlink r:id="rId91" ref="G100"/>
-    <hyperlink r:id="rId92" ref="G101"/>
+    <hyperlink r:id="rId79" ref="G89"/>
+    <hyperlink r:id="rId80" ref="G90"/>
+    <hyperlink r:id="rId81" ref="G91"/>
+    <hyperlink r:id="rId82" ref="G92"/>
+    <hyperlink r:id="rId83" ref="G93"/>
+    <hyperlink r:id="rId84" ref="G94"/>
+    <hyperlink r:id="rId85" ref="G95"/>
+    <hyperlink r:id="rId86" ref="G96"/>
+    <hyperlink r:id="rId87" ref="G97"/>
+    <hyperlink r:id="rId88" ref="G98"/>
+    <hyperlink r:id="rId89" ref="G99"/>
+    <hyperlink r:id="rId90" ref="G100"/>
+    <hyperlink r:id="rId91" ref="G101"/>
+    <hyperlink r:id="rId92" ref="G102"/>
+    <hyperlink r:id="rId93" ref="G103"/>
+    <hyperlink r:id="rId94" ref="G104"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId93"/>
+  <drawing r:id="rId95"/>
 </worksheet>
 </file>
--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="mVYAxCEhvWkd6fsJKxrQ7n6B6HYocaG4rDqhgGyG9KE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="lRGfBzzT8FExW9Yv7l7mHJMhDQd134GPNyZykox/3uY="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="314">
   <si>
     <t>County</t>
   </si>
@@ -234,6 +234,51 @@
   </si>
   <si>
     <t xml:space="preserve">Portal </t>
+  </si>
+  <si>
+    <t>Pahokee</t>
+  </si>
+  <si>
+    <t>City of Pahokee Building Department</t>
+  </si>
+  <si>
+    <t>https://www.cityofpahokee.com/home/webforms/request-document-city</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Use link</t>
+  </si>
+  <si>
+    <t>City of Pahokee Planning Department</t>
+  </si>
+  <si>
+    <t>City of Pahokee Environmental Department</t>
+  </si>
+  <si>
+    <t>City of Pahokee Fire Department</t>
+  </si>
+  <si>
+    <t>Delray</t>
+  </si>
+  <si>
+    <t>City of Delray Building Department</t>
+  </si>
+  <si>
+    <t>https://city-delraybeach.govqa.us/WEBAPP/_rs/(S(vmgkkqn3vefsw0blriyshuqe))/requestopen.aspx?sSessionID=3514539110:43072VJIFUKWURKRERNAX[KJOBIXW&amp;rqst=1</t>
+  </si>
+  <si>
+    <t>Use Portal</t>
+  </si>
+  <si>
+    <t>City of Delray Planning Department</t>
+  </si>
+  <si>
+    <t>City of Delray Environmental Department</t>
+  </si>
+  <si>
+    <t>City of Delray Fire Department</t>
   </si>
   <si>
     <t>Lee</t>
@@ -448,454 +493,463 @@
     <t>DermRecords@miamidade.gov</t>
   </si>
   <si>
+    <t>https://ecmrer.miamidade.gov/document-search</t>
+  </si>
+  <si>
+    <t>Use self lookup</t>
+  </si>
+  <si>
+    <t>Miami Gardens</t>
+  </si>
+  <si>
+    <t>City of Miami Gardens — Building Services</t>
+  </si>
+  <si>
+    <t>Mario Bataille, CMC, City Clerk</t>
+  </si>
+  <si>
+    <t>recordsrequest@miamigardens-fl.gov</t>
+  </si>
+  <si>
+    <t>https://trakit.miamilakes-fl.gov/etrakit/Search/permit.aspx</t>
+  </si>
+  <si>
+    <t>Use portal to search for building permits</t>
+  </si>
+  <si>
+    <t>Search by FOLIO/APN (no dashes)</t>
+  </si>
+  <si>
+    <t>City of Miami Gardens — Planning &amp; Zoning</t>
+  </si>
+  <si>
+    <t>https://miamigardensfl.justfoia.com/publicportal</t>
+  </si>
+  <si>
+    <t>Clerk Portal + Email (All-in-one)</t>
+  </si>
+  <si>
+    <t>Public records portal; City Clerk is custodian</t>
+  </si>
+  <si>
+    <t>Miami-Dade Fire Rescue — Public Records</t>
+  </si>
+  <si>
+    <t>Christie Toledo-Fernandez</t>
+  </si>
+  <si>
+    <t>Christie.Toledo-Fernandez@miamidade.gov</t>
+  </si>
+  <si>
+    <t>Direct E-MAIL: Special MDFR Email</t>
+  </si>
+  <si>
+    <t>Miami Lakes</t>
+  </si>
+  <si>
+    <t>City of Miami Lakes - Building Department</t>
+  </si>
+  <si>
+    <t>Gina M. Inguanzo, Town Clerk/Records Custodian</t>
+  </si>
+  <si>
+    <t>inguanzog@miamilakes-fl.gov</t>
+  </si>
+  <si>
+    <t>https://miamilakes.mycusthelp.com/WEBAPP/_rs/(S(no0ibw4xhm1n01pqrtygxfwr))/supporthome.aspx</t>
+  </si>
+  <si>
+    <t>Portal (Select Building Permits)</t>
+  </si>
+  <si>
+    <t>City of Miami Lakes - Planning Department</t>
+  </si>
+  <si>
+    <t>Portal (Select Planning &amp; Zoning)</t>
+  </si>
+  <si>
+    <t>Miami Beach</t>
+  </si>
+  <si>
+    <t>City of Miami Beach Building Department</t>
+  </si>
+  <si>
+    <t>researchrequest@miamibeachfl.gov</t>
+  </si>
+  <si>
+    <t>https://energovcss.miamibeachfl.gov/energovprod/selfservice?_gl=1*r0vqki*_ga*MTM4MDY1ODM4LjE3Njg4NTA5MTU.*_ga_KJVW20J3BM*czE3Njg4NTA5MTQkbzEkZzEkdDE3Njg4NTA5NDEkajMzJGwwJGgw#/search</t>
+  </si>
+  <si>
+    <t>Self Lookup for Permits</t>
+  </si>
+  <si>
+    <t>City of Miami Beach Planning Department</t>
+  </si>
+  <si>
+    <t>https://miamibeachfl.justfoia.com/publicportal/home/newrequest</t>
+  </si>
+  <si>
+    <t>Use Miami Beach JUSTFOIA Portal + All-in-one Email</t>
+  </si>
+  <si>
+    <t>City of Miami Beach Fire Rescue</t>
+  </si>
+  <si>
+    <t>Portal (Not MDFR)</t>
+  </si>
+  <si>
+    <t>Use Miami Beach JUSTFOIA Portal (No Special MDFR EMAIL)</t>
+  </si>
+  <si>
+    <t>Doral</t>
+  </si>
+  <si>
+    <t>City of Doral Building Department</t>
+  </si>
+  <si>
+    <t>BuildingRecordsClerk@cityofdoral.com</t>
+  </si>
+  <si>
+    <t>https://doralfl-energovweb.tylerhost.net/apps/SelfService#/home</t>
+  </si>
+  <si>
+    <t>Email or Search Yourself</t>
+  </si>
+  <si>
+    <t>Use OpenForms Request Portal for Doral + Special MDFR Email Template</t>
+  </si>
+  <si>
+    <t>City of Doral Planning Department</t>
+  </si>
+  <si>
+    <t>https://us.openforms.com/Form/ef5b0b78-c7b6-4c25-9cb3-0c2a114fa72c</t>
+  </si>
+  <si>
+    <t>Miami</t>
+  </si>
+  <si>
+    <t>City of Miami Building Department</t>
+  </si>
+  <si>
+    <t>PublicRecords@miamigov.com</t>
+  </si>
+  <si>
+    <t>https://apps.miamigov.com/iBuildPortal/BuildingInspection/InspectionsHistory/Search/</t>
+  </si>
+  <si>
+    <t>Search for permits using FOLIO or Address</t>
+  </si>
+  <si>
+    <t>City of Miami Planning Department</t>
+  </si>
+  <si>
+    <t>https://www.miami.gov/My-Government/Government-Services/Request-Public-Records</t>
+  </si>
+  <si>
+    <t>Send email to email</t>
+  </si>
+  <si>
+    <t>City of Miami Fire Department</t>
+  </si>
+  <si>
+    <t>fire@miamigov.com</t>
+  </si>
+  <si>
+    <t>Cutler Bay</t>
+  </si>
+  <si>
+    <t>City of Cutler Bay Building Department</t>
+  </si>
+  <si>
+    <t>MMelinu@cutlerbay-fl.gov</t>
+  </si>
+  <si>
+    <t>https://www.cutlerbay-fl.gov/townclerk/webform/public-records-request</t>
+  </si>
+  <si>
+    <t>Email or Portal</t>
+  </si>
+  <si>
+    <t>City of Cutler Bay Planning Department</t>
+  </si>
+  <si>
+    <t>Opa-Locka</t>
+  </si>
+  <si>
+    <t>City of Opa Locka Building Department</t>
+  </si>
+  <si>
+    <t>jflores@opalockafl.gov</t>
+  </si>
+  <si>
+    <t>https://opalockafl.justfoia.com/Forms/Launch/d705cbd6-1396-49b7-939e-8d86c5a87deb</t>
+  </si>
+  <si>
+    <t>City of Opa Locka Planning Department</t>
+  </si>
+  <si>
+    <t>Hialeah</t>
+  </si>
+  <si>
+    <t>City of Hialeah Building Department</t>
+  </si>
+  <si>
+    <t>https://cityofhialeahfl.nextrequest.com/requests/new</t>
+  </si>
+  <si>
+    <t>Next Request Portal</t>
+  </si>
+  <si>
+    <t>City of Hialeah Planning Department</t>
+  </si>
+  <si>
+    <t>City of Hialeah Fire Department</t>
+  </si>
+  <si>
+    <t>Broward</t>
+  </si>
+  <si>
+    <t>Pompano Beach</t>
+  </si>
+  <si>
+    <t>Pompano Beach Building Department</t>
+  </si>
+  <si>
+    <t>https://pompanobeachfl.justfoia.com/publicportal/home/newrequest</t>
+  </si>
+  <si>
+    <t>Portal (New Request)</t>
+  </si>
+  <si>
+    <t>Use Pompano Beach JUSTFOIA Portal + All-in-one email</t>
+  </si>
+  <si>
+    <t>Pompano Beach Planning Department</t>
+  </si>
+  <si>
+    <t>Broward County ENVIROS</t>
+  </si>
+  <si>
+    <t>https://dpep.broward.org/Enviros/default.aspx</t>
+  </si>
+  <si>
+    <t>Use ENVIROS to lookup</t>
+  </si>
+  <si>
+    <t>Facility -&gt; Address Lookup -&gt; Print to PDF</t>
+  </si>
+  <si>
+    <t>Pompano Beach Fire Department</t>
+  </si>
+  <si>
+    <t>Coral Springs</t>
+  </si>
+  <si>
+    <t>Coral Springs Building Department</t>
+  </si>
+  <si>
+    <t>https://coralspringsfl.justfoia.com/publicportal/home/newrequest</t>
+  </si>
+  <si>
+    <t>Coral Springs Planning Department</t>
+  </si>
+  <si>
+    <t>Coral Springs Fire Department</t>
+  </si>
+  <si>
+    <t>Fort Lauderdale</t>
+  </si>
+  <si>
+    <t>City of Ft. Lauderdale Building Department</t>
+  </si>
+  <si>
+    <t>https://fortlauderdalefl.justfoia.com/Forms/Launch/d705cbd6-1396-49b7-939e-8d86c5a87deb</t>
+  </si>
+  <si>
+    <t>City of Ft. Lauderdale Planning Department</t>
+  </si>
+  <si>
+    <t>City of Ft. Lauderdale Fire Department</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broward </t>
+  </si>
+  <si>
+    <t>Margate</t>
+  </si>
+  <si>
+    <t>City of Margate Building Department</t>
+  </si>
+  <si>
+    <t>https://margatefl.justfoia.com/publicportal/home/newrequest</t>
+  </si>
+  <si>
+    <t>Use portal</t>
+  </si>
+  <si>
+    <t>City of Margate Planning Department</t>
+  </si>
+  <si>
+    <t>City of Margate Fire Department</t>
+  </si>
+  <si>
+    <t>Davie</t>
+  </si>
+  <si>
+    <t>Town of Davie Building Department</t>
+  </si>
+  <si>
+    <t>https://davie.mycusthelp.com/webapp/_rs/(S(asb4pnav23ewevaielfelbjx))/supporthome.aspx</t>
+  </si>
+  <si>
+    <t>Town of Davie Planning Department</t>
+  </si>
+  <si>
+    <t>Town of Davie Fire Department</t>
+  </si>
+  <si>
+    <t>Hollywood</t>
+  </si>
+  <si>
+    <t>City of Hollywood Building Department</t>
+  </si>
+  <si>
+    <t>https://hollywoodfl.mycusthelp.com/WEBAPP/_rs/(S(xr41gwiwjorobutcmhaq3ufs))/supporthome.aspx</t>
+  </si>
+  <si>
+    <t>City of Hollywood Planning Department</t>
+  </si>
+  <si>
+    <t>City of Hollywood Fire Department</t>
+  </si>
+  <si>
+    <t>Parkland</t>
+  </si>
+  <si>
+    <t>City of Parkland Building Department</t>
+  </si>
+  <si>
+    <t>amorales@cityofparkland.org</t>
+  </si>
+  <si>
+    <t>Email City Clerk</t>
+  </si>
+  <si>
+    <t>City of Parkland Planning Department</t>
+  </si>
+  <si>
+    <t>City of Coral Springs-Parkland Fire Department</t>
+  </si>
+  <si>
+    <t>DDiaz@CoralSprings.org</t>
+  </si>
+  <si>
+    <t>Email Coral Springs-Parkland Fire Department</t>
+  </si>
+  <si>
+    <t>Miramar</t>
+  </si>
+  <si>
+    <t>City of Miramar Building Department</t>
+  </si>
+  <si>
+    <t>clerksoffice@miramarfl.gov</t>
+  </si>
+  <si>
+    <t>https://miramarfl.justfoia.com/Forms/Launch/d705cbd6-1396-49b7-939e-8d86c5a87deb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use portal </t>
+  </si>
+  <si>
+    <t>City of Miramar Planning Department</t>
+  </si>
+  <si>
+    <t>City of Miramar Environmental Department</t>
+  </si>
+  <si>
+    <t>City of Miramar Fire Department</t>
+  </si>
+  <si>
+    <t>Pembroke Pines</t>
+  </si>
+  <si>
+    <t>City of Pembroke Pines Building Department</t>
+  </si>
+  <si>
+    <t>gfernandez@ppines.com</t>
+  </si>
+  <si>
+    <t>https://crm-pembrokepinesfl.mycusthelp.com/WEBAPP/_rs/(S(xlkwufcy0yplyl4kwki35vmy))/SupportHome.aspx?sSessionID=999416543XJBLEPSSYVC[QTFHGNWNFKNRDRMHJGH</t>
+  </si>
+  <si>
+    <t>Email Clerk or Use Portal</t>
+  </si>
+  <si>
+    <t>City of Pembroke Pines Planning Department</t>
+  </si>
+  <si>
+    <t>City of Pembroke Pines Environmental Department</t>
+  </si>
+  <si>
+    <t>City of Pembroke Pines Fire Department</t>
+  </si>
+  <si>
+    <t>Plantation</t>
+  </si>
+  <si>
+    <t>City of Plantation Building Department</t>
+  </si>
+  <si>
+    <t>CityClerk@plantation.org</t>
+  </si>
+  <si>
+    <t>https://plantationfl.mycusthelp.com/webapp/_rs/(S(rypd5ubcdranmyztd0c50ajb))/SupportHome.aspx?sSessionID=999416543LTBNOGSPZOEEPCFTLIATHNQAMSSBJZF&amp;lp=2</t>
+  </si>
+  <si>
+    <t>City of Plantation Planning Department</t>
+  </si>
+  <si>
+    <t>City of Plantation Environmental Department</t>
+  </si>
+  <si>
+    <t>City of Plantation Fire Department</t>
+  </si>
+  <si>
+    <t>Collier</t>
+  </si>
+  <si>
+    <t>Marco Island</t>
+  </si>
+  <si>
+    <t>City of Marco Island Building Department</t>
+  </si>
+  <si>
+    <t>https://cityofmarcoislandpublicrecords.justfoia.com/Forms/Launch/74d9d907-5bb2-4ea5-8585-62563d66e8f9</t>
+  </si>
+  <si>
+    <t>Use portal for building, fire, &amp; planning</t>
+  </si>
+  <si>
+    <t>City of Marco Island Planning Department</t>
+  </si>
+  <si>
+    <t>City of Marco Island Environmental Department</t>
+  </si>
+  <si>
+    <t>City of Marco Island Fire Department</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>Orange County Building Department</t>
+  </si>
+  <si>
+    <t>PublicRecordRequest@ocfl.net</t>
+  </si>
+  <si>
     <t>Use email</t>
-  </si>
-  <si>
-    <t>Miami Gardens</t>
-  </si>
-  <si>
-    <t>City of Miami Gardens — Building Services</t>
-  </si>
-  <si>
-    <t>Mario Bataille, CMC, City Clerk</t>
-  </si>
-  <si>
-    <t>recordsrequest@miamigardens-fl.gov</t>
-  </si>
-  <si>
-    <t>https://trakit.miamilakes-fl.gov/etrakit/Search/permit.aspx</t>
-  </si>
-  <si>
-    <t>Use portal to search for building permits</t>
-  </si>
-  <si>
-    <t>Search by FOLIO/APN (no dashes)</t>
-  </si>
-  <si>
-    <t>City of Miami Gardens — Planning &amp; Zoning</t>
-  </si>
-  <si>
-    <t>https://miamigardensfl.justfoia.com/publicportal</t>
-  </si>
-  <si>
-    <t>Clerk Portal + Email (All-in-one)</t>
-  </si>
-  <si>
-    <t>Public records portal; City Clerk is custodian</t>
-  </si>
-  <si>
-    <t>Miami-Dade Fire Rescue — Public Records</t>
-  </si>
-  <si>
-    <t>Christie Toledo-Fernandez</t>
-  </si>
-  <si>
-    <t>Christie.Toledo-Fernandez@miamidade.gov</t>
-  </si>
-  <si>
-    <t>Direct E-MAIL: Special MDFR Email</t>
-  </si>
-  <si>
-    <t>Miami Lakes</t>
-  </si>
-  <si>
-    <t>City of Miami Lakes - Building Department</t>
-  </si>
-  <si>
-    <t>Gina M. Inguanzo, Town Clerk/Records Custodian</t>
-  </si>
-  <si>
-    <t>inguanzog@miamilakes-fl.gov</t>
-  </si>
-  <si>
-    <t>https://miamilakes.mycusthelp.com/WEBAPP/_rs/(S(no0ibw4xhm1n01pqrtygxfwr))/supporthome.aspx</t>
-  </si>
-  <si>
-    <t>Portal (Select Building Permits)</t>
-  </si>
-  <si>
-    <t>City of Miami Lakes - Planning Department</t>
-  </si>
-  <si>
-    <t>Portal (Select Planning &amp; Zoning)</t>
-  </si>
-  <si>
-    <t>Miami Beach</t>
-  </si>
-  <si>
-    <t>City of Miami Beach Building Department</t>
-  </si>
-  <si>
-    <t>researchrequest@miamibeachfl.gov</t>
-  </si>
-  <si>
-    <t>https://miamibeachfl.justfoia.com/publicportal/home/newrequest</t>
-  </si>
-  <si>
-    <t>Use Miami Beach JUSTFOIA Portal + All-in-one Email</t>
-  </si>
-  <si>
-    <t>City of Miami Beach Planning Department</t>
-  </si>
-  <si>
-    <t>City of Miami Beach Fire Rescue</t>
-  </si>
-  <si>
-    <t>Portal (Not MDFR)</t>
-  </si>
-  <si>
-    <t>Use Miami Beach JUSTFOIA Portal (No Special MDFR EMAIL)</t>
-  </si>
-  <si>
-    <t>Doral</t>
-  </si>
-  <si>
-    <t>City of Doral Building Department</t>
-  </si>
-  <si>
-    <t>BuildingRecordsClerk@cityofdoral.com</t>
-  </si>
-  <si>
-    <t>https://doralfl-energovweb.tylerhost.net/apps/SelfService#/home</t>
-  </si>
-  <si>
-    <t>Email or Search Yourself</t>
-  </si>
-  <si>
-    <t>Use OpenForms Request Portal for Doral + Special MDFR Email Template</t>
-  </si>
-  <si>
-    <t>City of Doral Planning Department</t>
-  </si>
-  <si>
-    <t>https://us.openforms.com/Form/ef5b0b78-c7b6-4c25-9cb3-0c2a114fa72c</t>
-  </si>
-  <si>
-    <t>Miami</t>
-  </si>
-  <si>
-    <t>City of Miami Building Department</t>
-  </si>
-  <si>
-    <t>PublicRecords@miamigov.com</t>
-  </si>
-  <si>
-    <t>https://apps.miamigov.com/iBuildPortal/BuildingInspection/InspectionsHistory/Search/</t>
-  </si>
-  <si>
-    <t>Search for permits using FOLIO or Address</t>
-  </si>
-  <si>
-    <t>City of Miami Planning Department</t>
-  </si>
-  <si>
-    <t>https://www.miami.gov/My-Government/Government-Services/Request-Public-Records</t>
-  </si>
-  <si>
-    <t>Send email to email</t>
-  </si>
-  <si>
-    <t>City of Miami Fire Department</t>
-  </si>
-  <si>
-    <t>fire@miamigov.com</t>
-  </si>
-  <si>
-    <t>Cutler Bay</t>
-  </si>
-  <si>
-    <t>City of Cutler Bay Building Department</t>
-  </si>
-  <si>
-    <t>MMelinu@cutlerbay-fl.gov</t>
-  </si>
-  <si>
-    <t>https://www.cutlerbay-fl.gov/townclerk/webform/public-records-request</t>
-  </si>
-  <si>
-    <t>Email or Portal</t>
-  </si>
-  <si>
-    <t>City of Cutler Bay Planning Department</t>
-  </si>
-  <si>
-    <t>Opa-Locka</t>
-  </si>
-  <si>
-    <t>City of Opa Locka Building Department</t>
-  </si>
-  <si>
-    <t>jflores@opalockafl.gov</t>
-  </si>
-  <si>
-    <t>https://opalockafl.justfoia.com/Forms/Launch/d705cbd6-1396-49b7-939e-8d86c5a87deb</t>
-  </si>
-  <si>
-    <t>City of Opa Locka Planning Department</t>
-  </si>
-  <si>
-    <t>Hialeah</t>
-  </si>
-  <si>
-    <t>City of Hialeah Building Department</t>
-  </si>
-  <si>
-    <t>https://cityofhialeahfl.nextrequest.com/requests/new</t>
-  </si>
-  <si>
-    <t>Next Request Portal</t>
-  </si>
-  <si>
-    <t>City of Hialeah Planning Department</t>
-  </si>
-  <si>
-    <t>City of Hialeah Fire Department</t>
-  </si>
-  <si>
-    <t>Broward</t>
-  </si>
-  <si>
-    <t>Pompano Beach</t>
-  </si>
-  <si>
-    <t>Pompano Beach Building Department</t>
-  </si>
-  <si>
-    <t>https://pompanobeachfl.justfoia.com/publicportal/home/newrequest</t>
-  </si>
-  <si>
-    <t>Portal (New Request)</t>
-  </si>
-  <si>
-    <t>Use Pompano Beach JUSTFOIA Portal + All-in-one email</t>
-  </si>
-  <si>
-    <t>Pompano Beach Planning Department</t>
-  </si>
-  <si>
-    <t>Broward County ENVIROS</t>
-  </si>
-  <si>
-    <t>https://dpep.broward.org/Enviros/default.aspx</t>
-  </si>
-  <si>
-    <t>Use ENVIROS to lookup</t>
-  </si>
-  <si>
-    <t>Facility -&gt; Address Lookup -&gt; Print to PDF</t>
-  </si>
-  <si>
-    <t>Pompano Beach Fire Department</t>
-  </si>
-  <si>
-    <t>Coral Springs</t>
-  </si>
-  <si>
-    <t>Coral Springs Building Department</t>
-  </si>
-  <si>
-    <t>https://coralspringsfl.justfoia.com/publicportal/home/newrequest</t>
-  </si>
-  <si>
-    <t>Use Portal</t>
-  </si>
-  <si>
-    <t>Coral Springs Planning Department</t>
-  </si>
-  <si>
-    <t>Coral Springs Fire Department</t>
-  </si>
-  <si>
-    <t>Fort Lauderdale</t>
-  </si>
-  <si>
-    <t>City of Ft. Lauderdale Building Department</t>
-  </si>
-  <si>
-    <t>https://fortlauderdalefl.justfoia.com/Forms/Launch/d705cbd6-1396-49b7-939e-8d86c5a87deb</t>
-  </si>
-  <si>
-    <t>City of Ft. Lauderdale Planning Department</t>
-  </si>
-  <si>
-    <t>City of Ft. Lauderdale Fire Department</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Broward </t>
-  </si>
-  <si>
-    <t>Margate</t>
-  </si>
-  <si>
-    <t>City of Margate Building Department</t>
-  </si>
-  <si>
-    <t>https://margatefl.justfoia.com/publicportal/home/newrequest</t>
-  </si>
-  <si>
-    <t>Use portal</t>
-  </si>
-  <si>
-    <t>City of Margate Planning Department</t>
-  </si>
-  <si>
-    <t>City of Margate Fire Department</t>
-  </si>
-  <si>
-    <t>Davie</t>
-  </si>
-  <si>
-    <t>Town of Davie Building Department</t>
-  </si>
-  <si>
-    <t>https://davie.mycusthelp.com/webapp/_rs/(S(asb4pnav23ewevaielfelbjx))/supporthome.aspx</t>
-  </si>
-  <si>
-    <t>Town of Davie Planning Department</t>
-  </si>
-  <si>
-    <t>Town of Davie Fire Department</t>
-  </si>
-  <si>
-    <t>Hollywood</t>
-  </si>
-  <si>
-    <t>City of Hollywood Building Department</t>
-  </si>
-  <si>
-    <t>https://hollywoodfl.mycusthelp.com/WEBAPP/_rs/(S(xr41gwiwjorobutcmhaq3ufs))/supporthome.aspx</t>
-  </si>
-  <si>
-    <t>City of Hollywood Planning Department</t>
-  </si>
-  <si>
-    <t>City of Hollywood Fire Department</t>
-  </si>
-  <si>
-    <t>Parkland</t>
-  </si>
-  <si>
-    <t>City of Parkland Building Department</t>
-  </si>
-  <si>
-    <t>amorales@cityofparkland.org</t>
-  </si>
-  <si>
-    <t>Email City Clerk</t>
-  </si>
-  <si>
-    <t>City of Parkland Planning Department</t>
-  </si>
-  <si>
-    <t>City of Coral Springs-Parkland Fire Department</t>
-  </si>
-  <si>
-    <t>DDiaz@CoralSprings.org</t>
-  </si>
-  <si>
-    <t>Email Coral Springs-Parkland Fire Department</t>
-  </si>
-  <si>
-    <t>Miramar</t>
-  </si>
-  <si>
-    <t>City of Miramar Building Department</t>
-  </si>
-  <si>
-    <t>clerksoffice@miramarfl.gov</t>
-  </si>
-  <si>
-    <t>https://miramarfl.justfoia.com/Forms/Launch/d705cbd6-1396-49b7-939e-8d86c5a87deb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use portal </t>
-  </si>
-  <si>
-    <t>City of Miramar Planning Department</t>
-  </si>
-  <si>
-    <t>City of Miramar Environmental Department</t>
-  </si>
-  <si>
-    <t>City of Miramar Fire Department</t>
-  </si>
-  <si>
-    <t>Pembroke Pines</t>
-  </si>
-  <si>
-    <t>City of Pembroke Pines Building Department</t>
-  </si>
-  <si>
-    <t>gfernandez@ppines.com</t>
-  </si>
-  <si>
-    <t>https://crm-pembrokepinesfl.mycusthelp.com/WEBAPP/_rs/(S(xlkwufcy0yplyl4kwki35vmy))/SupportHome.aspx?sSessionID=999416543XJBLEPSSYVC[QTFHGNWNFKNRDRMHJGH</t>
-  </si>
-  <si>
-    <t>Email Clerk or Use Portal</t>
-  </si>
-  <si>
-    <t>City of Pembroke Pines Planning Department</t>
-  </si>
-  <si>
-    <t>City of Pembroke Pines Environmental Department</t>
-  </si>
-  <si>
-    <t>City of Pembroke Pines Fire Department</t>
-  </si>
-  <si>
-    <t>Plantation</t>
-  </si>
-  <si>
-    <t>City of Plantation Building Department</t>
-  </si>
-  <si>
-    <t>CityClerk@plantation.org</t>
-  </si>
-  <si>
-    <t>https://plantationfl.mycusthelp.com/webapp/_rs/(S(rypd5ubcdranmyztd0c50ajb))/SupportHome.aspx?sSessionID=999416543LTBNOGSPZOEEPCFTLIATHNQAMSSBJZF&amp;lp=2</t>
-  </si>
-  <si>
-    <t>City of Plantation Planning Department</t>
-  </si>
-  <si>
-    <t>City of Plantation Environmental Department</t>
-  </si>
-  <si>
-    <t>City of Plantation Fire Department</t>
-  </si>
-  <si>
-    <t>Collier</t>
-  </si>
-  <si>
-    <t>Marco Island</t>
-  </si>
-  <si>
-    <t>City of Marco Island Building Department</t>
-  </si>
-  <si>
-    <t>https://cityofmarcoislandpublicrecords.justfoia.com/Forms/Launch/74d9d907-5bb2-4ea5-8585-62563d66e8f9</t>
-  </si>
-  <si>
-    <t>Use portal for building, fire, &amp; planning</t>
-  </si>
-  <si>
-    <t>City of Marco Island Planning Department</t>
-  </si>
-  <si>
-    <t>City of Marco Island Environmental Department</t>
-  </si>
-  <si>
-    <t>City of Marco Island Fire Department</t>
-  </si>
-  <si>
-    <t>Orange</t>
-  </si>
-  <si>
-    <t>Orange County Building Department</t>
-  </si>
-  <si>
-    <t>PublicRecordRequest@ocfl.net</t>
   </si>
   <si>
     <t>Email + FastTrack lookup if login works</t>
@@ -1823,880 +1877,808 @@
       <c r="K17" s="9"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="2"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="H18" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="I18" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="J18" s="2"/>
+      <c r="K18" s="9"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="E19" s="2"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J19" s="2"/>
+      <c r="K19" s="9"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="J18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
+      <c r="E20" s="2"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J20" s="2"/>
+      <c r="K20" s="9"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="C21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>81</v>
-      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J21" s="2"/>
+      <c r="K21" s="9"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E22" s="2"/>
-      <c r="F22" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>85</v>
+      <c r="F22" s="3"/>
+      <c r="G22" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>87</v>
+        <v>36</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="9"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="G23" s="12"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="7" t="s">
+        <v>74</v>
+      </c>
       <c r="H23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>89</v>
+        <v>36</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="9"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="G24" s="12"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="7" t="s">
+        <v>74</v>
+      </c>
       <c r="H24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>89</v>
+        <v>36</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="9"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="E25" s="2"/>
-      <c r="F25" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="G25" s="12"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="7" t="s">
+        <v>74</v>
+      </c>
       <c r="H25" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>89</v>
+        <v>36</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="9"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>93</v>
+      <c r="D26" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>15</v>
+        <v>81</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K26" s="9" t="s">
-        <v>96</v>
+      <c r="K26" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>97</v>
+      <c r="D27" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>15</v>
+        <v>87</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>95</v>
+      <c r="I27" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K27" s="9" t="s">
-        <v>98</v>
+      <c r="K27" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B28" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>94</v>
+      <c r="G28" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>101</v>
+      <c r="D29" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I29" s="3" t="s">
+      <c r="H29" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>95</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>108</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="J30" s="2"/>
+      <c r="K30" s="9"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>107</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G31" s="12"/>
       <c r="H31" s="3" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K31" s="9" t="s">
-        <v>110</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="J31" s="2"/>
+      <c r="K31" s="9"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>107</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G32" s="12"/>
       <c r="H32" s="3" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K32" s="9" t="s">
-        <v>38</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="J32" s="2"/>
+      <c r="K32" s="9"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E33" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="E33" s="2"/>
+      <c r="F33" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G33" s="12"/>
+      <c r="H33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J33" s="2"/>
+      <c r="K33" s="9"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="G34" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D35" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G35" s="5" t="s">
+      <c r="H35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>106</v>
+        <v>114</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="G36" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>106</v>
+        <v>116</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J37" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J37" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K37" s="9" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>117</v>
+      <c r="D38" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I38" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="J38" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J38" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>81</v>
+      <c r="K38" s="9" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="G39" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="F39" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>124</v>
-      </c>
       <c r="H39" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I39" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K39" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G40" s="5"/>
+        <v>121</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>122</v>
+      </c>
       <c r="H40" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="J40" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J40" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K40" s="2" t="s">
-        <v>81</v>
+      <c r="K40" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>132</v>
+        <v>118</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>127</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="J41" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J41" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K41" s="2" t="s">
-        <v>81</v>
+      <c r="K41" s="9" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C42" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K42" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="G42" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J42" s="2" t="s">
+      <c r="D43" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J43" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K42" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B43" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="F43" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="I43" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="J43" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K43" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="16"/>
-      <c r="O43" s="16"/>
-      <c r="P43" s="16"/>
-      <c r="Q43" s="16"/>
-      <c r="R43" s="16"/>
-      <c r="S43" s="16"/>
-      <c r="T43" s="16"/>
-      <c r="U43" s="16"/>
-      <c r="V43" s="16"/>
-      <c r="W43" s="16"/>
-      <c r="X43" s="16"/>
-      <c r="Y43" s="16"/>
-      <c r="Z43" s="16"/>
+      <c r="K43" s="9" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J44" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J44" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K44" s="9" t="s">
@@ -2705,1248 +2687,1333 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>21</v>
+        <v>53</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>150</v>
+        <v>121</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="J45" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J45" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>38</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C46" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3" t="s">
-        <v>156</v>
+      <c r="D46" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="J46" s="2"/>
-      <c r="K46" s="9"/>
+        <v>134</v>
+      </c>
+      <c r="I46" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C47" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="E47" s="3"/>
+      <c r="D47" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>137</v>
+      </c>
       <c r="F47" s="3" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="J47" s="2"/>
-      <c r="K47" s="9"/>
+        <v>140</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E48" s="3"/>
+        <v>142</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="F48" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="J48" s="2"/>
-      <c r="K48" s="9"/>
+        <v>146</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C49" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E49" s="3"/>
+      <c r="D49" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="F49" s="3" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="J49" s="2"/>
-      <c r="K49" s="9"/>
+        <v>153</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C50" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="5" t="s">
-        <v>170</v>
+      <c r="D50" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G50" s="14" t="s">
+        <v>155</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="J50" s="2"/>
-      <c r="K50" s="9"/>
+        <v>156</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="J51" s="2"/>
-      <c r="K51" s="9"/>
+      <c r="A51" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="E51" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="G51" s="15"/>
+      <c r="H51" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="I51" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="J51" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L51" s="16"/>
+      <c r="M51" s="16"/>
+      <c r="N51" s="16"/>
+      <c r="O51" s="16"/>
+      <c r="P51" s="16"/>
+      <c r="Q51" s="16"/>
+      <c r="R51" s="16"/>
+      <c r="S51" s="16"/>
+      <c r="T51" s="16"/>
+      <c r="U51" s="16"/>
+      <c r="V51" s="16"/>
+      <c r="W51" s="16"/>
+      <c r="X51" s="16"/>
+      <c r="Y51" s="16"/>
+      <c r="Z51" s="16"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>21</v>
+        <v>162</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E52" s="3"/>
+        <v>163</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>164</v>
+      </c>
       <c r="F52" s="3" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="J52" s="2"/>
-      <c r="K52" s="9"/>
+        <v>167</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K52" s="9" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>28</v>
+        <v>162</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E53" s="3"/>
+        <v>168</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>164</v>
+      </c>
       <c r="F53" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>177</v>
+        <v>165</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>166</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="J53" s="2"/>
-      <c r="K53" s="9"/>
+        <v>169</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K53" s="9" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>185</v>
+        <v>18</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="9"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>185</v>
+        <v>36</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="9"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>36</v>
+        <v>179</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="9"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>36</v>
+        <v>185</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>36</v>
+        <v>186</v>
       </c>
       <c r="J57" s="2"/>
       <c r="K57" s="9"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="5" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="J58" s="2"/>
       <c r="K58" s="9"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B59" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G59" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="5" t="s">
-        <v>194</v>
-      </c>
       <c r="H59" s="3" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="9"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
+      <c r="F60" s="3" t="s">
+        <v>191</v>
+      </c>
       <c r="G60" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="9"/>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="G61" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="J61" s="2"/>
+      <c r="K61" s="9"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C62" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="D62" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="G61" s="7" t="s">
+      <c r="E62" s="3"/>
+      <c r="F62" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="H61" s="6" t="s">
+      <c r="G62" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="I61" s="6" t="s">
+      <c r="H62" s="3" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B62" s="6" t="s">
+      <c r="I62" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="J62" s="2"/>
+      <c r="K62" s="9"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C63" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D62" s="6" t="s">
+      <c r="D63" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G62" s="7" t="s">
+      <c r="E63" s="3"/>
+      <c r="F63" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="H62" s="6" t="s">
+      <c r="G63" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="I62" s="6" t="s">
+      <c r="H63" s="3" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D63" s="6" t="s">
+      <c r="I63" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="J63" s="2"/>
+      <c r="K63" s="9"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F63" s="6"/>
-      <c r="G63" s="7" t="s">
+      <c r="C64" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="H63" s="6" t="s">
+      <c r="E64" s="3"/>
+      <c r="F64" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="I63" s="6" t="s">
+      <c r="G64" s="5" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="C64" s="6" t="s">
+      <c r="H64" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J64" s="2"/>
+      <c r="K64" s="9"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J65" s="2"/>
+      <c r="K65" s="9"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="J66" s="2"/>
+      <c r="K66" s="9"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="J67" s="2"/>
+      <c r="K67" s="9"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D64" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="I64" s="6" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="G65" s="7" t="s">
+      <c r="D68" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="H65" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I65" s="6" t="s">
+      <c r="H68" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I68" s="3" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="G66" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I66" s="6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="F67" s="6"/>
-      <c r="G67" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="H67" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="I67" s="6" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="G68" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I68" s="6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
+      <c r="J68" s="2"/>
+      <c r="K68" s="9"/>
+    </row>
+    <row r="69">
       <c r="A69" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D69" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B70" s="6" t="s">
         <v>217</v>
-      </c>
-      <c r="G69" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="H69" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I69" s="6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>216</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D70" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="G70" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="G70" s="7" t="s">
-        <v>218</v>
-      </c>
       <c r="H70" s="6" t="s">
-        <v>36</v>
+        <v>220</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="F71" s="6"/>
       <c r="G71" s="7" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="72">
       <c r="A72" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D72" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="G72" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>36</v>
-      </c>
       <c r="I72" s="6" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="6" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>225</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="6" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>225</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="F75" s="6"/>
       <c r="G75" s="7" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="6" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>225</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>225</v>
+        <v>75</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>225</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="F79" s="6"/>
       <c r="G79" s="7" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>225</v>
+        <v>75</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="6" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>213</v>
+        <v>242</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="6" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>213</v>
+        <v>242</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="F83" s="6"/>
       <c r="G83" s="7" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="6" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>213</v>
+        <v>242</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="F85" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="G85" s="10"/>
+        <v>246</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>247</v>
+      </c>
       <c r="H85" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D86" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I86" s="6" t="s">
         <v>242</v>
-      </c>
-      <c r="F86" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="G86" s="10"/>
-      <c r="H86" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I86" s="6" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="F87" s="6"/>
       <c r="G87" s="7" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="F88" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="G88" s="10"/>
+        <v>249</v>
+      </c>
+      <c r="G88" s="7" t="s">
+        <v>247</v>
+      </c>
       <c r="H88" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="H89" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>250</v>
+        <v>75</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="H90" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>250</v>
+        <v>75</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>248</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="F91" s="6"/>
       <c r="G91" s="7" t="s">
-        <v>249</v>
+        <v>224</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>36</v>
+        <v>225</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>250</v>
+        <v>75</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>15</v>
+        <v>256</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="G93" s="7" t="s">
         <v>257</v>
       </c>
+      <c r="G93" s="10"/>
       <c r="H93" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I93" s="6" t="s">
         <v>258</v>
@@ -3954,10 +4021,10 @@
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>21</v>
@@ -3965,17 +4032,12 @@
       <c r="D94" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="E94" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="F94" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="G94" s="7" t="s">
         <v>257</v>
       </c>
+      <c r="G94" s="10"/>
       <c r="H94" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I94" s="6" t="s">
         <v>258</v>
@@ -3983,486 +4045,688 @@
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F95" s="6" t="s">
-        <v>256</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="F95" s="6"/>
       <c r="G95" s="7" t="s">
-        <v>257</v>
+        <v>224</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>36</v>
+        <v>225</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>258</v>
+        <v>226</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D96" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="F96" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="E96" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="G96" s="7" t="s">
-        <v>257</v>
-      </c>
+      <c r="G96" s="10"/>
       <c r="H96" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>15</v>
+        <v>264</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H97" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D98" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="G98" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="E98" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F98" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>265</v>
-      </c>
       <c r="H98" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D99" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I99" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="G99" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I99" s="6" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="E100" s="6" t="s">
-        <v>15</v>
+        <v>270</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H100" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="6" t="s">
-        <v>269</v>
+        <v>216</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>273</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H101" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="J101" s="6" t="s">
-        <v>19</v>
+        <v>275</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="6" t="s">
-        <v>269</v>
+        <v>216</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D102" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="G102" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="G102" s="7" t="s">
-        <v>272</v>
-      </c>
       <c r="H102" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="J102" s="6" t="s">
-        <v>19</v>
+        <v>275</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="6" t="s">
-        <v>269</v>
+        <v>216</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D103" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="G103" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I103" s="6" t="s">
         <v>275</v>
-      </c>
-      <c r="G103" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I103" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="J103" s="6" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="6" t="s">
-        <v>269</v>
+        <v>216</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>273</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H104" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="J104" s="6" t="s">
-        <v>19</v>
+        <v>275</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="6" t="s">
-        <v>277</v>
+        <v>216</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>53</v>
+        <v>279</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>282</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="6" t="s">
-        <v>277</v>
+        <v>216</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>53</v>
+        <v>279</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D106" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="E106" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F106" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="F106" s="6" t="s">
-        <v>279</v>
+      <c r="G106" s="7" t="s">
+        <v>282</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>5</v>
+        <v>275</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="6" t="s">
-        <v>277</v>
+        <v>216</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>53</v>
+        <v>279</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D107" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G107" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="F107" s="6" t="s">
-        <v>283</v>
-      </c>
       <c r="H107" s="6" t="s">
-        <v>284</v>
+        <v>36</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="6" t="s">
-        <v>277</v>
+        <v>216</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>53</v>
+        <v>279</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
+      </c>
+      <c r="G108" s="7" t="s">
+        <v>282</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>89</v>
+        <v>275</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B109" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>288</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D109" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="G109" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="E109" s="6" t="s">
+      <c r="H109" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I109" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="F109" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="H109" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="I109" s="6" t="s">
-        <v>292</v>
+      <c r="J109" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B110" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>288</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="E110" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G110" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I110" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="F110" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="I110" s="6" t="s">
-        <v>292</v>
+      <c r="J110" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B111" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>288</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="E111" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="G111" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="H111" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I111" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="F111" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="H111" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="I111" s="6" t="s">
-        <v>292</v>
+      <c r="J111" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B112" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>288</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D112" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="G112" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I112" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="J112" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="A113" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D113" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="E112" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="F112" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="I112" s="6" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
+      <c r="F113" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="H113" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="I113" s="6" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="A114" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="H114" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="I114" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="A115" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="H115" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="I115" s="6" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="A116" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="H116" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="I116" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="A117" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="H117" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="I117" s="6" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="A118" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="I118" s="6" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="A119" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="H119" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="I119" s="6" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="120" ht="15.75" customHeight="1">
+      <c r="A120" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="I120" s="6" t="s">
+        <v>310</v>
+      </c>
+    </row>
     <row r="121" ht="15.75" customHeight="1"/>
     <row r="122" ht="15.75" customHeight="1"/>
     <row r="123" ht="15.75" customHeight="1"/>
@@ -5419,6 +5683,14 @@
     <row r="1074" ht="15.75" customHeight="1"/>
     <row r="1075" ht="15.75" customHeight="1"/>
     <row r="1076" ht="15.75" customHeight="1"/>
+    <row r="1077" ht="15.75" customHeight="1"/>
+    <row r="1078" ht="15.75" customHeight="1"/>
+    <row r="1079" ht="15.75" customHeight="1"/>
+    <row r="1080" ht="15.75" customHeight="1"/>
+    <row r="1081" ht="15.75" customHeight="1"/>
+    <row r="1082" ht="15.75" customHeight="1"/>
+    <row r="1083" ht="15.75" customHeight="1"/>
+    <row r="1084" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" location="/home" ref="G2"/>
@@ -5439,86 +5711,95 @@
     <hyperlink r:id="rId16" ref="G19"/>
     <hyperlink r:id="rId17" ref="G20"/>
     <hyperlink r:id="rId18" ref="G21"/>
-    <hyperlink r:id="rId19" location="/home" ref="G22"/>
-    <hyperlink r:id="rId20" ref="G26"/>
-    <hyperlink r:id="rId21" ref="G27"/>
-    <hyperlink r:id="rId22" ref="G28"/>
-    <hyperlink r:id="rId23" ref="G29"/>
-    <hyperlink r:id="rId24" ref="G30"/>
-    <hyperlink r:id="rId25" ref="G31"/>
-    <hyperlink r:id="rId26" ref="G32"/>
-    <hyperlink r:id="rId27" ref="G33"/>
+    <hyperlink r:id="rId19" ref="G22"/>
+    <hyperlink r:id="rId20" ref="G23"/>
+    <hyperlink r:id="rId21" ref="G24"/>
+    <hyperlink r:id="rId22" ref="G25"/>
+    <hyperlink r:id="rId23" ref="G26"/>
+    <hyperlink r:id="rId24" ref="G27"/>
+    <hyperlink r:id="rId25" ref="G28"/>
+    <hyperlink r:id="rId26" ref="G29"/>
+    <hyperlink r:id="rId27" location="/home" ref="G30"/>
     <hyperlink r:id="rId28" ref="G34"/>
     <hyperlink r:id="rId29" ref="G35"/>
     <hyperlink r:id="rId30" ref="G36"/>
     <hyperlink r:id="rId31" ref="G37"/>
     <hyperlink r:id="rId32" ref="G38"/>
-    <hyperlink r:id="rId33" ref="I38"/>
-    <hyperlink r:id="rId34" ref="G39"/>
+    <hyperlink r:id="rId33" ref="G39"/>
+    <hyperlink r:id="rId34" ref="G40"/>
     <hyperlink r:id="rId35" ref="G41"/>
     <hyperlink r:id="rId36" ref="G42"/>
-    <hyperlink r:id="rId37" ref="G44"/>
-    <hyperlink r:id="rId38" ref="G45"/>
-    <hyperlink r:id="rId39" ref="G46"/>
-    <hyperlink r:id="rId40" ref="G47"/>
-    <hyperlink r:id="rId41" ref="G48"/>
-    <hyperlink r:id="rId42" location="/home" ref="G49"/>
-    <hyperlink r:id="rId43" ref="G50"/>
-    <hyperlink r:id="rId44" ref="G51"/>
-    <hyperlink r:id="rId45" ref="G52"/>
-    <hyperlink r:id="rId46" ref="G53"/>
-    <hyperlink r:id="rId47" ref="G54"/>
-    <hyperlink r:id="rId48" ref="G55"/>
-    <hyperlink r:id="rId49" ref="G56"/>
-    <hyperlink r:id="rId50" ref="G57"/>
-    <hyperlink r:id="rId51" ref="G58"/>
-    <hyperlink r:id="rId52" ref="G59"/>
-    <hyperlink r:id="rId53" ref="G60"/>
-    <hyperlink r:id="rId54" ref="G61"/>
-    <hyperlink r:id="rId55" ref="G62"/>
-    <hyperlink r:id="rId56" ref="G63"/>
-    <hyperlink r:id="rId57" ref="G64"/>
-    <hyperlink r:id="rId58" ref="G65"/>
-    <hyperlink r:id="rId59" ref="G66"/>
-    <hyperlink r:id="rId60" ref="G67"/>
-    <hyperlink r:id="rId61" ref="G68"/>
-    <hyperlink r:id="rId62" ref="G69"/>
-    <hyperlink r:id="rId63" ref="G70"/>
-    <hyperlink r:id="rId64" ref="G71"/>
-    <hyperlink r:id="rId65" ref="G72"/>
-    <hyperlink r:id="rId66" ref="G73"/>
-    <hyperlink r:id="rId67" ref="G74"/>
-    <hyperlink r:id="rId68" ref="G75"/>
-    <hyperlink r:id="rId69" ref="G76"/>
-    <hyperlink r:id="rId70" ref="G77"/>
-    <hyperlink r:id="rId71" ref="G78"/>
-    <hyperlink r:id="rId72" ref="G79"/>
-    <hyperlink r:id="rId73" ref="G80"/>
-    <hyperlink r:id="rId74" ref="G81"/>
-    <hyperlink r:id="rId75" ref="G82"/>
-    <hyperlink r:id="rId76" ref="G83"/>
-    <hyperlink r:id="rId77" ref="G84"/>
-    <hyperlink r:id="rId78" ref="G87"/>
-    <hyperlink r:id="rId79" ref="G89"/>
-    <hyperlink r:id="rId80" ref="G90"/>
-    <hyperlink r:id="rId81" ref="G91"/>
-    <hyperlink r:id="rId82" ref="G92"/>
-    <hyperlink r:id="rId83" ref="G93"/>
-    <hyperlink r:id="rId84" ref="G94"/>
-    <hyperlink r:id="rId85" ref="G95"/>
-    <hyperlink r:id="rId86" ref="G96"/>
-    <hyperlink r:id="rId87" ref="G97"/>
-    <hyperlink r:id="rId88" ref="G98"/>
-    <hyperlink r:id="rId89" ref="G99"/>
-    <hyperlink r:id="rId90" ref="G100"/>
-    <hyperlink r:id="rId91" ref="G101"/>
-    <hyperlink r:id="rId92" ref="G102"/>
-    <hyperlink r:id="rId93" ref="G103"/>
-    <hyperlink r:id="rId94" ref="G104"/>
+    <hyperlink r:id="rId37" ref="G43"/>
+    <hyperlink r:id="rId38" ref="G44"/>
+    <hyperlink r:id="rId39" ref="G45"/>
+    <hyperlink r:id="rId40" ref="G46"/>
+    <hyperlink r:id="rId41" ref="I46"/>
+    <hyperlink r:id="rId42" ref="G47"/>
+    <hyperlink r:id="rId43" ref="G48"/>
+    <hyperlink r:id="rId44" ref="G49"/>
+    <hyperlink r:id="rId45" ref="G50"/>
+    <hyperlink r:id="rId46" ref="G52"/>
+    <hyperlink r:id="rId47" ref="G53"/>
+    <hyperlink r:id="rId48" ref="G54"/>
+    <hyperlink r:id="rId49" ref="G55"/>
+    <hyperlink r:id="rId50" ref="G56"/>
+    <hyperlink r:id="rId51" location="/home" ref="G57"/>
+    <hyperlink r:id="rId52" ref="G58"/>
+    <hyperlink r:id="rId53" ref="G59"/>
+    <hyperlink r:id="rId54" ref="G60"/>
+    <hyperlink r:id="rId55" ref="G61"/>
+    <hyperlink r:id="rId56" ref="G62"/>
+    <hyperlink r:id="rId57" ref="G63"/>
+    <hyperlink r:id="rId58" ref="G64"/>
+    <hyperlink r:id="rId59" ref="G65"/>
+    <hyperlink r:id="rId60" ref="G66"/>
+    <hyperlink r:id="rId61" ref="G67"/>
+    <hyperlink r:id="rId62" ref="G68"/>
+    <hyperlink r:id="rId63" ref="G69"/>
+    <hyperlink r:id="rId64" ref="G70"/>
+    <hyperlink r:id="rId65" ref="G71"/>
+    <hyperlink r:id="rId66" ref="G72"/>
+    <hyperlink r:id="rId67" ref="G73"/>
+    <hyperlink r:id="rId68" ref="G74"/>
+    <hyperlink r:id="rId69" ref="G75"/>
+    <hyperlink r:id="rId70" ref="G76"/>
+    <hyperlink r:id="rId71" ref="G77"/>
+    <hyperlink r:id="rId72" ref="G78"/>
+    <hyperlink r:id="rId73" ref="G79"/>
+    <hyperlink r:id="rId74" ref="G80"/>
+    <hyperlink r:id="rId75" ref="G81"/>
+    <hyperlink r:id="rId76" ref="G82"/>
+    <hyperlink r:id="rId77" ref="G83"/>
+    <hyperlink r:id="rId78" ref="G84"/>
+    <hyperlink r:id="rId79" ref="G85"/>
+    <hyperlink r:id="rId80" ref="G86"/>
+    <hyperlink r:id="rId81" ref="G87"/>
+    <hyperlink r:id="rId82" ref="G88"/>
+    <hyperlink r:id="rId83" ref="G89"/>
+    <hyperlink r:id="rId84" ref="G90"/>
+    <hyperlink r:id="rId85" ref="G91"/>
+    <hyperlink r:id="rId86" ref="G92"/>
+    <hyperlink r:id="rId87" ref="G95"/>
+    <hyperlink r:id="rId88" ref="G97"/>
+    <hyperlink r:id="rId89" ref="G98"/>
+    <hyperlink r:id="rId90" ref="G99"/>
+    <hyperlink r:id="rId91" ref="G100"/>
+    <hyperlink r:id="rId92" ref="G101"/>
+    <hyperlink r:id="rId93" ref="G102"/>
+    <hyperlink r:id="rId94" ref="G103"/>
+    <hyperlink r:id="rId95" ref="G104"/>
+    <hyperlink r:id="rId96" ref="G105"/>
+    <hyperlink r:id="rId97" ref="G106"/>
+    <hyperlink r:id="rId98" ref="G107"/>
+    <hyperlink r:id="rId99" ref="G108"/>
+    <hyperlink r:id="rId100" ref="G109"/>
+    <hyperlink r:id="rId101" ref="G110"/>
+    <hyperlink r:id="rId102" ref="G111"/>
+    <hyperlink r:id="rId103" ref="G112"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId95"/>
+  <drawing r:id="rId104"/>
 </worksheet>
 </file>
--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="lRGfBzzT8FExW9Yv7l7mHJMhDQd134GPNyZykox/3uY="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Oc3QG2j82QTTpMJdMTtco/OHvJOY3ciGopg0F7LwR10="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="353">
   <si>
     <t>County</t>
   </si>
@@ -225,6 +225,9 @@
   </si>
   <si>
     <t>PublicRecordsRequest@flhealth.gov</t>
+  </si>
+  <si>
+    <t>https://www.pbcgov.org/eprr/erm</t>
   </si>
   <si>
     <t>Palm Beach County Fire Department</t>
@@ -709,6 +712,39 @@
     <t>Broward</t>
   </si>
   <si>
+    <t>Broward County Building Department</t>
+  </si>
+  <si>
+    <t>https://browardcounty.govqa.us/WEBAPP/_rs/(S(my5kju2idk0iq31a4uhcxvh1))/RequestSelect.aspx?sSessionID=</t>
+  </si>
+  <si>
+    <t>Select -&gt; Permitting and Licensing</t>
+  </si>
+  <si>
+    <t>Broward County Planning Department</t>
+  </si>
+  <si>
+    <t>Select -&gt; Community Services</t>
+  </si>
+  <si>
+    <t>Broward County ENVIROS</t>
+  </si>
+  <si>
+    <t>https://dpep.broward.org/Enviros/default.aspx?PossePresentation=FacilityAddressSearch</t>
+  </si>
+  <si>
+    <t>Broward ENVIROS - Facility -&gt; Address Lookup -&gt; Print to PDF</t>
+  </si>
+  <si>
+    <t>Broward County Sherrif Office</t>
+  </si>
+  <si>
+    <t>https://nogroup-browardcountysheriff.govqa.us/WEBAPP/_rs/(S(andjsxtamtz0ccju03u21cpp))/SupportHome.aspx?lp=3&amp;sSessionID=</t>
+  </si>
+  <si>
+    <t>Select -&gt; Fire Rescue Records Request</t>
+  </si>
+  <si>
     <t>Pompano Beach</t>
   </si>
   <si>
@@ -727,9 +763,6 @@
     <t>Pompano Beach Planning Department</t>
   </si>
   <si>
-    <t>Broward County ENVIROS</t>
-  </si>
-  <si>
     <t>https://dpep.broward.org/Enviros/default.aspx</t>
   </si>
   <si>
@@ -919,6 +952,27 @@
     <t>Collier</t>
   </si>
   <si>
+    <t>Collier County Building Department</t>
+  </si>
+  <si>
+    <t>Renata Robbins Custodian of Public Records</t>
+  </si>
+  <si>
+    <t>PublicRecordsRequest@CollierClerk.com</t>
+  </si>
+  <si>
+    <t>Collier County Planning Department</t>
+  </si>
+  <si>
+    <t>Collier County Environmental Department</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMDPublicRecordRequest@CollierCountyFL.gov </t>
+  </si>
+  <si>
+    <t>Collier County Fire Department</t>
+  </si>
+  <si>
     <t>Marco Island</t>
   </si>
   <si>
@@ -998,6 +1052,83 @@
   </si>
   <si>
     <t>City of Sebring Fire Department</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highlands County Building Department </t>
+  </si>
+  <si>
+    <t>https://highlandsfl.justfoia.com/publicportal/home/newrequest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highlands County Planning Department </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highlands County Environmental Department </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highlands County Fire Department </t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>Martin County Building Department</t>
+  </si>
+  <si>
+    <t>https://www.martin.fl.us/martin-county-services/request-blue-prints</t>
+  </si>
+  <si>
+    <t>Building Portal</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">Use Portal or self-lookup: </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://aca-prod.accela.com/MARTINCO/Welcome.aspx</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Martin County Planning Department</t>
+  </si>
+  <si>
+    <t>https://rfs.martin.fl.us/app/f?p=1010:550:3833741149701::::REQUEST_TYPE_ID_APPITM:731</t>
+  </si>
+  <si>
+    <t>Martin County Environmental Department</t>
+  </si>
+  <si>
+    <t>Martin County Fire Department</t>
+  </si>
+  <si>
+    <t>Indian River</t>
+  </si>
+  <si>
+    <t>Indian River County Building Department</t>
+  </si>
+  <si>
+    <t>Indian River County Clerk</t>
+  </si>
+  <si>
+    <t>clerk@indianriverclerk.com</t>
+  </si>
+  <si>
+    <t>Indian River County Planning Department</t>
+  </si>
+  <si>
+    <t>Indian River County Environmental Department</t>
+  </si>
+  <si>
+    <t>Indian River County Fire Department</t>
   </si>
 </sst>
 </file>
@@ -1126,9 +1257,6 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -1142,6 +1270,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1839,12 +1970,14 @@
       <c r="F16" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G16" s="10"/>
+      <c r="G16" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="H16" s="3" t="s">
         <v>57</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="9"/>
@@ -1860,15 +1993,15 @@
         <v>28</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3"/>
       <c r="G17" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I17" s="6" t="s">
         <v>36</v>
@@ -1881,24 +2014,24 @@
         <v>11</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="3"/>
       <c r="G18" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="9"/>
@@ -1908,24 +2041,24 @@
         <v>11</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3"/>
       <c r="G19" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="9"/>
@@ -1935,24 +2068,24 @@
         <v>11</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3"/>
       <c r="G20" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="9"/>
@@ -1962,24 +2095,24 @@
         <v>11</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3"/>
       <c r="G21" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="9"/>
@@ -1989,24 +2122,24 @@
         <v>11</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="3"/>
       <c r="G22" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="9"/>
@@ -2016,24 +2149,24 @@
         <v>11</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="3"/>
       <c r="G23" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="9"/>
@@ -2043,24 +2176,24 @@
         <v>11</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="3"/>
       <c r="G24" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="9"/>
@@ -2070,31 +2203,31 @@
         <v>11</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="3"/>
       <c r="G25" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="9"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>53</v>
@@ -2103,22 +2236,22 @@
         <v>13</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>19</v>
@@ -2129,7 +2262,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>53</v>
@@ -2138,16 +2271,16 @@
         <v>21</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>36</v>
@@ -2164,7 +2297,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>53</v>
@@ -2173,16 +2306,16 @@
         <v>23</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G28" s="7" t="s">
         <v>90</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>36</v>
@@ -2193,7 +2326,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>53</v>
@@ -2202,353 +2335,353 @@
         <v>28</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G29" s="11" t="s">
-        <v>94</v>
+      <c r="G29" s="10" t="s">
+        <v>95</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="9"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="G31" s="12"/>
+        <v>100</v>
+      </c>
+      <c r="G31" s="11"/>
       <c r="H31" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="9"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="G32" s="12"/>
+        <v>100</v>
+      </c>
+      <c r="G32" s="11"/>
       <c r="H32" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="9"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="G33" s="12"/>
+        <v>100</v>
+      </c>
+      <c r="G33" s="11"/>
       <c r="H33" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="9"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K37" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>19</v>
@@ -2559,39 +2692,39 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>53</v>
@@ -2600,30 +2733,30 @@
         <v>13</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>53</v>
@@ -2632,30 +2765,30 @@
         <v>21</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K43" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>53</v>
@@ -2664,19 +2797,19 @@
         <v>23</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>19</v>
@@ -2687,7 +2820,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>53</v>
@@ -2696,30 +2829,30 @@
         <v>28</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>53</v>
@@ -2728,33 +2861,33 @@
         <v>13</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="I46" s="13" t="s">
         <v>135</v>
+      </c>
+      <c r="I46" s="12" t="s">
+        <v>136</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>53</v>
@@ -2763,210 +2896,210 @@
         <v>21</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="G50" s="14" t="s">
-        <v>155</v>
+        <v>151</v>
+      </c>
+      <c r="G50" s="13" t="s">
+        <v>156</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="B51" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="C51" s="16" t="s">
+      <c r="A51" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C51" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D51" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="E51" s="15" t="s">
+      <c r="D51" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="F51" s="15" t="s">
+      <c r="E51" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="G51" s="15"/>
-      <c r="H51" s="15" t="s">
+      <c r="F51" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="I51" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="J51" s="16" t="s">
+      <c r="G51" s="14"/>
+      <c r="H51" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="I51" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="J51" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="K51" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="16"/>
-      <c r="O51" s="16"/>
-      <c r="P51" s="16"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="16"/>
-      <c r="S51" s="16"/>
-      <c r="T51" s="16"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="16"/>
-      <c r="W51" s="16"/>
-      <c r="X51" s="16"/>
-      <c r="Y51" s="16"/>
-      <c r="Z51" s="16"/>
+      <c r="K51" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="L51" s="15"/>
+      <c r="M51" s="15"/>
+      <c r="N51" s="15"/>
+      <c r="O51" s="15"/>
+      <c r="P51" s="15"/>
+      <c r="Q51" s="15"/>
+      <c r="R51" s="15"/>
+      <c r="S51" s="15"/>
+      <c r="T51" s="15"/>
+      <c r="U51" s="15"/>
+      <c r="V51" s="15"/>
+      <c r="W51" s="15"/>
+      <c r="X51" s="15"/>
+      <c r="Y51" s="15"/>
+      <c r="Z51" s="15"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>19</v>
@@ -2977,31 +3110,31 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>19</v>
@@ -3012,311 +3145,311 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="9"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="9"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="9"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J57" s="2"/>
       <c r="K57" s="9"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J58" s="2"/>
       <c r="K58" s="9"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="9"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="9"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="9"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="9"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="9"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>36</v>
@@ -3329,23 +3462,23 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>36</v>
@@ -3358,230 +3491,245 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="9"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="9"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="9"/>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="B69" s="6" t="s">
+      <c r="A69" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="B69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="D69" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="G69" s="7" t="s">
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="H69" s="6" t="s">
+      <c r="H69" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I69" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="I69" s="6" t="s">
+      <c r="J69" s="2"/>
+      <c r="K69" s="9"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="B70" s="6" t="s">
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="J70" s="2"/>
+      <c r="K70" s="9"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C70" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="G70" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="I70" s="6" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="J71" s="2"/>
+      <c r="K71" s="9"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C71" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="F71" s="6"/>
-      <c r="G71" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="H71" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="I71" s="6" t="s">
+      <c r="B72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="B72" s="6" t="s">
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="J72" s="2"/>
+      <c r="K72" s="9"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="C72" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="I72" s="6" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="6" t="s">
-        <v>216</v>
-      </c>
       <c r="B73" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D73" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="B74" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="G73" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="H73" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I73" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D74" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="G74" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="G74" s="7" t="s">
-        <v>230</v>
-      </c>
       <c r="H74" s="6" t="s">
-        <v>36</v>
+        <v>232</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>75</v>
+        <v>233</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>23</v>
@@ -3591,90 +3739,90 @@
       </c>
       <c r="F75" s="6"/>
       <c r="G75" s="7" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="76">
       <c r="A76" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D76" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="G76" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="G76" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>36</v>
-      </c>
       <c r="I76" s="6" t="s">
-        <v>75</v>
+        <v>233</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>23</v>
@@ -3684,90 +3832,90 @@
       </c>
       <c r="F79" s="6"/>
       <c r="G79" s="7" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="6" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>242</v>
+        <v>76</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="6" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>242</v>
+        <v>76</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>23</v>
@@ -3777,90 +3925,90 @@
       </c>
       <c r="F83" s="6"/>
       <c r="G83" s="7" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="6" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>242</v>
+        <v>76</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="6" t="s">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="6" t="s">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>23</v>
@@ -3870,90 +4018,90 @@
       </c>
       <c r="F87" s="6"/>
       <c r="G87" s="7" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="6" t="s">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="H88" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="H89" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>75</v>
+        <v>253</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D90" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I90" s="6" t="s">
         <v>253</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I90" s="6" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>23</v>
@@ -3963,92 +4111,90 @@
       </c>
       <c r="F91" s="6"/>
       <c r="G91" s="7" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>75</v>
+        <v>253</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F93" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="G93" s="10"/>
+        <v>262</v>
+      </c>
+      <c r="G93" s="7" t="s">
+        <v>263</v>
+      </c>
       <c r="H93" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>258</v>
+        <v>76</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="F94" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="G94" s="10"/>
+        <v>264</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>263</v>
+      </c>
       <c r="H94" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>258</v>
+        <v>76</v>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>23</v>
@@ -4058,482 +4204,473 @@
       </c>
       <c r="F95" s="6"/>
       <c r="G95" s="7" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="G96" s="10"/>
+        <v>265</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>263</v>
+      </c>
       <c r="H96" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>262</v>
+        <v>76</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="G97" s="7" t="s">
-        <v>266</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="G97" s="16"/>
       <c r="H97" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D98" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="F98" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="F98" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>266</v>
-      </c>
+      <c r="G98" s="16"/>
       <c r="H98" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>265</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="F99" s="6"/>
       <c r="G99" s="7" t="s">
-        <v>266</v>
+        <v>235</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>36</v>
+        <v>236</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>267</v>
+        <v>237</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="G100" s="7" t="s">
-        <v>266</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="G100" s="16"/>
       <c r="H100" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="E101" s="6" t="s">
-        <v>15</v>
+        <v>275</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="H101" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D102" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="F102" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="E102" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F102" s="6" t="s">
-        <v>273</v>
-      </c>
       <c r="G102" s="7" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="H102" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D103" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="G103" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="E103" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="G103" s="7" t="s">
-        <v>274</v>
-      </c>
       <c r="H103" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D104" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I104" s="6" t="s">
         <v>278</v>
-      </c>
-      <c r="E104" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="G104" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I104" s="6" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E105" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H105" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H106" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E107" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H107" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H108" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="6" t="s">
-        <v>286</v>
+        <v>217</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>288</v>
+        <v>291</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>292</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="H109" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="J109" s="6" t="s">
-        <v>19</v>
+        <v>286</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="6" t="s">
-        <v>286</v>
+        <v>217</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>291</v>
+        <v>294</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>292</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="H110" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="J110" s="6" t="s">
-        <v>19</v>
+        <v>286</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="6" t="s">
-        <v>286</v>
+        <v>217</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D111" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F111" s="6" t="s">
         <v>292</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="J111" s="6" t="s">
-        <v>19</v>
+        <v>286</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="6" t="s">
-        <v>286</v>
+        <v>217</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D112" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="E112" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="G112" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="G112" s="7" t="s">
-        <v>289</v>
-      </c>
       <c r="H112" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="J112" s="6" t="s">
-        <v>19</v>
+        <v>286</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="6" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>53</v>
@@ -4542,21 +4679,25 @@
         <v>13</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>295</v>
+        <v>298</v>
+      </c>
+      <c r="E113" s="6" t="s">
+        <v>299</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>296</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="G113" s="16"/>
       <c r="H113" s="6" t="s">
-        <v>297</v>
+        <v>5</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>298</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="6" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>53</v>
@@ -4565,21 +4706,25 @@
         <v>21</v>
       </c>
       <c r="D114" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="E114" s="6" t="s">
         <v>299</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>296</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="G114" s="16"/>
       <c r="H114" s="6" t="s">
-        <v>297</v>
+        <v>5</v>
       </c>
       <c r="I114" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" ht="16.5" customHeight="1">
       <c r="A115" s="6" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>53</v>
@@ -4588,21 +4733,23 @@
         <v>23</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>300</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="E115" s="6"/>
       <c r="F115" s="6" t="s">
-        <v>301</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="G115" s="16"/>
       <c r="H115" s="6" t="s">
-        <v>302</v>
+        <v>5</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>303</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="6" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>53</v>
@@ -4613,140 +4760,608 @@
       <c r="D116" s="6" t="s">
         <v>304</v>
       </c>
+      <c r="E116" s="6" t="s">
+        <v>299</v>
+      </c>
       <c r="F116" s="6" t="s">
-        <v>296</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="G116" s="16"/>
       <c r="H116" s="6" t="s">
-        <v>297</v>
+        <v>5</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>104</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="B117" s="6" t="s">
         <v>305</v>
-      </c>
-      <c r="B117" s="6" t="s">
-        <v>306</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D117" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="G117" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="E117" s="6" t="s">
+      <c r="H117" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I117" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="F117" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="H117" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="I117" s="6" t="s">
-        <v>310</v>
+      <c r="J117" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="B118" s="6" t="s">
         <v>305</v>
-      </c>
-      <c r="B118" s="6" t="s">
-        <v>306</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="E118" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G118" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I118" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="F118" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="I118" s="6" t="s">
-        <v>310</v>
+      <c r="J118" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="B119" s="6" t="s">
         <v>305</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>306</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="E119" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="G119" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="H119" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I119" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="F119" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="H119" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="I119" s="6" t="s">
-        <v>310</v>
+      <c r="J119" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="B120" s="6" t="s">
         <v>305</v>
-      </c>
-      <c r="B120" s="6" t="s">
-        <v>306</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D120" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="G120" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I120" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="J120" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="121" ht="15.75" customHeight="1">
+      <c r="A121" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D121" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="E120" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="F120" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="I120" s="6" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
+      <c r="F121" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="H121" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="I121" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="I122" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="A123" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="H123" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="I123" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="124" ht="15.75" customHeight="1">
+      <c r="A124" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="I124" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
+      <c r="A125" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="H125" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="I125" s="6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="A126" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="I126" s="6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="127" ht="15.75" customHeight="1">
+      <c r="A127" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="F127" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="H127" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="I127" s="6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="128" ht="15.75" customHeight="1">
+      <c r="A128" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="H128" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="I128" s="6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="129" ht="15.75" customHeight="1">
+      <c r="A129" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="H129" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I129" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="130" ht="15.75" customHeight="1">
+      <c r="A130" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I130" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="131" ht="15.75" customHeight="1">
+      <c r="A131" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="H131" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I131" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="132" ht="15.75" customHeight="1">
+      <c r="A132" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="H132" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I132" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="133" ht="15.75" customHeight="1">
+      <c r="A133" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="G133" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="H133" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="I133" s="7" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="134" ht="15.75" customHeight="1">
+      <c r="A134" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="G134" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="H134" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I134" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="135" ht="15.75" customHeight="1">
+      <c r="A135" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="G135" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="H135" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I135" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="136" ht="15.75" customHeight="1">
+      <c r="A136" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="G136" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="H136" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I136" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="137" ht="15.75" customHeight="1">
+      <c r="A137" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="F137" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="H137" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I137" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="138" ht="15.75" customHeight="1">
+      <c r="A138" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="F138" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="H138" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I138" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="139" ht="15.75" customHeight="1">
+      <c r="A139" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="F139" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="H139" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I139" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="140" ht="15.75" customHeight="1">
+      <c r="A140" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="H140" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I140" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
     <row r="141" ht="15.75" customHeight="1"/>
     <row r="142" ht="15.75" customHeight="1"/>
     <row r="143" ht="15.75" customHeight="1"/>
@@ -5691,6 +6306,14 @@
     <row r="1082" ht="15.75" customHeight="1"/>
     <row r="1083" ht="15.75" customHeight="1"/>
     <row r="1084" ht="15.75" customHeight="1"/>
+    <row r="1085" ht="15.75" customHeight="1"/>
+    <row r="1086" ht="15.75" customHeight="1"/>
+    <row r="1087" ht="15.75" customHeight="1"/>
+    <row r="1088" ht="15.75" customHeight="1"/>
+    <row r="1089" ht="15.75" customHeight="1"/>
+    <row r="1090" ht="15.75" customHeight="1"/>
+    <row r="1091" ht="15.75" customHeight="1"/>
+    <row r="1092" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" location="/home" ref="G2"/>
@@ -5706,100 +6329,114 @@
     <hyperlink r:id="rId11" ref="G13"/>
     <hyperlink r:id="rId12" ref="G14"/>
     <hyperlink r:id="rId13" ref="G15"/>
-    <hyperlink r:id="rId14" ref="G17"/>
-    <hyperlink r:id="rId15" ref="G18"/>
-    <hyperlink r:id="rId16" ref="G19"/>
-    <hyperlink r:id="rId17" ref="G20"/>
-    <hyperlink r:id="rId18" ref="G21"/>
-    <hyperlink r:id="rId19" ref="G22"/>
-    <hyperlink r:id="rId20" ref="G23"/>
-    <hyperlink r:id="rId21" ref="G24"/>
-    <hyperlink r:id="rId22" ref="G25"/>
-    <hyperlink r:id="rId23" ref="G26"/>
-    <hyperlink r:id="rId24" ref="G27"/>
-    <hyperlink r:id="rId25" ref="G28"/>
-    <hyperlink r:id="rId26" ref="G29"/>
-    <hyperlink r:id="rId27" location="/home" ref="G30"/>
-    <hyperlink r:id="rId28" ref="G34"/>
-    <hyperlink r:id="rId29" ref="G35"/>
-    <hyperlink r:id="rId30" ref="G36"/>
-    <hyperlink r:id="rId31" ref="G37"/>
-    <hyperlink r:id="rId32" ref="G38"/>
-    <hyperlink r:id="rId33" ref="G39"/>
-    <hyperlink r:id="rId34" ref="G40"/>
-    <hyperlink r:id="rId35" ref="G41"/>
-    <hyperlink r:id="rId36" ref="G42"/>
-    <hyperlink r:id="rId37" ref="G43"/>
-    <hyperlink r:id="rId38" ref="G44"/>
-    <hyperlink r:id="rId39" ref="G45"/>
-    <hyperlink r:id="rId40" ref="G46"/>
-    <hyperlink r:id="rId41" ref="I46"/>
-    <hyperlink r:id="rId42" ref="G47"/>
-    <hyperlink r:id="rId43" ref="G48"/>
-    <hyperlink r:id="rId44" ref="G49"/>
-    <hyperlink r:id="rId45" ref="G50"/>
-    <hyperlink r:id="rId46" ref="G52"/>
-    <hyperlink r:id="rId47" ref="G53"/>
-    <hyperlink r:id="rId48" ref="G54"/>
-    <hyperlink r:id="rId49" ref="G55"/>
-    <hyperlink r:id="rId50" ref="G56"/>
-    <hyperlink r:id="rId51" location="/home" ref="G57"/>
-    <hyperlink r:id="rId52" ref="G58"/>
-    <hyperlink r:id="rId53" ref="G59"/>
-    <hyperlink r:id="rId54" ref="G60"/>
-    <hyperlink r:id="rId55" ref="G61"/>
-    <hyperlink r:id="rId56" ref="G62"/>
-    <hyperlink r:id="rId57" ref="G63"/>
-    <hyperlink r:id="rId58" ref="G64"/>
-    <hyperlink r:id="rId59" ref="G65"/>
-    <hyperlink r:id="rId60" ref="G66"/>
-    <hyperlink r:id="rId61" ref="G67"/>
-    <hyperlink r:id="rId62" ref="G68"/>
-    <hyperlink r:id="rId63" ref="G69"/>
-    <hyperlink r:id="rId64" ref="G70"/>
-    <hyperlink r:id="rId65" ref="G71"/>
-    <hyperlink r:id="rId66" ref="G72"/>
-    <hyperlink r:id="rId67" ref="G73"/>
-    <hyperlink r:id="rId68" ref="G74"/>
-    <hyperlink r:id="rId69" ref="G75"/>
-    <hyperlink r:id="rId70" ref="G76"/>
-    <hyperlink r:id="rId71" ref="G77"/>
-    <hyperlink r:id="rId72" ref="G78"/>
-    <hyperlink r:id="rId73" ref="G79"/>
-    <hyperlink r:id="rId74" ref="G80"/>
-    <hyperlink r:id="rId75" ref="G81"/>
-    <hyperlink r:id="rId76" ref="G82"/>
-    <hyperlink r:id="rId77" ref="G83"/>
-    <hyperlink r:id="rId78" ref="G84"/>
-    <hyperlink r:id="rId79" ref="G85"/>
-    <hyperlink r:id="rId80" ref="G86"/>
-    <hyperlink r:id="rId81" ref="G87"/>
-    <hyperlink r:id="rId82" ref="G88"/>
-    <hyperlink r:id="rId83" ref="G89"/>
-    <hyperlink r:id="rId84" ref="G90"/>
-    <hyperlink r:id="rId85" ref="G91"/>
-    <hyperlink r:id="rId86" ref="G92"/>
-    <hyperlink r:id="rId87" ref="G95"/>
-    <hyperlink r:id="rId88" ref="G97"/>
-    <hyperlink r:id="rId89" ref="G98"/>
-    <hyperlink r:id="rId90" ref="G99"/>
-    <hyperlink r:id="rId91" ref="G100"/>
-    <hyperlink r:id="rId92" ref="G101"/>
-    <hyperlink r:id="rId93" ref="G102"/>
-    <hyperlink r:id="rId94" ref="G103"/>
-    <hyperlink r:id="rId95" ref="G104"/>
-    <hyperlink r:id="rId96" ref="G105"/>
-    <hyperlink r:id="rId97" ref="G106"/>
-    <hyperlink r:id="rId98" ref="G107"/>
-    <hyperlink r:id="rId99" ref="G108"/>
-    <hyperlink r:id="rId100" ref="G109"/>
-    <hyperlink r:id="rId101" ref="G110"/>
-    <hyperlink r:id="rId102" ref="G111"/>
-    <hyperlink r:id="rId103" ref="G112"/>
+    <hyperlink r:id="rId14" ref="G16"/>
+    <hyperlink r:id="rId15" ref="G17"/>
+    <hyperlink r:id="rId16" ref="G18"/>
+    <hyperlink r:id="rId17" ref="G19"/>
+    <hyperlink r:id="rId18" ref="G20"/>
+    <hyperlink r:id="rId19" ref="G21"/>
+    <hyperlink r:id="rId20" ref="G22"/>
+    <hyperlink r:id="rId21" ref="G23"/>
+    <hyperlink r:id="rId22" ref="G24"/>
+    <hyperlink r:id="rId23" ref="G25"/>
+    <hyperlink r:id="rId24" ref="G26"/>
+    <hyperlink r:id="rId25" ref="G27"/>
+    <hyperlink r:id="rId26" ref="G28"/>
+    <hyperlink r:id="rId27" ref="G29"/>
+    <hyperlink r:id="rId28" location="/home" ref="G30"/>
+    <hyperlink r:id="rId29" ref="G34"/>
+    <hyperlink r:id="rId30" ref="G35"/>
+    <hyperlink r:id="rId31" ref="G36"/>
+    <hyperlink r:id="rId32" ref="G37"/>
+    <hyperlink r:id="rId33" ref="G38"/>
+    <hyperlink r:id="rId34" ref="G39"/>
+    <hyperlink r:id="rId35" ref="G40"/>
+    <hyperlink r:id="rId36" ref="G41"/>
+    <hyperlink r:id="rId37" ref="G42"/>
+    <hyperlink r:id="rId38" ref="G43"/>
+    <hyperlink r:id="rId39" ref="G44"/>
+    <hyperlink r:id="rId40" ref="G45"/>
+    <hyperlink r:id="rId41" ref="G46"/>
+    <hyperlink r:id="rId42" ref="I46"/>
+    <hyperlink r:id="rId43" ref="G47"/>
+    <hyperlink r:id="rId44" ref="G48"/>
+    <hyperlink r:id="rId45" ref="G49"/>
+    <hyperlink r:id="rId46" ref="G50"/>
+    <hyperlink r:id="rId47" ref="G52"/>
+    <hyperlink r:id="rId48" ref="G53"/>
+    <hyperlink r:id="rId49" ref="G54"/>
+    <hyperlink r:id="rId50" ref="G55"/>
+    <hyperlink r:id="rId51" ref="G56"/>
+    <hyperlink r:id="rId52" location="/home" ref="G57"/>
+    <hyperlink r:id="rId53" ref="G58"/>
+    <hyperlink r:id="rId54" ref="G59"/>
+    <hyperlink r:id="rId55" ref="G60"/>
+    <hyperlink r:id="rId56" ref="G61"/>
+    <hyperlink r:id="rId57" ref="G62"/>
+    <hyperlink r:id="rId58" ref="G63"/>
+    <hyperlink r:id="rId59" ref="G64"/>
+    <hyperlink r:id="rId60" ref="G65"/>
+    <hyperlink r:id="rId61" ref="G66"/>
+    <hyperlink r:id="rId62" ref="G67"/>
+    <hyperlink r:id="rId63" ref="G68"/>
+    <hyperlink r:id="rId64" ref="G69"/>
+    <hyperlink r:id="rId65" ref="G70"/>
+    <hyperlink r:id="rId66" ref="G71"/>
+    <hyperlink r:id="rId67" ref="G72"/>
+    <hyperlink r:id="rId68" ref="G73"/>
+    <hyperlink r:id="rId69" ref="G74"/>
+    <hyperlink r:id="rId70" ref="G75"/>
+    <hyperlink r:id="rId71" ref="G76"/>
+    <hyperlink r:id="rId72" ref="G77"/>
+    <hyperlink r:id="rId73" ref="G78"/>
+    <hyperlink r:id="rId74" ref="G79"/>
+    <hyperlink r:id="rId75" ref="G80"/>
+    <hyperlink r:id="rId76" ref="G81"/>
+    <hyperlink r:id="rId77" ref="G82"/>
+    <hyperlink r:id="rId78" ref="G83"/>
+    <hyperlink r:id="rId79" ref="G84"/>
+    <hyperlink r:id="rId80" ref="G85"/>
+    <hyperlink r:id="rId81" ref="G86"/>
+    <hyperlink r:id="rId82" ref="G87"/>
+    <hyperlink r:id="rId83" ref="G88"/>
+    <hyperlink r:id="rId84" ref="G89"/>
+    <hyperlink r:id="rId85" ref="G90"/>
+    <hyperlink r:id="rId86" ref="G91"/>
+    <hyperlink r:id="rId87" ref="G92"/>
+    <hyperlink r:id="rId88" ref="G93"/>
+    <hyperlink r:id="rId89" ref="G94"/>
+    <hyperlink r:id="rId90" ref="G95"/>
+    <hyperlink r:id="rId91" ref="G96"/>
+    <hyperlink r:id="rId92" ref="G99"/>
+    <hyperlink r:id="rId93" ref="G101"/>
+    <hyperlink r:id="rId94" ref="G102"/>
+    <hyperlink r:id="rId95" ref="G103"/>
+    <hyperlink r:id="rId96" ref="G104"/>
+    <hyperlink r:id="rId97" ref="G105"/>
+    <hyperlink r:id="rId98" ref="G106"/>
+    <hyperlink r:id="rId99" ref="G107"/>
+    <hyperlink r:id="rId100" ref="G108"/>
+    <hyperlink r:id="rId101" ref="G109"/>
+    <hyperlink r:id="rId102" ref="G110"/>
+    <hyperlink r:id="rId103" ref="G111"/>
+    <hyperlink r:id="rId104" ref="G112"/>
+    <hyperlink r:id="rId105" ref="G117"/>
+    <hyperlink r:id="rId106" ref="G118"/>
+    <hyperlink r:id="rId107" ref="G119"/>
+    <hyperlink r:id="rId108" ref="G120"/>
+    <hyperlink r:id="rId109" ref="G129"/>
+    <hyperlink r:id="rId110" ref="G130"/>
+    <hyperlink r:id="rId111" ref="G131"/>
+    <hyperlink r:id="rId112" ref="G132"/>
+    <hyperlink r:id="rId113" ref="G133"/>
+    <hyperlink r:id="rId114" ref="I133"/>
+    <hyperlink r:id="rId115" ref="G134"/>
+    <hyperlink r:id="rId116" ref="G135"/>
+    <hyperlink r:id="rId117" ref="G136"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId104"/>
+  <drawing r:id="rId118"/>
 </worksheet>
 </file>
--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Oc3QG2j82QTTpMJdMTtco/OHvJOY3ciGopg0F7LwR10="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="iDawz/RLxtopVSfNMejEDj4vPqPRh3haGFonxe3AFck="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="362">
   <si>
     <t>County</t>
   </si>
@@ -154,20 +154,7 @@
     <t>Select Planning &amp; Zoning</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://www.pbcgov.org/eprr/erm</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF0000FF"/>
-        <u/>
-      </rPr>
-      <t>m</t>
-    </r>
+    <t>https://www.pbcgov.org/eprr/erm</t>
   </si>
   <si>
     <t>Boynton Beach Fire Rescue</t>
@@ -227,13 +214,10 @@
     <t>PublicRecordsRequest@flhealth.gov</t>
   </si>
   <si>
-    <t>https://www.pbcgov.org/eprr/erm</t>
-  </si>
-  <si>
     <t>Palm Beach County Fire Department</t>
   </si>
   <si>
-    <t>https://pbcfr.justfoia.com/Forms/Launch/a3770868-033f-442c-b6d0-a11d3493c386</t>
+    <t>https://pbcfr.justfoia.com/publicportal/home/newrequest</t>
   </si>
   <si>
     <t xml:space="preserve">Portal </t>
@@ -282,6 +266,30 @@
   </si>
   <si>
     <t>City of Delray Fire Department</t>
+  </si>
+  <si>
+    <t>West Palm Beach</t>
+  </si>
+  <si>
+    <t>City of West Palm Beach Building Department</t>
+  </si>
+  <si>
+    <t>https://westpalmbeachfl.govqa.us/WEBAPP/_rs/(S(rb2xhvxicdz0ax5cyrcosnte))/SupportHome.aspx?LP=2</t>
+  </si>
+  <si>
+    <t>Portal -&gt; Property Requests -&gt; Multiple Departments</t>
+  </si>
+  <si>
+    <t>City of West Palm Beach Planning Department</t>
+  </si>
+  <si>
+    <t>Palm Beach County Environmental Resources Management</t>
+  </si>
+  <si>
+    <t>City of West Palm Fire Department</t>
+  </si>
+  <si>
+    <t>Portal -&gt; General Request</t>
   </si>
   <si>
     <t>Lee</t>
@@ -526,6 +534,9 @@
     <t>City of Miami Gardens — Planning &amp; Zoning</t>
   </si>
   <si>
+    <t>zoninginfo@miamigardens-fl.gov</t>
+  </si>
+  <si>
     <t>https://miamigardensfl.justfoia.com/publicportal</t>
   </si>
   <si>
@@ -1120,6 +1131,9 @@
   </si>
   <si>
     <t>clerk@indianriverclerk.com</t>
+  </si>
+  <si>
+    <t>https://indianriver.justfoia.com/publicportal/home/newrequest</t>
   </si>
   <si>
     <t>Indian River County Planning Department</t>
@@ -1971,7 +1985,7 @@
         <v>60</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>57</v>
@@ -1993,15 +2007,15 @@
         <v>28</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3"/>
       <c r="G17" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="I17" s="6" t="s">
         <v>36</v>
@@ -2014,24 +2028,24 @@
         <v>11</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="3"/>
       <c r="G18" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="I18" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="9"/>
@@ -2041,24 +2055,24 @@
         <v>11</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3"/>
       <c r="G19" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="I19" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="9"/>
@@ -2068,24 +2082,24 @@
         <v>11</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3"/>
       <c r="G20" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="9"/>
@@ -2095,24 +2109,24 @@
         <v>11</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3"/>
       <c r="G21" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="I21" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="9"/>
@@ -2122,24 +2136,24 @@
         <v>11</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="3"/>
       <c r="G22" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I22" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="9"/>
@@ -2149,24 +2163,24 @@
         <v>11</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="3"/>
       <c r="G23" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I23" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="9"/>
@@ -2176,24 +2190,24 @@
         <v>11</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="3"/>
       <c r="G24" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I24" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="9"/>
@@ -2203,613 +2217,593 @@
         <v>11</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="3"/>
       <c r="G25" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I25" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="9"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="E26" s="2"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J26" s="2"/>
+      <c r="K26" s="9"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J27" s="2"/>
+      <c r="K27" s="9"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J28" s="2"/>
+      <c r="K28" s="9"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="J29" s="2"/>
+      <c r="K29" s="9"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J26" s="2" t="s">
+      <c r="D30" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="K30" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B27" s="2" t="s">
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J27" s="2" t="s">
+      <c r="B32" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J33" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K27" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E30" s="2"/>
-      <c r="F30" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="J30" s="2"/>
-      <c r="K30" s="9"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31" s="3" t="s">
+      <c r="K33" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E31" s="2"/>
-      <c r="F31" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G31" s="11"/>
-      <c r="H31" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I31" s="3" t="s">
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="J31" s="2"/>
-      <c r="K31" s="9"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G32" s="11"/>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J32" s="2"/>
-      <c r="K32" s="9"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G33" s="11"/>
-      <c r="H33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J33" s="2"/>
-      <c r="K33" s="9"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="H34" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G34" s="5" t="s">
+      <c r="I34" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>112</v>
-      </c>
+      <c r="J34" s="2"/>
+      <c r="K34" s="9"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="s">
-        <v>80</v>
+      <c r="A35" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>110</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G35" s="11"/>
       <c r="H35" s="3" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>114</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="J35" s="2"/>
+      <c r="K35" s="9"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="s">
-        <v>80</v>
+      <c r="A36" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>110</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G36" s="11"/>
       <c r="H36" s="3" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>116</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="J36" s="2"/>
+      <c r="K36" s="9"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="s">
-        <v>80</v>
+      <c r="A37" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>110</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G37" s="11"/>
       <c r="H37" s="3" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>118</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="J37" s="2"/>
+      <c r="K37" s="9"/>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="s">
-        <v>119</v>
+      <c r="A38" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>122</v>
+        <v>116</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="J38" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J38" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="s">
-        <v>119</v>
+      <c r="A39" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="J39" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J39" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="s">
-        <v>119</v>
+      <c r="A40" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E40" s="3" t="s">
         <v>122</v>
       </c>
+      <c r="E40" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="G40" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K40" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="H40" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K40" s="9" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="s">
-        <v>119</v>
+      <c r="A41" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="J41" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J41" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>53</v>
+        <v>127</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>53</v>
+        <v>127</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K43" s="9" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>53</v>
+        <v>127</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>19</v>
@@ -2820,800 +2814,820 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>53</v>
+        <v>127</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G46" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="2" t="s">
+      <c r="H46" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K46" s="9" t="s">
         <v>131</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="I46" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G47" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>140</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="J47" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K47" s="2" t="s">
-        <v>97</v>
+      <c r="K47" s="9" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>142</v>
+        <v>53</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="J48" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J48" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K48" s="2" t="s">
-        <v>97</v>
+      <c r="K48" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G49" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>152</v>
-      </c>
       <c r="H49" s="3" t="s">
-        <v>153</v>
+        <v>36</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="J49" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J49" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K49" s="2" t="s">
-        <v>97</v>
+      <c r="K49" s="9" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>148</v>
+        <v>53</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G50" s="13" t="s">
-        <v>156</v>
+        <v>138</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>158</v>
+        <v>142</v>
+      </c>
+      <c r="I50" s="12" t="s">
+        <v>143</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="B51" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="C51" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D51" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="E51" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="F51" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="I51" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="J51" s="15" t="s">
+      <c r="A51" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="J51" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K51" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="L51" s="15"/>
-      <c r="M51" s="15"/>
-      <c r="N51" s="15"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="15"/>
-      <c r="R51" s="15"/>
-      <c r="S51" s="15"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="15"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="15"/>
-      <c r="Z51" s="15"/>
+      <c r="K51" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>13</v>
+        <v>149</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K52" s="9" t="s">
-        <v>38</v>
+      <c r="K52" s="2" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>163</v>
+        <v>137</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>169</v>
+        <v>13</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>167</v>
+        <v>158</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>159</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>36</v>
+        <v>160</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K53" s="9" t="s">
-        <v>38</v>
+      <c r="K53" s="2" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E54" s="3"/>
+        <v>137</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>157</v>
+      </c>
       <c r="F54" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>174</v>
+        <v>163</v>
+      </c>
+      <c r="G54" s="13" t="s">
+        <v>164</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="J54" s="2"/>
-      <c r="K54" s="9"/>
+        <v>165</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="J55" s="2"/>
-      <c r="K55" s="9"/>
+      <c r="A55" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="E55" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="F55" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="I55" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="J55" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="K55" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="L55" s="15"/>
+      <c r="M55" s="15"/>
+      <c r="N55" s="15"/>
+      <c r="O55" s="15"/>
+      <c r="P55" s="15"/>
+      <c r="Q55" s="15"/>
+      <c r="R55" s="15"/>
+      <c r="S55" s="15"/>
+      <c r="T55" s="15"/>
+      <c r="U55" s="15"/>
+      <c r="V55" s="15"/>
+      <c r="W55" s="15"/>
+      <c r="X55" s="15"/>
+      <c r="Y55" s="15"/>
+      <c r="Z55" s="15"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>28</v>
+      <c r="C56" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E56" s="3"/>
+        <v>172</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>173</v>
+      </c>
       <c r="F56" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>180</v>
+        <v>36</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J56" s="2"/>
-      <c r="K56" s="9"/>
+        <v>176</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K56" s="9" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>13</v>
+        <v>171</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E57" s="3"/>
+        <v>177</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>173</v>
+      </c>
       <c r="F57" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>185</v>
+        <v>174</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>175</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>186</v>
+        <v>36</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J57" s="2"/>
-      <c r="K57" s="9"/>
+        <v>178</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K57" s="9" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G58" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-      <c r="G58" s="5" t="s">
-        <v>189</v>
-      </c>
       <c r="H58" s="3" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J58" s="2"/>
       <c r="K58" s="9"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="9"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>36</v>
+        <v>188</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="9"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>190</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>36</v>
+        <v>194</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="9"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E62" s="3"/>
-      <c r="F62" s="3" t="s">
-        <v>202</v>
-      </c>
+      <c r="F62" s="3"/>
       <c r="G62" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>204</v>
+        <v>36</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="9"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I63" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>204</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="9"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>36</v>
+        <v>205</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="9"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B65" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>36</v>
+        <v>205</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="9"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D66" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="H66" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="I66" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="9"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
+      <c r="F67" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="G67" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>36</v>
+        <v>212</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="9"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D68" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
       <c r="G68" s="5" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>214</v>
+        <v>36</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="9"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>217</v>
+        <v>137</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>53</v>
+        <v>214</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>218</v>
       </c>
       <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
+      <c r="F69" s="3" t="s">
+        <v>216</v>
+      </c>
       <c r="G69" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>220</v>
+        <v>36</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="9"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>217</v>
+        <v>137</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>36</v>
@@ -3626,13 +3640,13 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>217</v>
+        <v>137</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>223</v>
@@ -3640,166 +3654,181 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="9"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>217</v>
+        <v>137</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="5" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="J72" s="2"/>
       <c r="K72" s="9"/>
     </row>
     <row r="73">
-      <c r="A73" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B73" s="6" t="s">
+      <c r="A73" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="J73" s="2"/>
+      <c r="K73" s="9"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C73" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D73" s="6" t="s">
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I74" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="G73" s="7" t="s">
+      <c r="J74" s="2"/>
+      <c r="K74" s="9"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="H73" s="6" t="s">
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="I73" s="6" t="s">
+      <c r="H75" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I75" s="3" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D74" s="6" t="s">
+      <c r="J75" s="2"/>
+      <c r="K75" s="9"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="G74" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="I74" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="F75" s="6"/>
-      <c r="G75" s="7" t="s">
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="H75" s="6" t="s">
+      <c r="H76" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I76" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I75" s="6" t="s">
+      <c r="J76" s="2"/>
+      <c r="K76" s="9"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B77" s="6" t="s">
         <v>237</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="G76" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="I76" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D77" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="H77" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="G77" s="7" t="s">
+      <c r="I77" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="H77" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I77" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
+    </row>
+    <row r="78">
       <c r="A78" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>21</v>
@@ -3808,533 +3837,530 @@
         <v>242</v>
       </c>
       <c r="G78" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="I78" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I78" s="6" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F79" s="6"/>
       <c r="G79" s="7" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I79" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B80" s="6" t="s">
         <v>237</v>
-      </c>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G80" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="I80" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I80" s="6" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F83" s="6"/>
       <c r="G83" s="7" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="6" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>253</v>
+        <v>75</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="6" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D86" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="G86" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="G86" s="7" t="s">
-        <v>252</v>
-      </c>
       <c r="H86" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>253</v>
+        <v>75</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F87" s="6"/>
       <c r="G87" s="7" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="6" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H88" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>253</v>
+        <v>75</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="6" t="s">
-        <v>217</v>
+        <v>257</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H89" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="6" t="s">
-        <v>217</v>
+        <v>257</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H90" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F91" s="6"/>
       <c r="G91" s="7" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="6" t="s">
-        <v>217</v>
+        <v>257</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D92" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="G92" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="G92" s="7" t="s">
-        <v>258</v>
-      </c>
       <c r="H92" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>76</v>
+        <v>261</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>76</v>
+        <v>261</v>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F95" s="6"/>
       <c r="G95" s="7" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="H96" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>76</v>
+        <v>261</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="F97" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="G97" s="16"/>
+        <v>270</v>
+      </c>
+      <c r="G97" s="7" t="s">
+        <v>271</v>
+      </c>
       <c r="H97" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>269</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="F98" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="G98" s="16"/>
+        <v>272</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>271</v>
+      </c>
       <c r="H98" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>269</v>
+        <v>75</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F99" s="6"/>
       <c r="G99" s="7" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D100" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="G100" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="F100" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="G100" s="16"/>
       <c r="H100" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>274</v>
@@ -4348,19 +4374,17 @@
       <c r="F101" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="G101" s="7" t="s">
+      <c r="G101" s="16"/>
+      <c r="H101" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I101" s="6" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>274</v>
@@ -4369,24 +4393,22 @@
         <v>21</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="G102" s="7" t="s">
+      <c r="G102" s="16"/>
+      <c r="H102" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I102" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I102" s="6" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>274</v>
@@ -4395,24 +4417,22 @@
         <v>23</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>276</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="F103" s="6"/>
       <c r="G103" s="7" t="s">
-        <v>277</v>
+        <v>243</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>36</v>
+        <v>244</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>278</v>
+        <v>245</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>274</v>
@@ -4421,24 +4441,22 @@
         <v>28</v>
       </c>
       <c r="D104" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="G104" s="16"/>
+      <c r="H104" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I104" s="6" t="s">
         <v>281</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="G104" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I104" s="6" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>282</v>
@@ -4449,9 +4467,6 @@
       <c r="D105" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="E105" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="F105" s="6" t="s">
         <v>284</v>
       </c>
@@ -4467,7 +4482,7 @@
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>282</v>
@@ -4478,9 +4493,6 @@
       <c r="D106" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="E106" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="F106" s="6" t="s">
         <v>284</v>
       </c>
@@ -4496,7 +4508,7 @@
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>282</v>
@@ -4507,9 +4519,6 @@
       <c r="D107" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="E107" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="F107" s="6" t="s">
         <v>284</v>
       </c>
@@ -4525,7 +4534,7 @@
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>282</v>
@@ -4536,9 +4545,6 @@
       <c r="D108" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="E108" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="F108" s="6" t="s">
         <v>284</v>
       </c>
@@ -4554,7 +4560,7 @@
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>290</v>
@@ -4578,12 +4584,12 @@
         <v>36</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>290</v>
@@ -4592,7 +4598,7 @@
         <v>21</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>15</v>
@@ -4607,12 +4613,12 @@
         <v>36</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>290</v>
@@ -4621,7 +4627,7 @@
         <v>23</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E111" s="6" t="s">
         <v>15</v>
@@ -4636,12 +4642,12 @@
         <v>36</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>290</v>
@@ -4650,7 +4656,7 @@
         <v>28</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>15</v>
@@ -4665,94 +4671,102 @@
         <v>36</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="6" t="s">
-        <v>297</v>
+        <v>225</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>53</v>
+        <v>298</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>299</v>
+        <v>15</v>
       </c>
       <c r="F113" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="G113" s="16"/>
+      <c r="G113" s="7" t="s">
+        <v>301</v>
+      </c>
       <c r="H113" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>5</v>
+        <v>294</v>
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="6" t="s">
-        <v>297</v>
+        <v>225</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>53</v>
+        <v>298</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>299</v>
+        <v>15</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="G114" s="16"/>
+      <c r="G114" s="7" t="s">
+        <v>301</v>
+      </c>
       <c r="H114" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="115" ht="16.5" customHeight="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="6" t="s">
-        <v>297</v>
+        <v>225</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>53</v>
+        <v>298</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="E115" s="6"/>
+        <v>303</v>
+      </c>
+      <c r="E115" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="F115" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="G115" s="16"/>
+        <v>300</v>
+      </c>
+      <c r="G115" s="7" t="s">
+        <v>301</v>
+      </c>
       <c r="H115" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>5</v>
+        <v>294</v>
       </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="6" t="s">
-        <v>297</v>
+        <v>225</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>53</v>
+        <v>298</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>28</v>
@@ -4761,25 +4775,27 @@
         <v>304</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>299</v>
+        <v>15</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="G116" s="16"/>
+      <c r="G116" s="7" t="s">
+        <v>301</v>
+      </c>
       <c r="H116" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>5</v>
+        <v>294</v>
       </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="6" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>305</v>
+        <v>53</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>13</v>
@@ -4787,25 +4803,26 @@
       <c r="D117" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="G117" s="7" t="s">
+      <c r="E117" s="6" t="s">
         <v>307</v>
       </c>
+      <c r="F117" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="G117" s="16"/>
       <c r="H117" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="J117" s="6" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="6" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>305</v>
+        <v>53</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>21</v>
@@ -4813,25 +4830,26 @@
       <c r="D118" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="G118" s="7" t="s">
+      <c r="E118" s="6" t="s">
         <v>307</v>
       </c>
+      <c r="F118" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="G118" s="16"/>
       <c r="H118" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="J118" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="119" ht="15.75" customHeight="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" ht="16.5" customHeight="1">
       <c r="A119" s="6" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>305</v>
+        <v>53</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>23</v>
@@ -4839,74 +4857,77 @@
       <c r="D119" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="G119" s="7" t="s">
-        <v>307</v>
-      </c>
+      <c r="E119" s="6"/>
+      <c r="F119" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="G119" s="16"/>
       <c r="H119" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="J119" s="6" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="6" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>305</v>
+        <v>53</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="G120" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="E120" s="6" t="s">
         <v>307</v>
       </c>
+      <c r="F120" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="G120" s="16"/>
       <c r="H120" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="J120" s="6" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="6" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>53</v>
+        <v>313</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="F121" s="6" t="s">
         <v>314</v>
       </c>
+      <c r="G121" s="7" t="s">
+        <v>315</v>
+      </c>
       <c r="H121" s="6" t="s">
-        <v>315</v>
+        <v>36</v>
       </c>
       <c r="I121" s="6" t="s">
         <v>316</v>
       </c>
+      <c r="J121" s="6" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="6" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>53</v>
+        <v>313</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>21</v>
@@ -4914,22 +4935,25 @@
       <c r="D122" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="F122" s="6" t="s">
-        <v>314</v>
+      <c r="G122" s="7" t="s">
+        <v>315</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>315</v>
+        <v>36</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>5</v>
+        <v>316</v>
+      </c>
+      <c r="J122" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="6" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>53</v>
+        <v>313</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>23</v>
@@ -4937,238 +4961,244 @@
       <c r="D123" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="F123" s="6" t="s">
-        <v>319</v>
+      <c r="G123" s="7" t="s">
+        <v>315</v>
       </c>
       <c r="H123" s="6" t="s">
-        <v>320</v>
+        <v>36</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>321</v>
+        <v>316</v>
+      </c>
+      <c r="J123" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="6" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>53</v>
+        <v>313</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="F124" s="6" t="s">
-        <v>314</v>
+        <v>319</v>
+      </c>
+      <c r="G124" s="7" t="s">
+        <v>315</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>315</v>
+        <v>36</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>105</v>
+        <v>316</v>
+      </c>
+      <c r="J124" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>324</v>
+        <v>53</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="E125" s="6" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="H125" s="6" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>324</v>
+        <v>53</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="E126" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>328</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>324</v>
+        <v>53</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="E127" s="6" t="s">
         <v>326</v>
       </c>
       <c r="F127" s="6" t="s">
         <v>327</v>
       </c>
       <c r="H127" s="6" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>324</v>
+        <v>53</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="E128" s="6" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>328</v>
+        <v>112</v>
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="6" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>53</v>
+        <v>332</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="G129" s="8" t="s">
         <v>333</v>
       </c>
+      <c r="E129" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>335</v>
+      </c>
       <c r="H129" s="6" t="s">
-        <v>36</v>
+        <v>323</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>253</v>
+        <v>336</v>
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="6" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>53</v>
+        <v>332</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D130" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="E130" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="G130" s="8" t="s">
-        <v>333</v>
+      <c r="F130" s="6" t="s">
+        <v>335</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>36</v>
+        <v>323</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>253</v>
+        <v>336</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="6" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>53</v>
+        <v>332</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D131" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F131" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="G131" s="8" t="s">
-        <v>333</v>
-      </c>
       <c r="H131" s="6" t="s">
-        <v>36</v>
+        <v>323</v>
       </c>
       <c r="I131" s="6" t="s">
-        <v>253</v>
+        <v>336</v>
       </c>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="6" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>53</v>
+        <v>332</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D132" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F132" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="H132" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="I132" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="G132" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I132" s="6" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="6" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>53</v>
@@ -5177,21 +5207,21 @@
         <v>13</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="G133" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
+      </c>
+      <c r="G133" s="8" t="s">
+        <v>341</v>
       </c>
       <c r="H133" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="I133" s="7" t="s">
-        <v>341</v>
+        <v>36</v>
+      </c>
+      <c r="I133" s="6" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="6" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>53</v>
@@ -5202,19 +5232,19 @@
       <c r="D134" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="G134" s="7" t="s">
-        <v>343</v>
+      <c r="G134" s="8" t="s">
+        <v>341</v>
       </c>
       <c r="H134" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="6" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>53</v>
@@ -5223,21 +5253,21 @@
         <v>23</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="G135" s="7" t="s">
         <v>343</v>
       </c>
+      <c r="G135" s="8" t="s">
+        <v>341</v>
+      </c>
       <c r="H135" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="6" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>53</v>
@@ -5246,21 +5276,21 @@
         <v>28</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="G136" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
+      </c>
+      <c r="G136" s="8" t="s">
+        <v>341</v>
       </c>
       <c r="H136" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I136" s="6" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>53</v>
@@ -5269,24 +5299,21 @@
         <v>13</v>
       </c>
       <c r="D137" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="G137" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="E137" s="6" t="s">
+      <c r="H137" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="F137" s="6" t="s">
+      <c r="I137" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="H137" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I137" s="6" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>53</v>
@@ -5297,22 +5324,19 @@
       <c r="D138" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="E138" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="F138" s="6" t="s">
-        <v>349</v>
+      <c r="G138" s="7" t="s">
+        <v>351</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>315</v>
+        <v>261</v>
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>53</v>
@@ -5321,24 +5345,21 @@
         <v>23</v>
       </c>
       <c r="D139" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="G139" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="E139" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="F139" s="6" t="s">
-        <v>349</v>
-      </c>
       <c r="H139" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>315</v>
+        <v>261</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>53</v>
@@ -5347,25 +5368,134 @@
         <v>28</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="E140" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="F140" s="6" t="s">
-        <v>349</v>
+        <v>353</v>
+      </c>
+      <c r="G140" s="7" t="s">
+        <v>351</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
+        <v>261</v>
+      </c>
+    </row>
+    <row r="141" ht="15.75" customHeight="1">
+      <c r="A141" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="F141" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="G141" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="H141" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I141" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="142" ht="15.75" customHeight="1">
+      <c r="A142" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="F142" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="G142" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="H142" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I142" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="143" ht="15.75" customHeight="1">
+      <c r="A143" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="F143" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="H143" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I143" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="144" ht="15.75" customHeight="1">
+      <c r="A144" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="E144" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="F144" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="G144" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="H144" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I144" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
     <row r="145" ht="15.75" customHeight="1"/>
     <row r="146" ht="15.75" customHeight="1"/>
     <row r="147" ht="15.75" customHeight="1"/>
@@ -6314,6 +6444,10 @@
     <row r="1090" ht="15.75" customHeight="1"/>
     <row r="1091" ht="15.75" customHeight="1"/>
     <row r="1092" ht="15.75" customHeight="1"/>
+    <row r="1093" ht="15.75" customHeight="1"/>
+    <row r="1094" ht="15.75" customHeight="1"/>
+    <row r="1095" ht="15.75" customHeight="1"/>
+    <row r="1096" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" location="/home" ref="G2"/>
@@ -6343,11 +6477,11 @@
     <hyperlink r:id="rId25" ref="G27"/>
     <hyperlink r:id="rId26" ref="G28"/>
     <hyperlink r:id="rId27" ref="G29"/>
-    <hyperlink r:id="rId28" location="/home" ref="G30"/>
-    <hyperlink r:id="rId29" ref="G34"/>
-    <hyperlink r:id="rId30" ref="G35"/>
-    <hyperlink r:id="rId31" ref="G36"/>
-    <hyperlink r:id="rId32" ref="G37"/>
+    <hyperlink r:id="rId28" ref="G30"/>
+    <hyperlink r:id="rId29" ref="G31"/>
+    <hyperlink r:id="rId30" ref="G32"/>
+    <hyperlink r:id="rId31" ref="G33"/>
+    <hyperlink r:id="rId32" location="/home" ref="G34"/>
     <hyperlink r:id="rId33" ref="G38"/>
     <hyperlink r:id="rId34" ref="G39"/>
     <hyperlink r:id="rId35" ref="G40"/>
@@ -6357,21 +6491,21 @@
     <hyperlink r:id="rId39" ref="G44"/>
     <hyperlink r:id="rId40" ref="G45"/>
     <hyperlink r:id="rId41" ref="G46"/>
-    <hyperlink r:id="rId42" ref="I46"/>
-    <hyperlink r:id="rId43" ref="G47"/>
-    <hyperlink r:id="rId44" ref="G48"/>
-    <hyperlink r:id="rId45" ref="G49"/>
-    <hyperlink r:id="rId46" ref="G50"/>
-    <hyperlink r:id="rId47" ref="G52"/>
-    <hyperlink r:id="rId48" ref="G53"/>
-    <hyperlink r:id="rId49" ref="G54"/>
-    <hyperlink r:id="rId50" ref="G55"/>
+    <hyperlink r:id="rId42" ref="G47"/>
+    <hyperlink r:id="rId43" ref="G48"/>
+    <hyperlink r:id="rId44" ref="G49"/>
+    <hyperlink r:id="rId45" ref="G50"/>
+    <hyperlink r:id="rId46" ref="I50"/>
+    <hyperlink r:id="rId47" ref="G51"/>
+    <hyperlink r:id="rId48" ref="G52"/>
+    <hyperlink r:id="rId49" ref="G53"/>
+    <hyperlink r:id="rId50" ref="G54"/>
     <hyperlink r:id="rId51" ref="G56"/>
-    <hyperlink r:id="rId52" location="/home" ref="G57"/>
+    <hyperlink r:id="rId52" ref="G57"/>
     <hyperlink r:id="rId53" ref="G58"/>
     <hyperlink r:id="rId54" ref="G59"/>
     <hyperlink r:id="rId55" ref="G60"/>
-    <hyperlink r:id="rId56" ref="G61"/>
+    <hyperlink r:id="rId56" location="/home" ref="G61"/>
     <hyperlink r:id="rId57" ref="G62"/>
     <hyperlink r:id="rId58" ref="G63"/>
     <hyperlink r:id="rId59" ref="G64"/>
@@ -6407,11 +6541,11 @@
     <hyperlink r:id="rId89" ref="G94"/>
     <hyperlink r:id="rId90" ref="G95"/>
     <hyperlink r:id="rId91" ref="G96"/>
-    <hyperlink r:id="rId92" ref="G99"/>
-    <hyperlink r:id="rId93" ref="G101"/>
-    <hyperlink r:id="rId94" ref="G102"/>
-    <hyperlink r:id="rId95" ref="G103"/>
-    <hyperlink r:id="rId96" ref="G104"/>
+    <hyperlink r:id="rId92" ref="G97"/>
+    <hyperlink r:id="rId93" ref="G98"/>
+    <hyperlink r:id="rId94" ref="G99"/>
+    <hyperlink r:id="rId95" ref="G100"/>
+    <hyperlink r:id="rId96" ref="G103"/>
     <hyperlink r:id="rId97" ref="G105"/>
     <hyperlink r:id="rId98" ref="G106"/>
     <hyperlink r:id="rId99" ref="G107"/>
@@ -6420,23 +6554,31 @@
     <hyperlink r:id="rId102" ref="G110"/>
     <hyperlink r:id="rId103" ref="G111"/>
     <hyperlink r:id="rId104" ref="G112"/>
-    <hyperlink r:id="rId105" ref="G117"/>
-    <hyperlink r:id="rId106" ref="G118"/>
-    <hyperlink r:id="rId107" ref="G119"/>
-    <hyperlink r:id="rId108" ref="G120"/>
-    <hyperlink r:id="rId109" ref="G129"/>
-    <hyperlink r:id="rId110" ref="G130"/>
-    <hyperlink r:id="rId111" ref="G131"/>
-    <hyperlink r:id="rId112" ref="G132"/>
+    <hyperlink r:id="rId105" ref="G113"/>
+    <hyperlink r:id="rId106" ref="G114"/>
+    <hyperlink r:id="rId107" ref="G115"/>
+    <hyperlink r:id="rId108" ref="G116"/>
+    <hyperlink r:id="rId109" ref="G121"/>
+    <hyperlink r:id="rId110" ref="G122"/>
+    <hyperlink r:id="rId111" ref="G123"/>
+    <hyperlink r:id="rId112" ref="G124"/>
     <hyperlink r:id="rId113" ref="G133"/>
-    <hyperlink r:id="rId114" ref="I133"/>
-    <hyperlink r:id="rId115" ref="G134"/>
-    <hyperlink r:id="rId116" ref="G135"/>
-    <hyperlink r:id="rId117" ref="G136"/>
+    <hyperlink r:id="rId114" ref="G134"/>
+    <hyperlink r:id="rId115" ref="G135"/>
+    <hyperlink r:id="rId116" ref="G136"/>
+    <hyperlink r:id="rId117" ref="G137"/>
+    <hyperlink r:id="rId118" ref="I137"/>
+    <hyperlink r:id="rId119" ref="G138"/>
+    <hyperlink r:id="rId120" ref="G139"/>
+    <hyperlink r:id="rId121" ref="G140"/>
+    <hyperlink r:id="rId122" ref="G141"/>
+    <hyperlink r:id="rId123" ref="G142"/>
+    <hyperlink r:id="rId124" ref="G143"/>
+    <hyperlink r:id="rId125" ref="G144"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId118"/>
+  <drawing r:id="rId126"/>
 </worksheet>
 </file>
--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="iDawz/RLxtopVSfNMejEDj4vPqPRh3haGFonxe3AFck="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="RdiF6kLVNzkAeygFopr3SJlzlqP0yrbxd3G8YVRnbT0="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="408">
   <si>
     <t>County</t>
   </si>
@@ -720,6 +720,18 @@
     <t>City of Hialeah Fire Department</t>
   </si>
   <si>
+    <t>North Bay Village</t>
+  </si>
+  <si>
+    <t>City of North Bay Village Building Department</t>
+  </si>
+  <si>
+    <t>https://northbayvillage-fl.gov/public-records/</t>
+  </si>
+  <si>
+    <t>City of North Bay Village Planning Department</t>
+  </si>
+  <si>
     <t>Broward</t>
   </si>
   <si>
@@ -958,6 +970,30 @@
   </si>
   <si>
     <t>City of Plantation Fire Department</t>
+  </si>
+  <si>
+    <t>Lauderhill</t>
+  </si>
+  <si>
+    <t>City of Lauderhill Building Department</t>
+  </si>
+  <si>
+    <t>City Clerk Public Records Custodian</t>
+  </si>
+  <si>
+    <t>aanderson@lauderhill-fl.gov</t>
+  </si>
+  <si>
+    <t>https://lauderhillfl.govqa.us/WEBAPP/_rs/(S(kseb3g0wr5imy23fd5dabij3))/SupportHome.aspx?sSessionID=</t>
+  </si>
+  <si>
+    <t>Use portal or Email</t>
+  </si>
+  <si>
+    <t>City of Lauderhill Planning Department</t>
+  </si>
+  <si>
+    <t>City of Lauderhill Fire Department</t>
   </si>
   <si>
     <t>Collier</t>
@@ -1143,6 +1179,108 @@
   </si>
   <si>
     <t>Indian River County Fire Department</t>
+  </si>
+  <si>
+    <t>Brevard</t>
+  </si>
+  <si>
+    <t>Cocoa Beach</t>
+  </si>
+  <si>
+    <t>Cocoa Beach Building Department</t>
+  </si>
+  <si>
+    <t>https://cityofcocoabeach.nextrequest.com/</t>
+  </si>
+  <si>
+    <t>Cocoa Beach Planning Department</t>
+  </si>
+  <si>
+    <t>Cocoa Beach Environmental Department</t>
+  </si>
+  <si>
+    <t>Cocoa Beach Fire Department</t>
+  </si>
+  <si>
+    <t>Marion</t>
+  </si>
+  <si>
+    <t>Ocala</t>
+  </si>
+  <si>
+    <t>Ocala Building Department</t>
+  </si>
+  <si>
+    <t>https://ocalafl.justfoia.com/publicportal/home/newrequest</t>
+  </si>
+  <si>
+    <t>Ocala Planning Department</t>
+  </si>
+  <si>
+    <t>Ocala Environmental Department</t>
+  </si>
+  <si>
+    <t>Ocala Fire Department</t>
+  </si>
+  <si>
+    <t>Volusia</t>
+  </si>
+  <si>
+    <t>Holly Hill</t>
+  </si>
+  <si>
+    <t>Holly Hill Building Department</t>
+  </si>
+  <si>
+    <t>https://cityofhollyhillfl.nextrequest.com/requests/new</t>
+  </si>
+  <si>
+    <t>Holly Hill Planning Department</t>
+  </si>
+  <si>
+    <t>Holly Hill Environmental Department</t>
+  </si>
+  <si>
+    <t>Holly Hill Fire Department</t>
+  </si>
+  <si>
+    <t>Pinellas</t>
+  </si>
+  <si>
+    <t>Safety Harbor</t>
+  </si>
+  <si>
+    <t>Safety Harbor Building Department</t>
+  </si>
+  <si>
+    <t>https://cityofsafetyharbor.govqa.us/WEBAPP/_rs/(S(551syhymtnv4xy34oxmnaqxh))/SupportHome.aspx?sSessionID=3514539110:42583GCUFBVOVVNFTFFO[QMHCJFJV&amp;lp=2</t>
+  </si>
+  <si>
+    <t>Safety Harbor Planning Department</t>
+  </si>
+  <si>
+    <t>Safety Harbor Environmental Department</t>
+  </si>
+  <si>
+    <t>Safety Harbor Fire Department</t>
+  </si>
+  <si>
+    <t>Saint Lucie</t>
+  </si>
+  <si>
+    <t>Saint Lucie County Building Department</t>
+  </si>
+  <si>
+    <t>https://stluciecounty.formstack.com/forms/public_records_request</t>
+  </si>
+  <si>
+    <t>Saint Lucie County Planning Department</t>
+  </si>
+  <si>
+    <t>Saint Lucie County Environmental Department</t>
+  </si>
+  <si>
+    <t>Saint Lucie County Fire Department</t>
   </si>
 </sst>
 </file>
@@ -3694,10 +3832,10 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>13</v>
@@ -3714,23 +3852,23 @@
         <v>36</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>228</v>
+        <v>75</v>
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="9"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
@@ -3741,125 +3879,132 @@
         <v>36</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="9"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
       <c r="G75" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I75" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>233</v>
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="9"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="5" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="9"/>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="B77" s="6" t="s">
+      <c r="A77" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I77" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="J77" s="2"/>
+      <c r="K77" s="9"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="J78" s="2"/>
+      <c r="K78" s="9"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D77" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="G77" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="H77" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="I77" s="6" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D78" s="6" t="s">
+      <c r="D79" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="G78" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="I78" s="6" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="F79" s="6"/>
       <c r="G79" s="7" t="s">
         <v>243</v>
       </c>
@@ -3872,112 +4017,112 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>246</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B81" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="F81" s="6"/>
+      <c r="G81" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="C81" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D81" s="6" t="s">
+      <c r="H81" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="G81" s="7" t="s">
+      <c r="I81" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="H81" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I81" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
+    </row>
+    <row r="82">
       <c r="A82" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>250</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>36</v>
+        <v>244</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>75</v>
+        <v>245</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="F83" s="6"/>
+        <v>252</v>
+      </c>
       <c r="G83" s="7" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>244</v>
+        <v>36</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>245</v>
+        <v>75</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>36</v>
@@ -3988,42 +4133,43 @@
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>253</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="F85" s="6"/>
       <c r="G85" s="7" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>36</v>
+        <v>248</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>75</v>
+        <v>249</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>255</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>36</v>
@@ -4034,43 +4180,42 @@
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="F87" s="6"/>
+        <v>257</v>
+      </c>
       <c r="G87" s="7" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>244</v>
+        <v>36</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>245</v>
+        <v>75</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="H88" s="6" t="s">
         <v>36</v>
@@ -4081,275 +4226,275 @@
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="6" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>259</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="F89" s="6"/>
       <c r="G89" s="7" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>36</v>
+        <v>248</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="6" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="B90" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="G90" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="C90" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>260</v>
-      </c>
       <c r="H90" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>261</v>
+        <v>75</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="6" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="F91" s="6"/>
+        <v>263</v>
+      </c>
       <c r="G91" s="7" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>244</v>
+        <v>36</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="6" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>265</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="F93" s="6"/>
       <c r="G93" s="7" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>36</v>
+        <v>248</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="6" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>267</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="F95" s="6"/>
+        <v>269</v>
+      </c>
       <c r="G95" s="7" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>244</v>
+        <v>36</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H96" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>270</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="F97" s="6"/>
       <c r="G97" s="7" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>36</v>
+        <v>248</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>75</v>
+        <v>249</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>272</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H98" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>75</v>
+        <v>265</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="F99" s="6"/>
+        <v>274</v>
+      </c>
       <c r="G99" s="7" t="s">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>244</v>
+        <v>36</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>245</v>
+        <v>75</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="H100" s="6" t="s">
         <v>36</v>
@@ -4360,88 +4505,87 @@
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="G101" s="16"/>
+        <v>235</v>
+      </c>
+      <c r="F101" s="6"/>
+      <c r="G101" s="7" t="s">
+        <v>247</v>
+      </c>
       <c r="H101" s="6" t="s">
-        <v>5</v>
+        <v>248</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="F102" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="G102" s="16"/>
+        <v>277</v>
+      </c>
+      <c r="G102" s="7" t="s">
+        <v>275</v>
+      </c>
       <c r="H102" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>277</v>
+        <v>75</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="F103" s="6"/>
-      <c r="G103" s="7" t="s">
-        <v>243</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="G103" s="16"/>
       <c r="H103" s="6" t="s">
-        <v>244</v>
+        <v>5</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>245</v>
+        <v>281</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>280</v>
@@ -4456,291 +4600,281 @@
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="F105" s="6" t="s">
-        <v>284</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="F105" s="6"/>
       <c r="G105" s="7" t="s">
-        <v>285</v>
+        <v>247</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>36</v>
+        <v>248</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>286</v>
+        <v>249</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="G106" s="7" t="s">
+      <c r="G106" s="16"/>
+      <c r="H106" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I106" s="6" t="s">
         <v>285</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I106" s="6" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D107" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F107" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="F107" s="6" t="s">
-        <v>284</v>
-      </c>
       <c r="G107" s="7" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="H107" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D108" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="G108" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="F108" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="G108" s="7" t="s">
-        <v>285</v>
-      </c>
       <c r="H108" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B109" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="G109" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="H109" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I109" s="6" t="s">
         <v>290</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D109" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="E109" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F109" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="G109" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="H109" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I109" s="6" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B110" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="G110" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I110" s="6" t="s">
         <v>290</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="E110" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F110" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="G110" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I110" s="6" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E111" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="H112" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E113" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="H113" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="H114" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>303</v>
@@ -4749,298 +4883,318 @@
         <v>15</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="H115" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G116" s="7" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="H116" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="G117" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="B117" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C117" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D117" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="E117" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="F117" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="G117" s="16"/>
       <c r="H117" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>5</v>
+        <v>298</v>
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="G118" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="B118" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C118" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D118" s="6" t="s">
+      <c r="H118" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I118" s="6" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="A119" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B119" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="E118" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="F118" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="G118" s="16"/>
-      <c r="H118" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I118" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="119" ht="16.5" customHeight="1">
-      <c r="A119" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="C119" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="E119" s="6"/>
+      <c r="E119" s="6" t="s">
+        <v>311</v>
+      </c>
       <c r="F119" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="G119" s="16"/>
+        <v>312</v>
+      </c>
+      <c r="G119" s="7" t="s">
+        <v>313</v>
+      </c>
       <c r="H119" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>5</v>
+        <v>314</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="6" t="s">
-        <v>305</v>
+        <v>229</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>53</v>
+        <v>309</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D120" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="F120" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="E120" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="F120" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="G120" s="16"/>
+      <c r="G120" s="7" t="s">
+        <v>313</v>
+      </c>
       <c r="H120" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>5</v>
+        <v>314</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="6" t="s">
-        <v>305</v>
+        <v>229</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D121" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="E121" s="6"/>
+      <c r="F121" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="G121" s="16"/>
+      <c r="H121" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I121" s="6" t="s">
         <v>314</v>
-      </c>
-      <c r="G121" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="H121" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I121" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="J121" s="6" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="6" t="s">
-        <v>305</v>
+        <v>229</v>
       </c>
       <c r="B122" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="G122" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="C122" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D122" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="G122" s="7" t="s">
-        <v>315</v>
-      </c>
       <c r="H122" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="J122" s="6" t="s">
-        <v>19</v>
+        <v>314</v>
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="6" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>313</v>
+        <v>53</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="G123" s="7" t="s">
-        <v>315</v>
-      </c>
+      <c r="E123" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="G123" s="16"/>
       <c r="H123" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="J123" s="6" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="6" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>313</v>
+        <v>53</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D124" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E124" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="G124" s="7" t="s">
-        <v>315</v>
-      </c>
+      <c r="F124" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="G124" s="16"/>
       <c r="H124" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="J124" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="125" ht="15.75" customHeight="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" ht="16.5" customHeight="1">
       <c r="A125" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>321</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="E125" s="6"/>
       <c r="F125" s="6" t="s">
-        <v>322</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="G125" s="16"/>
       <c r="H125" s="6" t="s">
-        <v>323</v>
+        <v>5</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>324</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>319</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>322</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="G126" s="16"/>
       <c r="H126" s="6" t="s">
-        <v>323</v>
+        <v>5</v>
       </c>
       <c r="I126" s="6" t="s">
         <v>5</v>
@@ -5048,123 +5202,126 @@
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>53</v>
+        <v>325</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="F127" s="6" t="s">
+      <c r="G127" s="7" t="s">
         <v>327</v>
       </c>
       <c r="H127" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I127" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="I127" s="6" t="s">
-        <v>329</v>
+      <c r="J127" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>53</v>
+        <v>325</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="F128" s="6" t="s">
-        <v>322</v>
+        <v>329</v>
+      </c>
+      <c r="G128" s="7" t="s">
+        <v>327</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>323</v>
+        <v>36</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>112</v>
+        <v>328</v>
+      </c>
+      <c r="J128" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="6" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="E129" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="F129" s="6" t="s">
-        <v>335</v>
+        <v>330</v>
+      </c>
+      <c r="G129" s="7" t="s">
+        <v>327</v>
       </c>
       <c r="H129" s="6" t="s">
-        <v>323</v>
+        <v>36</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>336</v>
+        <v>328</v>
+      </c>
+      <c r="J129" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D130" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="B130" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="C130" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D130" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="E130" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="F130" s="6" t="s">
-        <v>335</v>
+      <c r="G130" s="7" t="s">
+        <v>327</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>323</v>
+        <v>36</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>336</v>
+        <v>328</v>
+      </c>
+      <c r="J130" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>332</v>
+        <v>53</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="E131" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="F131" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="F131" s="6" t="s">
+      <c r="H131" s="6" t="s">
         <v>335</v>
-      </c>
-      <c r="H131" s="6" t="s">
-        <v>323</v>
       </c>
       <c r="I131" s="6" t="s">
         <v>336</v>
@@ -5172,356 +5329,937 @@
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>332</v>
+        <v>53</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="E132" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="F132" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="F132" s="6" t="s">
+      <c r="H132" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="H132" s="6" t="s">
-        <v>323</v>
-      </c>
       <c r="I132" s="6" t="s">
-        <v>336</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D133" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="F133" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="H133" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="G133" s="8" t="s">
+      <c r="I133" s="6" t="s">
         <v>341</v>
-      </c>
-      <c r="H133" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I133" s="6" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="G134" s="8" t="s">
-        <v>341</v>
+      <c r="F134" s="6" t="s">
+        <v>334</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>36</v>
+        <v>335</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>261</v>
+        <v>112</v>
       </c>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="6" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>53</v>
+        <v>344</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="G135" s="8" t="s">
-        <v>341</v>
+        <v>345</v>
+      </c>
+      <c r="E135" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="F135" s="6" t="s">
+        <v>347</v>
       </c>
       <c r="H135" s="6" t="s">
-        <v>36</v>
+        <v>335</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>261</v>
+        <v>348</v>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="6" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>53</v>
+        <v>344</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="G136" s="8" t="s">
-        <v>341</v>
+        <v>349</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="F136" s="6" t="s">
+        <v>347</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>36</v>
+        <v>335</v>
       </c>
       <c r="I136" s="6" t="s">
-        <v>261</v>
+        <v>348</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>53</v>
+        <v>344</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D137" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E137" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="G137" s="7" t="s">
+      <c r="F137" s="6" t="s">
         <v>347</v>
       </c>
       <c r="H137" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="I137" s="6" t="s">
         <v>348</v>
-      </c>
-      <c r="I137" s="7" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>53</v>
+        <v>344</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="G138" s="7" t="s">
         <v>351</v>
       </c>
+      <c r="E138" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="F138" s="6" t="s">
+        <v>347</v>
+      </c>
       <c r="H138" s="6" t="s">
-        <v>36</v>
+        <v>335</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>261</v>
+        <v>348</v>
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="G139" s="7" t="s">
-        <v>351</v>
+      <c r="G139" s="8" t="s">
+        <v>353</v>
       </c>
       <c r="H139" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D140" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="G140" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="G140" s="7" t="s">
-        <v>351</v>
-      </c>
       <c r="H140" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="6" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="E141" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="F141" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="G141" s="7" t="s">
-        <v>358</v>
+      <c r="G141" s="8" t="s">
+        <v>353</v>
       </c>
       <c r="H141" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I141" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="6" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="E142" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="F142" s="6" t="s">
-        <v>357</v>
-      </c>
       <c r="G142" s="8" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="H142" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="6" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D143" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="G143" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="H143" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="E143" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="F143" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="G143" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="H143" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I143" s="6" t="s">
-        <v>261</v>
+      <c r="I143" s="7" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="6" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C144" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="G144" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="H144" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I144" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="145" ht="15.75" customHeight="1">
+      <c r="A145" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="G145" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="H145" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I145" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="146" ht="15.75" customHeight="1">
+      <c r="A146" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C146" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D144" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="E144" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="F144" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="G144" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I144" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
+      <c r="D146" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="G146" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="H146" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I146" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="147" ht="15.75" customHeight="1">
+      <c r="A147" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="F147" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="G147" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="H147" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I147" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="148" ht="15.75" customHeight="1">
+      <c r="A148" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="F148" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="H148" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I148" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="149" ht="15.75" customHeight="1">
+      <c r="A149" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="F149" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="H149" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I149" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="150" ht="15.75" customHeight="1">
+      <c r="A150" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="F150" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="H150" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I150" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="151" ht="15.75" customHeight="1">
+      <c r="A151" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="H151" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I151" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="152" ht="15.75" customHeight="1">
+      <c r="A152" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="H152" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I152" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="153" ht="15.75" customHeight="1">
+      <c r="A153" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D153" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="H153" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I153" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="154" ht="15.75" customHeight="1">
+      <c r="A154" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D154" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="H154" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I154" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="155" ht="15.75" customHeight="1">
+      <c r="A155" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="G155" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="H155" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I155" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="156" ht="15.75" customHeight="1">
+      <c r="A156" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="G156" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="H156" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I156" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="157" ht="15.75" customHeight="1">
+      <c r="A157" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="G157" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="H157" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I157" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="158" ht="15.75" customHeight="1">
+      <c r="A158" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="G158" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="H158" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I158" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="159" ht="15.75" customHeight="1">
+      <c r="A159" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="H159" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I159" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="160" ht="15.75" customHeight="1">
+      <c r="A160" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="H160" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I160" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="161" ht="15.75" customHeight="1">
+      <c r="A161" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="H161" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I161" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="162" ht="15.75" customHeight="1">
+      <c r="A162" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="H162" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I162" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="163" ht="15.75" customHeight="1">
+      <c r="A163" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="G163" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="H163" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I163" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="164" ht="15.75" customHeight="1">
+      <c r="A164" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="G164" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="H164" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I164" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="165" ht="15.75" customHeight="1">
+      <c r="A165" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D165" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="G165" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="H165" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I165" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="166" ht="15.75" customHeight="1">
+      <c r="A166" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="G166" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="H166" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I166" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="167" ht="15.75" customHeight="1">
+      <c r="A167" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="G167" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="H167" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I167" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="168" ht="15.75" customHeight="1">
+      <c r="A168" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D168" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="G168" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="H168" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I168" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="169" ht="15.75" customHeight="1">
+      <c r="A169" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="G169" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="H169" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I169" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="170" ht="15.75" customHeight="1">
+      <c r="A170" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D170" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="G170" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="H170" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I170" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
     <row r="171" ht="15.75" customHeight="1"/>
     <row r="172" ht="15.75" customHeight="1"/>
     <row r="173" ht="15.75" customHeight="1"/>
@@ -6448,6 +7186,12 @@
     <row r="1094" ht="15.75" customHeight="1"/>
     <row r="1095" ht="15.75" customHeight="1"/>
     <row r="1096" ht="15.75" customHeight="1"/>
+    <row r="1097" ht="15.75" customHeight="1"/>
+    <row r="1098" ht="15.75" customHeight="1"/>
+    <row r="1099" ht="15.75" customHeight="1"/>
+    <row r="1100" ht="15.75" customHeight="1"/>
+    <row r="1101" ht="15.75" customHeight="1"/>
+    <row r="1102" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" location="/home" ref="G2"/>
@@ -6545,9 +7289,9 @@
     <hyperlink r:id="rId93" ref="G98"/>
     <hyperlink r:id="rId94" ref="G99"/>
     <hyperlink r:id="rId95" ref="G100"/>
-    <hyperlink r:id="rId96" ref="G103"/>
-    <hyperlink r:id="rId97" ref="G105"/>
-    <hyperlink r:id="rId98" ref="G106"/>
+    <hyperlink r:id="rId96" ref="G101"/>
+    <hyperlink r:id="rId97" ref="G102"/>
+    <hyperlink r:id="rId98" ref="G105"/>
     <hyperlink r:id="rId99" ref="G107"/>
     <hyperlink r:id="rId100" ref="G108"/>
     <hyperlink r:id="rId101" ref="G109"/>
@@ -6558,27 +7302,53 @@
     <hyperlink r:id="rId106" ref="G114"/>
     <hyperlink r:id="rId107" ref="G115"/>
     <hyperlink r:id="rId108" ref="G116"/>
-    <hyperlink r:id="rId109" ref="G121"/>
-    <hyperlink r:id="rId110" ref="G122"/>
-    <hyperlink r:id="rId111" ref="G123"/>
-    <hyperlink r:id="rId112" ref="G124"/>
-    <hyperlink r:id="rId113" ref="G133"/>
-    <hyperlink r:id="rId114" ref="G134"/>
-    <hyperlink r:id="rId115" ref="G135"/>
-    <hyperlink r:id="rId116" ref="G136"/>
-    <hyperlink r:id="rId117" ref="G137"/>
-    <hyperlink r:id="rId118" ref="I137"/>
-    <hyperlink r:id="rId119" ref="G138"/>
-    <hyperlink r:id="rId120" ref="G139"/>
-    <hyperlink r:id="rId121" ref="G140"/>
-    <hyperlink r:id="rId122" ref="G141"/>
-    <hyperlink r:id="rId123" ref="G142"/>
-    <hyperlink r:id="rId124" ref="G143"/>
+    <hyperlink r:id="rId109" ref="G117"/>
+    <hyperlink r:id="rId110" ref="G118"/>
+    <hyperlink r:id="rId111" ref="G119"/>
+    <hyperlink r:id="rId112" ref="G120"/>
+    <hyperlink r:id="rId113" ref="F121"/>
+    <hyperlink r:id="rId114" ref="G122"/>
+    <hyperlink r:id="rId115" ref="G127"/>
+    <hyperlink r:id="rId116" ref="G128"/>
+    <hyperlink r:id="rId117" ref="G129"/>
+    <hyperlink r:id="rId118" ref="G130"/>
+    <hyperlink r:id="rId119" ref="G139"/>
+    <hyperlink r:id="rId120" ref="G140"/>
+    <hyperlink r:id="rId121" ref="G141"/>
+    <hyperlink r:id="rId122" ref="G142"/>
+    <hyperlink r:id="rId123" ref="G143"/>
+    <hyperlink r:id="rId124" ref="I143"/>
     <hyperlink r:id="rId125" ref="G144"/>
+    <hyperlink r:id="rId126" ref="G145"/>
+    <hyperlink r:id="rId127" ref="G146"/>
+    <hyperlink r:id="rId128" ref="G147"/>
+    <hyperlink r:id="rId129" ref="G148"/>
+    <hyperlink r:id="rId130" ref="G149"/>
+    <hyperlink r:id="rId131" ref="G150"/>
+    <hyperlink r:id="rId132" ref="G151"/>
+    <hyperlink r:id="rId133" ref="G152"/>
+    <hyperlink r:id="rId134" ref="G153"/>
+    <hyperlink r:id="rId135" ref="G154"/>
+    <hyperlink r:id="rId136" ref="G155"/>
+    <hyperlink r:id="rId137" ref="G156"/>
+    <hyperlink r:id="rId138" ref="G157"/>
+    <hyperlink r:id="rId139" ref="G158"/>
+    <hyperlink r:id="rId140" ref="G159"/>
+    <hyperlink r:id="rId141" ref="G160"/>
+    <hyperlink r:id="rId142" ref="G161"/>
+    <hyperlink r:id="rId143" ref="G162"/>
+    <hyperlink r:id="rId144" ref="G163"/>
+    <hyperlink r:id="rId145" ref="G164"/>
+    <hyperlink r:id="rId146" ref="G165"/>
+    <hyperlink r:id="rId147" ref="G166"/>
+    <hyperlink r:id="rId148" ref="G167"/>
+    <hyperlink r:id="rId149" ref="G168"/>
+    <hyperlink r:id="rId150" ref="G169"/>
+    <hyperlink r:id="rId151" ref="G170"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId126"/>
+  <drawing r:id="rId152"/>
 </worksheet>
 </file>
--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="410">
   <si>
     <t>County</t>
   </si>
@@ -1281,6 +1281,12 @@
   </si>
   <si>
     <t>Saint Lucie County Fire Department</t>
+  </si>
+  <si>
+    <t>kmachado@slcfd.org</t>
+  </si>
+  <si>
+    <t>Use Email</t>
   </si>
 </sst>
 </file>
@@ -6250,14 +6256,13 @@
       <c r="D170" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="G170" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="H170" s="6" t="s">
-        <v>36</v>
-      </c>
+      <c r="F170" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="G170" s="16"/>
+      <c r="H170" s="6"/>
       <c r="I170" s="6" t="s">
-        <v>265</v>
+        <v>409</v>
       </c>
     </row>
     <row r="171" ht="15.75" customHeight="1"/>
@@ -7344,11 +7349,10 @@
     <hyperlink r:id="rId148" ref="G167"/>
     <hyperlink r:id="rId149" ref="G168"/>
     <hyperlink r:id="rId150" ref="G169"/>
-    <hyperlink r:id="rId151" ref="G170"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId152"/>
+  <drawing r:id="rId151"/>
 </worksheet>
 </file>
--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="RdiF6kLVNzkAeygFopr3SJlzlqP0yrbxd3G8YVRnbT0="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="hTdZ7I96eXHJnVfcwaMWkA7VgWkCNcK3pFzfESiTqIw="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="418">
   <si>
     <t>County</t>
   </si>
@@ -290,6 +290,30 @@
   </si>
   <si>
     <t>Portal -&gt; General Request</t>
+  </si>
+  <si>
+    <t>Mangonia Park</t>
+  </si>
+  <si>
+    <t>Town of Mangonia Park Building Department</t>
+  </si>
+  <si>
+    <t>https://www.tompfl.com/th/page/public-records-request</t>
+  </si>
+  <si>
+    <t>Click Email</t>
+  </si>
+  <si>
+    <t>Email Clerk</t>
+  </si>
+  <si>
+    <t>Town of Mangonia Park Planning Department</t>
+  </si>
+  <si>
+    <t>Town of Mangonia Park Environmental Department</t>
+  </si>
+  <si>
+    <t>Town of Mangonia Park Fire Department</t>
   </si>
   <si>
     <t>Lee</t>
@@ -2492,590 +2516,570 @@
       <c r="K29" s="9"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="J30" s="2"/>
+      <c r="K30" s="9"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="J31" s="2"/>
+      <c r="K31" s="9"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="J32" s="2"/>
+      <c r="K32" s="9"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="J33" s="2"/>
+      <c r="K33" s="9"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J30" s="2" t="s">
+      <c r="D34" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J34" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="K34" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B31" s="2" t="s">
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="D35" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J31" s="2" t="s">
+      <c r="B36" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J37" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K31" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="J34" s="2"/>
-      <c r="K34" s="9"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="G35" s="11"/>
-      <c r="H35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I35" s="3" t="s">
+      <c r="K37" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="J35" s="2"/>
-      <c r="K35" s="9"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D36" s="3" t="s">
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="G36" s="11"/>
-      <c r="H36" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="J36" s="2"/>
-      <c r="K36" s="9"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E37" s="2"/>
-      <c r="F37" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="G37" s="11"/>
-      <c r="H37" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="J37" s="2"/>
-      <c r="K37" s="9"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D38" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G38" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38" s="5" t="s">
+      <c r="H38" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K38" s="9" t="s">
-        <v>119</v>
-      </c>
+      <c r="J38" s="2"/>
+      <c r="K38" s="9"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="s">
-        <v>87</v>
+      <c r="A39" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D39" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G39" s="11"/>
+      <c r="H39" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K39" s="9" t="s">
-        <v>121</v>
-      </c>
+      <c r="J39" s="2"/>
+      <c r="K39" s="9"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="s">
-        <v>87</v>
+      <c r="A40" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>117</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G40" s="11"/>
       <c r="H40" s="3" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K40" s="9" t="s">
-        <v>123</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="J40" s="2"/>
+      <c r="K40" s="9"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="s">
-        <v>87</v>
+      <c r="A41" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>117</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G41" s="11"/>
       <c r="H41" s="3" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K41" s="9" t="s">
-        <v>125</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="J41" s="2"/>
+      <c r="K41" s="9"/>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="s">
-        <v>126</v>
+      <c r="A42" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J42" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J42" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="s">
-        <v>126</v>
+      <c r="A43" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E43" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K43" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="G43" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K43" s="9" t="s">
-        <v>133</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="s">
-        <v>126</v>
+      <c r="A44" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J44" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J44" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K44" s="9" t="s">
-        <v>38</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="s">
-        <v>126</v>
+      <c r="A45" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J45" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J45" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K46" s="9" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K47" s="9" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>19</v>
@@ -3086,792 +3090,812 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="2" t="s">
+      <c r="G50" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="H50" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K50" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I50" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="G51" s="5" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="J51" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J51" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K51" s="2" t="s">
-        <v>104</v>
+      <c r="K51" s="9" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>149</v>
+        <v>53</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="J52" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J52" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K52" s="2" t="s">
-        <v>104</v>
+      <c r="K52" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="G53" s="5" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="J53" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J53" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K53" s="2" t="s">
-        <v>104</v>
+      <c r="K53" s="9" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>155</v>
+        <v>53</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G54" s="13" t="s">
-        <v>164</v>
+        <v>146</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>166</v>
+        <v>150</v>
+      </c>
+      <c r="I54" s="12" t="s">
+        <v>151</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B55" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="C55" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D55" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="E55" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="F55" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="I55" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="J55" s="15" t="s">
+      <c r="A55" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="J55" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K55" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="L55" s="15"/>
-      <c r="M55" s="15"/>
-      <c r="N55" s="15"/>
-      <c r="O55" s="15"/>
-      <c r="P55" s="15"/>
-      <c r="Q55" s="15"/>
-      <c r="R55" s="15"/>
-      <c r="S55" s="15"/>
-      <c r="T55" s="15"/>
-      <c r="U55" s="15"/>
-      <c r="V55" s="15"/>
-      <c r="W55" s="15"/>
-      <c r="X55" s="15"/>
-      <c r="Y55" s="15"/>
-      <c r="Z55" s="15"/>
+      <c r="K55" s="2" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>13</v>
+        <v>157</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K56" s="9" t="s">
-        <v>38</v>
+      <c r="K56" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>171</v>
+        <v>145</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>177</v>
+        <v>13</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>175</v>
+        <v>166</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>167</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>36</v>
+        <v>168</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K57" s="9" t="s">
-        <v>38</v>
+      <c r="K57" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E58" s="3"/>
+        <v>145</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>165</v>
+      </c>
       <c r="F58" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>182</v>
+        <v>171</v>
+      </c>
+      <c r="G58" s="13" t="s">
+        <v>172</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="J58" s="2"/>
-      <c r="K58" s="9"/>
+        <v>173</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G59" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="J59" s="2"/>
-      <c r="K59" s="9"/>
+      <c r="A59" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="E59" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="F59" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="I59" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="J59" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="K59" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="L59" s="15"/>
+      <c r="M59" s="15"/>
+      <c r="N59" s="15"/>
+      <c r="O59" s="15"/>
+      <c r="P59" s="15"/>
+      <c r="Q59" s="15"/>
+      <c r="R59" s="15"/>
+      <c r="S59" s="15"/>
+      <c r="T59" s="15"/>
+      <c r="U59" s="15"/>
+      <c r="V59" s="15"/>
+      <c r="W59" s="15"/>
+      <c r="X59" s="15"/>
+      <c r="Y59" s="15"/>
+      <c r="Z59" s="15"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>28</v>
+      <c r="C60" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E60" s="3"/>
+        <v>180</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>181</v>
+      </c>
       <c r="F60" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>188</v>
+        <v>36</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="J60" s="2"/>
-      <c r="K60" s="9"/>
+        <v>184</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K60" s="9" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>13</v>
+        <v>179</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E61" s="3"/>
+        <v>185</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>181</v>
+      </c>
       <c r="F61" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>193</v>
+        <v>182</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>183</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>194</v>
+        <v>36</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="J61" s="2"/>
-      <c r="K61" s="9"/>
+        <v>186</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K61" s="9" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G62" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="5" t="s">
-        <v>197</v>
-      </c>
       <c r="H62" s="3" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="9"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="9"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>36</v>
+        <v>196</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="9"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>36</v>
+        <v>202</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="9"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E66" s="3"/>
-      <c r="F66" s="3" t="s">
-        <v>210</v>
-      </c>
+      <c r="F66" s="3"/>
       <c r="G66" s="5" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>212</v>
+        <v>36</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="9"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I67" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="9"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>36</v>
+        <v>213</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="9"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>36</v>
+        <v>213</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="9"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D70" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="H70" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="I70" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="9"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
+      <c r="F71" s="3" t="s">
+        <v>218</v>
+      </c>
       <c r="G71" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>36</v>
+        <v>220</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="9"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D72" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
       <c r="G72" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>222</v>
+        <v>36</v>
       </c>
       <c r="J72" s="2"/>
       <c r="K72" s="9"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>226</v>
       </c>
       <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
+      <c r="F73" s="3" t="s">
+        <v>224</v>
+      </c>
       <c r="G73" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="9"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>228</v>
@@ -3879,247 +3903,262 @@
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="9"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>229</v>
+        <v>145</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>53</v>
+        <v>227</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
       <c r="G75" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="9"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>229</v>
+        <v>145</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>53</v>
+        <v>227</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="9"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>229</v>
+        <v>145</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>53</v>
+        <v>233</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>237</v>
+        <v>75</v>
       </c>
       <c r="J77" s="2"/>
       <c r="K77" s="9"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>229</v>
+        <v>145</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>53</v>
+        <v>233</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="5" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>240</v>
+        <v>75</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="9"/>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="B79" s="6" t="s">
+      <c r="A79" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="J79" s="2"/>
+      <c r="K79" s="9"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C79" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D79" s="6" t="s">
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I80" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="G79" s="7" t="s">
+      <c r="J80" s="2"/>
+      <c r="K80" s="9"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="H79" s="6" t="s">
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="I79" s="6" t="s">
+      <c r="H81" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I81" s="3" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D80" s="6" t="s">
+      <c r="J81" s="2"/>
+      <c r="K81" s="9"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="G80" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="I80" s="6" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="F81" s="6"/>
-      <c r="G81" s="7" t="s">
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="H81" s="6" t="s">
+      <c r="H82" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I82" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="I81" s="6" t="s">
+      <c r="J82" s="2"/>
+      <c r="K82" s="9"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="B83" s="6" t="s">
         <v>249</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="G82" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="I82" s="6" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>251</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D83" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="H83" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="G83" s="7" t="s">
+      <c r="I83" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="H83" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I83" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
+    </row>
+    <row r="84">
       <c r="A84" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>21</v>
@@ -4128,77 +4167,77 @@
         <v>254</v>
       </c>
       <c r="G84" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="I84" s="6" t="s">
         <v>253</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I84" s="6" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="F85" s="6"/>
       <c r="G85" s="7" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="I85" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="B86" s="6" t="s">
         <v>249</v>
-      </c>
-    </row>
-    <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>251</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G86" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="I86" s="6" t="s">
         <v>253</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I86" s="6" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H87" s="6" t="s">
         <v>36</v>
@@ -4209,19 +4248,19 @@
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H88" s="6" t="s">
         <v>36</v>
@@ -4232,43 +4271,43 @@
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="F89" s="6"/>
       <c r="G89" s="7" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H90" s="6" t="s">
         <v>36</v>
@@ -4279,382 +4318,379 @@
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="6" t="s">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>265</v>
+        <v>75</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="6" t="s">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D92" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="G92" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="G92" s="7" t="s">
-        <v>264</v>
-      </c>
       <c r="H92" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>265</v>
+        <v>75</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="F93" s="6"/>
       <c r="G93" s="7" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="6" t="s">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>265</v>
+        <v>75</v>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="6" t="s">
-        <v>229</v>
+        <v>269</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H95" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="6" t="s">
-        <v>229</v>
+        <v>269</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H96" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="F97" s="6"/>
       <c r="G97" s="7" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="6" t="s">
-        <v>229</v>
+        <v>269</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D98" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="G98" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="G98" s="7" t="s">
-        <v>270</v>
-      </c>
       <c r="H98" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H99" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H100" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="F101" s="6"/>
       <c r="G101" s="7" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H102" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="G103" s="16"/>
+        <v>282</v>
+      </c>
+      <c r="G103" s="7" t="s">
+        <v>283</v>
+      </c>
       <c r="H103" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>281</v>
+        <v>75</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="G104" s="16"/>
+        <v>284</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>283</v>
+      </c>
       <c r="H104" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>281</v>
+        <v>75</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="F105" s="6"/>
       <c r="G105" s="7" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D106" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G106" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="F106" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="G106" s="16"/>
       <c r="H106" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>285</v>
+        <v>75</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>286</v>
@@ -4668,19 +4704,17 @@
       <c r="F107" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="G107" s="7" t="s">
+      <c r="G107" s="16"/>
+      <c r="H107" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I107" s="6" t="s">
         <v>289</v>
-      </c>
-      <c r="H107" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I107" s="6" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>286</v>
@@ -4689,24 +4723,22 @@
         <v>21</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="G108" s="7" t="s">
+      <c r="G108" s="16"/>
+      <c r="H108" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I108" s="6" t="s">
         <v>289</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I108" s="6" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>286</v>
@@ -4715,24 +4747,22 @@
         <v>23</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="F109" s="6" t="s">
-        <v>288</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="F109" s="6"/>
       <c r="G109" s="7" t="s">
-        <v>289</v>
+        <v>255</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>36</v>
+        <v>256</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>290</v>
+        <v>257</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>286</v>
@@ -4741,24 +4771,22 @@
         <v>28</v>
       </c>
       <c r="D110" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="G110" s="16"/>
+      <c r="H110" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I110" s="6" t="s">
         <v>293</v>
-      </c>
-      <c r="F110" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="G110" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I110" s="6" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>294</v>
@@ -4769,9 +4797,6 @@
       <c r="D111" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="E111" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="F111" s="6" t="s">
         <v>296</v>
       </c>
@@ -4787,7 +4812,7 @@
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>294</v>
@@ -4798,9 +4823,6 @@
       <c r="D112" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="E112" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="F112" s="6" t="s">
         <v>296</v>
       </c>
@@ -4816,7 +4838,7 @@
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>294</v>
@@ -4827,9 +4849,6 @@
       <c r="D113" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="E113" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="F113" s="6" t="s">
         <v>296</v>
       </c>
@@ -4845,7 +4864,7 @@
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>294</v>
@@ -4856,9 +4875,6 @@
       <c r="D114" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="E114" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="F114" s="6" t="s">
         <v>296</v>
       </c>
@@ -4874,7 +4890,7 @@
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>302</v>
@@ -4898,12 +4914,12 @@
         <v>36</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>302</v>
@@ -4912,7 +4928,7 @@
         <v>21</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>15</v>
@@ -4927,12 +4943,12 @@
         <v>36</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>302</v>
@@ -4941,7 +4957,7 @@
         <v>23</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E117" s="6" t="s">
         <v>15</v>
@@ -4956,12 +4972,12 @@
         <v>36</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>302</v>
@@ -4970,7 +4986,7 @@
         <v>28</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>15</v>
@@ -4985,24 +5001,24 @@
         <v>36</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>311</v>
+        <v>15</v>
       </c>
       <c r="F119" s="6" t="s">
         <v>312</v>
@@ -5014,24 +5030,24 @@
         <v>36</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>311</v>
+        <v>15</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>312</v>
@@ -5043,40 +5059,44 @@
         <v>36</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="E121" s="6"/>
-      <c r="F121" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="G121" s="16"/>
+        <v>315</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="G121" s="7" t="s">
+        <v>313</v>
+      </c>
       <c r="H121" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>28</v>
@@ -5085,7 +5105,7 @@
         <v>316</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>311</v>
+        <v>15</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>312</v>
@@ -5097,15 +5117,15 @@
         <v>36</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="B123" s="6" t="s">
         <v>317</v>
-      </c>
-      <c r="B123" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>13</v>
@@ -5119,26 +5139,28 @@
       <c r="F123" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="G123" s="16"/>
+      <c r="G123" s="7" t="s">
+        <v>321</v>
+      </c>
       <c r="H123" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>5</v>
+        <v>322</v>
       </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="B124" s="6" t="s">
         <v>317</v>
-      </c>
-      <c r="B124" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>319</v>
@@ -5146,45 +5168,47 @@
       <c r="F124" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="G124" s="16"/>
+      <c r="G124" s="7" t="s">
+        <v>321</v>
+      </c>
       <c r="H124" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="125" ht="16.5" customHeight="1">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="B125" s="6" t="s">
         <v>317</v>
-      </c>
-      <c r="B125" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>322</v>
+        <v>243</v>
       </c>
       <c r="E125" s="6"/>
-      <c r="F125" s="6" t="s">
-        <v>323</v>
+      <c r="F125" s="7" t="s">
+        <v>255</v>
       </c>
       <c r="G125" s="16"/>
       <c r="H125" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>5</v>
+        <v>322</v>
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="B126" s="6" t="s">
         <v>317</v>
-      </c>
-      <c r="B126" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>28</v>
@@ -5198,20 +5222,22 @@
       <c r="F126" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="G126" s="16"/>
+      <c r="G126" s="7" t="s">
+        <v>321</v>
+      </c>
       <c r="H126" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>5</v>
+        <v>322</v>
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="6" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>325</v>
+        <v>53</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>13</v>
@@ -5219,25 +5245,26 @@
       <c r="D127" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="G127" s="7" t="s">
+      <c r="E127" s="6" t="s">
         <v>327</v>
       </c>
+      <c r="F127" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="G127" s="16"/>
       <c r="H127" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="J127" s="6" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="6" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>325</v>
+        <v>53</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>21</v>
@@ -5245,25 +5272,26 @@
       <c r="D128" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="G128" s="7" t="s">
+      <c r="E128" s="6" t="s">
         <v>327</v>
       </c>
+      <c r="F128" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="G128" s="16"/>
       <c r="H128" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="J128" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="129" ht="15.75" customHeight="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" ht="16.5" customHeight="1">
       <c r="A129" s="6" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>325</v>
+        <v>53</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>23</v>
@@ -5271,74 +5299,77 @@
       <c r="D129" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="G129" s="7" t="s">
-        <v>327</v>
-      </c>
+      <c r="E129" s="6"/>
+      <c r="F129" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="G129" s="16"/>
       <c r="H129" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="J129" s="6" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="6" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>325</v>
+        <v>53</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="G130" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E130" s="6" t="s">
         <v>327</v>
       </c>
+      <c r="F130" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="G130" s="16"/>
       <c r="H130" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="J130" s="6" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="6" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>53</v>
+        <v>333</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="F131" s="6" t="s">
         <v>334</v>
       </c>
+      <c r="G131" s="7" t="s">
+        <v>335</v>
+      </c>
       <c r="H131" s="6" t="s">
-        <v>335</v>
+        <v>36</v>
       </c>
       <c r="I131" s="6" t="s">
         <v>336</v>
       </c>
+      <c r="J131" s="6" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="6" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>53</v>
+        <v>333</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>21</v>
@@ -5346,22 +5377,25 @@
       <c r="D132" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="F132" s="6" t="s">
-        <v>334</v>
+      <c r="G132" s="7" t="s">
+        <v>335</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>335</v>
+        <v>36</v>
       </c>
       <c r="I132" s="6" t="s">
-        <v>5</v>
+        <v>336</v>
+      </c>
+      <c r="J132" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="6" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>53</v>
+        <v>333</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>23</v>
@@ -5369,238 +5403,244 @@
       <c r="D133" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="F133" s="6" t="s">
-        <v>339</v>
+      <c r="G133" s="7" t="s">
+        <v>335</v>
       </c>
       <c r="H133" s="6" t="s">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>341</v>
+        <v>336</v>
+      </c>
+      <c r="J133" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="6" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>53</v>
+        <v>333</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="F134" s="6" t="s">
-        <v>334</v>
+        <v>339</v>
+      </c>
+      <c r="G134" s="7" t="s">
+        <v>335</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>335</v>
+        <v>36</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>112</v>
+        <v>336</v>
+      </c>
+      <c r="J134" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="6" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>344</v>
+        <v>53</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="E135" s="6" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="H135" s="6" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="6" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>344</v>
+        <v>53</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="E136" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="I136" s="6" t="s">
-        <v>348</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="6" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>344</v>
+        <v>53</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="E137" s="6" t="s">
         <v>346</v>
       </c>
       <c r="F137" s="6" t="s">
         <v>347</v>
       </c>
       <c r="H137" s="6" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="6" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>344</v>
+        <v>53</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="E138" s="6" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>348</v>
+        <v>120</v>
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="6" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>53</v>
+        <v>352</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="G139" s="8" t="s">
         <v>353</v>
       </c>
+      <c r="E139" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="F139" s="6" t="s">
+        <v>355</v>
+      </c>
       <c r="H139" s="6" t="s">
-        <v>36</v>
+        <v>343</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>265</v>
+        <v>356</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="6" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>53</v>
+        <v>352</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D140" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E140" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="G140" s="8" t="s">
-        <v>353</v>
+      <c r="F140" s="6" t="s">
+        <v>355</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>36</v>
+        <v>343</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>265</v>
+        <v>356</v>
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="6" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>53</v>
+        <v>352</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D141" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="F141" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="G141" s="8" t="s">
-        <v>353</v>
-      </c>
       <c r="H141" s="6" t="s">
-        <v>36</v>
+        <v>343</v>
       </c>
       <c r="I141" s="6" t="s">
-        <v>265</v>
+        <v>356</v>
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="6" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>53</v>
+        <v>352</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D142" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="F142" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="H142" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="I142" s="6" t="s">
         <v>356</v>
-      </c>
-      <c r="G142" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I142" s="6" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="6" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>53</v>
@@ -5609,21 +5649,21 @@
         <v>13</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="G143" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>361</v>
       </c>
       <c r="H143" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="I143" s="7" t="s">
-        <v>361</v>
+        <v>36</v>
+      </c>
+      <c r="I143" s="6" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="6" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>53</v>
@@ -5634,19 +5674,19 @@
       <c r="D144" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="G144" s="7" t="s">
-        <v>363</v>
+      <c r="G144" s="8" t="s">
+        <v>361</v>
       </c>
       <c r="H144" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="6" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>53</v>
@@ -5655,21 +5695,21 @@
         <v>23</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="G145" s="7" t="s">
         <v>363</v>
       </c>
+      <c r="G145" s="8" t="s">
+        <v>361</v>
+      </c>
       <c r="H145" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I145" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="6" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>53</v>
@@ -5678,21 +5718,21 @@
         <v>28</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="G146" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
+      </c>
+      <c r="G146" s="8" t="s">
+        <v>361</v>
       </c>
       <c r="H146" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>53</v>
@@ -5701,27 +5741,21 @@
         <v>13</v>
       </c>
       <c r="D147" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="G147" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="E147" s="6" t="s">
+      <c r="H147" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="F147" s="6" t="s">
+      <c r="I147" s="7" t="s">
         <v>369</v>
-      </c>
-      <c r="G147" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="H147" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I147" s="6" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>53</v>
@@ -5730,27 +5764,21 @@
         <v>21</v>
       </c>
       <c r="D148" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="G148" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="E148" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="F148" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="G148" s="8" t="s">
-        <v>370</v>
-      </c>
       <c r="H148" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>53</v>
@@ -5761,25 +5789,19 @@
       <c r="D149" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="E149" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="F149" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="G149" s="8" t="s">
-        <v>370</v>
+      <c r="G149" s="7" t="s">
+        <v>371</v>
       </c>
       <c r="H149" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I149" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>53</v>
@@ -5790,20 +5812,14 @@
       <c r="D150" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="E150" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="F150" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="G150" s="8" t="s">
-        <v>370</v>
+      <c r="G150" s="7" t="s">
+        <v>371</v>
       </c>
       <c r="H150" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="151" ht="15.75" customHeight="1">
@@ -5811,22 +5827,28 @@
         <v>374</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>375</v>
+        <v>53</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D151" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="E151" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="G151" s="8" t="s">
+      <c r="F151" s="6" t="s">
         <v>377</v>
       </c>
+      <c r="G151" s="7" t="s">
+        <v>378</v>
+      </c>
       <c r="H151" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I151" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1">
@@ -5834,22 +5856,28 @@
         <v>374</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>375</v>
+        <v>53</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D152" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="E152" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="G152" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="G152" s="8" t="s">
-        <v>377</v>
-      </c>
       <c r="H152" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I152" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="153" ht="15.75" customHeight="1">
@@ -5857,22 +5885,28 @@
         <v>374</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>375</v>
+        <v>53</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
+      </c>
+      <c r="E153" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F153" s="6" t="s">
+        <v>377</v>
       </c>
       <c r="G153" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H153" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="154" ht="15.75" customHeight="1">
@@ -5880,395 +5914,489 @@
         <v>374</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>375</v>
+        <v>53</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F154" s="6" t="s">
+        <v>377</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H154" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I154" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="G155" s="7" t="s">
         <v>384</v>
       </c>
+      <c r="G155" s="8" t="s">
+        <v>385</v>
+      </c>
       <c r="H155" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D156" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="G156" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="G156" s="7" t="s">
-        <v>384</v>
-      </c>
       <c r="H156" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I156" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="G157" s="7" t="s">
-        <v>384</v>
+        <v>387</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>385</v>
       </c>
       <c r="H157" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="G158" s="7" t="s">
-        <v>384</v>
+        <v>388</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>385</v>
       </c>
       <c r="H158" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="G159" s="8" t="s">
         <v>391</v>
       </c>
+      <c r="G159" s="7" t="s">
+        <v>392</v>
+      </c>
       <c r="H159" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D160" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="G160" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="G160" s="8" t="s">
-        <v>391</v>
-      </c>
       <c r="H160" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I160" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="G161" s="8" t="s">
-        <v>391</v>
+        <v>394</v>
+      </c>
+      <c r="G161" s="7" t="s">
+        <v>392</v>
       </c>
       <c r="H161" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I161" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="G162" s="8" t="s">
-        <v>391</v>
+        <v>395</v>
+      </c>
+      <c r="G162" s="7" t="s">
+        <v>392</v>
       </c>
       <c r="H162" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I162" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H163" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I163" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D164" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="G164" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="G164" s="8" t="s">
-        <v>398</v>
-      </c>
       <c r="H164" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I164" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H165" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I165" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G166" s="8" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H166" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I166" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>53</v>
+        <v>404</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>403</v>
-      </c>
-      <c r="G167" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
+      </c>
+      <c r="G167" s="8" t="s">
+        <v>406</v>
       </c>
       <c r="H167" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I167" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>53</v>
+        <v>404</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>405</v>
-      </c>
-      <c r="G168" s="7" t="s">
-        <v>404</v>
+        <v>407</v>
+      </c>
+      <c r="G168" s="8" t="s">
+        <v>406</v>
       </c>
       <c r="H168" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I168" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>53</v>
+        <v>404</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D169" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="G169" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="G169" s="7" t="s">
-        <v>404</v>
-      </c>
       <c r="H169" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I169" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>53</v>
+        <v>404</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="F170" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="G170" s="16"/>
-      <c r="H170" s="6"/>
+        <v>409</v>
+      </c>
+      <c r="G170" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="H170" s="6" t="s">
+        <v>36</v>
+      </c>
       <c r="I170" s="6" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="171" ht="15.75" customHeight="1">
+      <c r="A171" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="G171" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="H171" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I171" s="6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="172" ht="15.75" customHeight="1">
+      <c r="A172" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="G172" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="H172" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I172" s="6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="173" ht="15.75" customHeight="1">
+      <c r="A173" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="G173" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="H173" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I173" s="6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="174" ht="15.75" customHeight="1">
+      <c r="A174" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="F174" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="G174" s="16"/>
+      <c r="H174" s="6"/>
+      <c r="I174" s="6" t="s">
+        <v>417</v>
+      </c>
+    </row>
     <row r="175" ht="15.75" customHeight="1"/>
     <row r="176" ht="15.75" customHeight="1"/>
     <row r="177" ht="15.75" customHeight="1"/>
@@ -7197,6 +7325,10 @@
     <row r="1100" ht="15.75" customHeight="1"/>
     <row r="1101" ht="15.75" customHeight="1"/>
     <row r="1102" ht="15.75" customHeight="1"/>
+    <row r="1103" ht="15.75" customHeight="1"/>
+    <row r="1104" ht="15.75" customHeight="1"/>
+    <row r="1105" ht="15.75" customHeight="1"/>
+    <row r="1106" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" location="/home" ref="G2"/>
@@ -7230,11 +7362,11 @@
     <hyperlink r:id="rId29" ref="G31"/>
     <hyperlink r:id="rId30" ref="G32"/>
     <hyperlink r:id="rId31" ref="G33"/>
-    <hyperlink r:id="rId32" location="/home" ref="G34"/>
-    <hyperlink r:id="rId33" ref="G38"/>
-    <hyperlink r:id="rId34" ref="G39"/>
-    <hyperlink r:id="rId35" ref="G40"/>
-    <hyperlink r:id="rId36" ref="G41"/>
+    <hyperlink r:id="rId32" ref="G34"/>
+    <hyperlink r:id="rId33" ref="G35"/>
+    <hyperlink r:id="rId34" ref="G36"/>
+    <hyperlink r:id="rId35" ref="G37"/>
+    <hyperlink r:id="rId36" location="/home" ref="G38"/>
     <hyperlink r:id="rId37" ref="G42"/>
     <hyperlink r:id="rId38" ref="G43"/>
     <hyperlink r:id="rId39" ref="G44"/>
@@ -7244,21 +7376,21 @@
     <hyperlink r:id="rId43" ref="G48"/>
     <hyperlink r:id="rId44" ref="G49"/>
     <hyperlink r:id="rId45" ref="G50"/>
-    <hyperlink r:id="rId46" ref="I50"/>
-    <hyperlink r:id="rId47" ref="G51"/>
-    <hyperlink r:id="rId48" ref="G52"/>
-    <hyperlink r:id="rId49" ref="G53"/>
-    <hyperlink r:id="rId50" ref="G54"/>
-    <hyperlink r:id="rId51" ref="G56"/>
-    <hyperlink r:id="rId52" ref="G57"/>
-    <hyperlink r:id="rId53" ref="G58"/>
-    <hyperlink r:id="rId54" ref="G59"/>
+    <hyperlink r:id="rId46" ref="G51"/>
+    <hyperlink r:id="rId47" ref="G52"/>
+    <hyperlink r:id="rId48" ref="G53"/>
+    <hyperlink r:id="rId49" ref="G54"/>
+    <hyperlink r:id="rId50" ref="I54"/>
+    <hyperlink r:id="rId51" ref="G55"/>
+    <hyperlink r:id="rId52" ref="G56"/>
+    <hyperlink r:id="rId53" ref="G57"/>
+    <hyperlink r:id="rId54" ref="G58"/>
     <hyperlink r:id="rId55" ref="G60"/>
-    <hyperlink r:id="rId56" location="/home" ref="G61"/>
+    <hyperlink r:id="rId56" ref="G61"/>
     <hyperlink r:id="rId57" ref="G62"/>
     <hyperlink r:id="rId58" ref="G63"/>
     <hyperlink r:id="rId59" ref="G64"/>
-    <hyperlink r:id="rId60" ref="G65"/>
+    <hyperlink r:id="rId60" location="/home" ref="G65"/>
     <hyperlink r:id="rId61" ref="G66"/>
     <hyperlink r:id="rId62" ref="G67"/>
     <hyperlink r:id="rId63" ref="G68"/>
@@ -7296,11 +7428,11 @@
     <hyperlink r:id="rId95" ref="G100"/>
     <hyperlink r:id="rId96" ref="G101"/>
     <hyperlink r:id="rId97" ref="G102"/>
-    <hyperlink r:id="rId98" ref="G105"/>
-    <hyperlink r:id="rId99" ref="G107"/>
-    <hyperlink r:id="rId100" ref="G108"/>
-    <hyperlink r:id="rId101" ref="G109"/>
-    <hyperlink r:id="rId102" ref="G110"/>
+    <hyperlink r:id="rId98" ref="G103"/>
+    <hyperlink r:id="rId99" ref="G104"/>
+    <hyperlink r:id="rId100" ref="G105"/>
+    <hyperlink r:id="rId101" ref="G106"/>
+    <hyperlink r:id="rId102" ref="G109"/>
     <hyperlink r:id="rId103" ref="G111"/>
     <hyperlink r:id="rId104" ref="G112"/>
     <hyperlink r:id="rId105" ref="G113"/>
@@ -7311,22 +7443,22 @@
     <hyperlink r:id="rId110" ref="G118"/>
     <hyperlink r:id="rId111" ref="G119"/>
     <hyperlink r:id="rId112" ref="G120"/>
-    <hyperlink r:id="rId113" ref="F121"/>
+    <hyperlink r:id="rId113" ref="G121"/>
     <hyperlink r:id="rId114" ref="G122"/>
-    <hyperlink r:id="rId115" ref="G127"/>
-    <hyperlink r:id="rId116" ref="G128"/>
-    <hyperlink r:id="rId117" ref="G129"/>
-    <hyperlink r:id="rId118" ref="G130"/>
-    <hyperlink r:id="rId119" ref="G139"/>
-    <hyperlink r:id="rId120" ref="G140"/>
-    <hyperlink r:id="rId121" ref="G141"/>
-    <hyperlink r:id="rId122" ref="G142"/>
+    <hyperlink r:id="rId115" ref="G123"/>
+    <hyperlink r:id="rId116" ref="G124"/>
+    <hyperlink r:id="rId117" ref="F125"/>
+    <hyperlink r:id="rId118" ref="G126"/>
+    <hyperlink r:id="rId119" ref="G131"/>
+    <hyperlink r:id="rId120" ref="G132"/>
+    <hyperlink r:id="rId121" ref="G133"/>
+    <hyperlink r:id="rId122" ref="G134"/>
     <hyperlink r:id="rId123" ref="G143"/>
-    <hyperlink r:id="rId124" ref="I143"/>
-    <hyperlink r:id="rId125" ref="G144"/>
-    <hyperlink r:id="rId126" ref="G145"/>
-    <hyperlink r:id="rId127" ref="G146"/>
-    <hyperlink r:id="rId128" ref="G147"/>
+    <hyperlink r:id="rId124" ref="G144"/>
+    <hyperlink r:id="rId125" ref="G145"/>
+    <hyperlink r:id="rId126" ref="G146"/>
+    <hyperlink r:id="rId127" ref="G147"/>
+    <hyperlink r:id="rId128" ref="I147"/>
     <hyperlink r:id="rId129" ref="G148"/>
     <hyperlink r:id="rId130" ref="G149"/>
     <hyperlink r:id="rId131" ref="G150"/>
@@ -7349,10 +7481,14 @@
     <hyperlink r:id="rId148" ref="G167"/>
     <hyperlink r:id="rId149" ref="G168"/>
     <hyperlink r:id="rId150" ref="G169"/>
+    <hyperlink r:id="rId151" ref="G170"/>
+    <hyperlink r:id="rId152" ref="G171"/>
+    <hyperlink r:id="rId153" ref="G172"/>
+    <hyperlink r:id="rId154" ref="G173"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId151"/>
+  <drawing r:id="rId155"/>
 </worksheet>
 </file>
--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="hTdZ7I96eXHJnVfcwaMWkA7VgWkCNcK3pFzfESiTqIw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="xm8+n929/seUvR1Ytz18XQ6KL6RjdSHCEneI7sc9JzA="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="444">
   <si>
     <t>County</t>
   </si>
@@ -316,6 +316,39 @@
     <t>Town of Mangonia Park Fire Department</t>
   </si>
   <si>
+    <t>Boca Raton</t>
+  </si>
+  <si>
+    <t>City of Boca Raton Building Department</t>
+  </si>
+  <si>
+    <t>https://bocaratonfl.justfoia.com/Forms/Launch/a30f7991-2d31-4550-baf7-888e0928ae17</t>
+  </si>
+  <si>
+    <t>Building/Code Request</t>
+  </si>
+  <si>
+    <t>City of Boca Raton Planning Department</t>
+  </si>
+  <si>
+    <t>https://bocaratonfl.justfoia.com/Forms/Launch/d705cbd6-1396-49b7-939e-8d86c5a87deb</t>
+  </si>
+  <si>
+    <t>General Request Form</t>
+  </si>
+  <si>
+    <t>City of Boca Raton Environmental Department</t>
+  </si>
+  <si>
+    <t>City of Boca Raton Fire Department</t>
+  </si>
+  <si>
+    <t>https://bocaratonfl.justfoia.com/Forms/Launch/8d829d17-13e7-4cc4-8c00-ed5bdb9a23d5</t>
+  </si>
+  <si>
+    <t>Fire Services Request</t>
+  </si>
+  <si>
     <t>Lee</t>
   </si>
   <si>
@@ -346,7 +379,7 @@
     <t>DCDRecords@leegov.com</t>
   </si>
   <si>
-    <t>https://leecountyfl.mycusthelp.com/webapp/_rs/(S(uzjtk0pwrrfwwzgtjo2t1b5f))/supporthome.aspx</t>
+    <t>https://leecountyfl.nextrequest.com/</t>
   </si>
   <si>
     <t>FL DOH — Lee (Env. Health)</t>
@@ -359,9 +392,6 @@
   </si>
   <si>
     <t>Lee County Fire Department</t>
-  </si>
-  <si>
-    <t>https://www.leegov.com/publicrecords</t>
   </si>
   <si>
     <t>Use portal or email clerk</t>
@@ -756,6 +786,18 @@
     <t>City of North Bay Village Planning Department</t>
   </si>
   <si>
+    <t>North Miami</t>
+  </si>
+  <si>
+    <t>City of North Miami Building Department</t>
+  </si>
+  <si>
+    <t>https://northmiamifl.justfoia.com/Forms/Launch/ad7531dc-11a3-4ec9-b579-b6ba88a811bd</t>
+  </si>
+  <si>
+    <t>City of North Miami Planning Department</t>
+  </si>
+  <si>
     <t>Broward</t>
   </si>
   <si>
@@ -1020,6 +1062,18 @@
     <t>City of Lauderhill Fire Department</t>
   </si>
   <si>
+    <t>Dania Beach</t>
+  </si>
+  <si>
+    <t>City of Dania Beach Building Department</t>
+  </si>
+  <si>
+    <t>https://daniabeachfl.justfoia.com/publicportal/home/newrequest</t>
+  </si>
+  <si>
+    <t>City of Dania Beach Planning Department</t>
+  </si>
+  <si>
     <t>Collier</t>
   </si>
   <si>
@@ -1063,6 +1117,30 @@
   </si>
   <si>
     <t>City of Marco Island Fire Department</t>
+  </si>
+  <si>
+    <t>Naples</t>
+  </si>
+  <si>
+    <t>City of Naples Building Department</t>
+  </si>
+  <si>
+    <t>https://www.naplesgov.com/cityclerk/page/public-records-requests</t>
+  </si>
+  <si>
+    <t>Use portal for building, click building</t>
+  </si>
+  <si>
+    <t>City of Naples Planning Department</t>
+  </si>
+  <si>
+    <t>City of Naples Environmental Department</t>
+  </si>
+  <si>
+    <t>City of Naples Fire Department</t>
+  </si>
+  <si>
+    <t>Use portal for Fire, click Fire</t>
   </si>
   <si>
     <t>Orange</t>
@@ -1317,7 +1395,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -1358,12 +1436,6 @@
     <font>
       <u/>
       <color rgb="FF0000FF"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11.0"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -1410,7 +1482,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1439,18 +1511,17 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -2624,249 +2695,247 @@
       <c r="K33" s="9"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="J34" s="2"/>
+      <c r="K34" s="9"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="J35" s="2"/>
+      <c r="K35" s="9"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="J36" s="2"/>
+      <c r="K36" s="9"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J37" s="2"/>
+      <c r="K37" s="9"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="J34" s="2" t="s">
+      <c r="D38" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J38" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="K38" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B35" s="2" t="s">
+    <row r="39">
+      <c r="A39" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J35" s="2" t="s">
+      <c r="D39" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J39" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K35" s="2" t="s">
+      <c r="K39" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B36" s="2" t="s">
+    <row r="40">
+      <c r="A40" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D40" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B37" s="2" t="s">
+      <c r="B41" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E37" s="2" t="s">
+      <c r="D41" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G37" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I37" s="2" t="s">
+      <c r="G41" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="H41" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="I41" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="J41" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K37" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J38" s="2"/>
-      <c r="K38" s="9"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E39" s="2"/>
-      <c r="F39" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="G39" s="11"/>
-      <c r="H39" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J39" s="2"/>
-      <c r="K39" s="9"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E40" s="2"/>
-      <c r="F40" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="G40" s="11"/>
-      <c r="H40" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J40" s="2"/>
-      <c r="K40" s="9"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D41" s="3" t="s">
+      <c r="K41" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E41" s="2"/>
-      <c r="F41" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="G41" s="11"/>
-      <c r="H41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J41" s="2"/>
-      <c r="K41" s="9"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="s">
-        <v>95</v>
+      <c r="A42" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>123</v>
@@ -2877,28 +2946,25 @@
       <c r="D42" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>15</v>
+      <c r="E42" s="2"/>
+      <c r="F42" s="6" t="s">
+        <v>125</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>36</v>
+        <v>127</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K42" s="9" t="s">
-        <v>127</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="J42" s="2"/>
+      <c r="K42" s="9"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="s">
-        <v>95</v>
+      <c r="A43" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>123</v>
@@ -2907,30 +2973,25 @@
         <v>21</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G43" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" s="6" t="s">
         <v>125</v>
       </c>
+      <c r="G43" s="10"/>
       <c r="H43" s="3" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K43" s="9" t="s">
-        <v>129</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="J43" s="2"/>
+      <c r="K43" s="9"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="s">
-        <v>95</v>
+      <c r="A44" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>123</v>
@@ -2939,30 +3000,25 @@
         <v>23</v>
       </c>
       <c r="D44" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="G44" s="10"/>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K44" s="9" t="s">
-        <v>131</v>
-      </c>
+      <c r="J44" s="2"/>
+      <c r="K44" s="9"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="s">
-        <v>95</v>
+      <c r="A45" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>123</v>
@@ -2973,241 +3029,236 @@
       <c r="D45" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G45" s="5" t="s">
+      <c r="E45" s="2"/>
+      <c r="F45" s="6" t="s">
         <v>125</v>
       </c>
+      <c r="G45" s="10"/>
       <c r="H45" s="3" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K45" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="J45" s="2"/>
+      <c r="K45" s="9"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D46" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="J46" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K46" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="G46" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K46" s="9" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="s">
-        <v>134</v>
+      <c r="A47" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J47" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J47" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K47" s="9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="s">
-        <v>134</v>
+      <c r="A48" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J48" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J48" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>38</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="s">
-        <v>134</v>
+      <c r="A49" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D49" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K49" s="9" t="s">
         <v>143</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K49" s="9" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D50" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>19</v>
@@ -3218,552 +3269,566 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K53" s="9" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B54" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="E54" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="G54" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G54" s="5" t="s">
+      <c r="H54" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K54" s="9" t="s">
         <v>149</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="I54" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B55" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>154</v>
+      <c r="D55" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="J55" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J55" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K55" s="2" t="s">
-        <v>112</v>
+      <c r="K55" s="9" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="J56" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J56" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K56" s="2" t="s">
-        <v>112</v>
+      <c r="K56" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>164</v>
+        <v>144</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>153</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>168</v>
+        <v>36</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J57" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J57" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K57" s="2" t="s">
-        <v>112</v>
+      <c r="K57" s="9" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G58" s="13" t="s">
-        <v>172</v>
+        <v>156</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>159</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>174</v>
+        <v>160</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>161</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="B59" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C59" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D59" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="E59" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="F59" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="I59" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="J59" s="15" t="s">
+      <c r="A59" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="J59" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K59" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="L59" s="15"/>
-      <c r="M59" s="15"/>
-      <c r="N59" s="15"/>
-      <c r="O59" s="15"/>
-      <c r="P59" s="15"/>
-      <c r="Q59" s="15"/>
-      <c r="R59" s="15"/>
-      <c r="S59" s="15"/>
-      <c r="T59" s="15"/>
-      <c r="U59" s="15"/>
-      <c r="V59" s="15"/>
-      <c r="W59" s="15"/>
-      <c r="X59" s="15"/>
-      <c r="Y59" s="15"/>
-      <c r="Z59" s="15"/>
+      <c r="K59" s="2" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>13</v>
+        <v>167</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K60" s="9" t="s">
-        <v>38</v>
+      <c r="K60" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B61" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I61" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K61" s="9" t="s">
-        <v>38</v>
+      <c r="K61" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B62" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G62" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C63" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D63" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="F63" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D62" s="3" t="s">
+      <c r="G63" s="13"/>
+      <c r="H63" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="J62" s="2"/>
-      <c r="K62" s="9"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="J63" s="2"/>
-      <c r="K63" s="9"/>
+      <c r="I63" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="J63" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="K63" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="L63" s="14"/>
+      <c r="M63" s="14"/>
+      <c r="N63" s="14"/>
+      <c r="O63" s="14"/>
+      <c r="P63" s="14"/>
+      <c r="Q63" s="14"/>
+      <c r="R63" s="14"/>
+      <c r="S63" s="14"/>
+      <c r="T63" s="14"/>
+      <c r="U63" s="14"/>
+      <c r="V63" s="14"/>
+      <c r="W63" s="14"/>
+      <c r="X63" s="14"/>
+      <c r="Y63" s="14"/>
+      <c r="Z63" s="14"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>28</v>
+        <v>189</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E64" s="3"/>
+        <v>190</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>191</v>
+      </c>
       <c r="F64" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>193</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>196</v>
+        <v>36</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J64" s="2"/>
-      <c r="K64" s="9"/>
+        <v>194</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K64" s="9" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>13</v>
+        <v>189</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E65" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>191</v>
+      </c>
       <c r="F65" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>201</v>
+        <v>192</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>193</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>202</v>
+        <v>36</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="J65" s="2"/>
-      <c r="K65" s="9"/>
+        <v>196</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K65" s="9" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
+      <c r="F66" s="3" t="s">
+        <v>199</v>
+      </c>
       <c r="G66" s="5" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="9"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="9"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>36</v>
+        <v>206</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="9"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="G69" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="H69" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>213</v>
@@ -3773,45 +3838,43 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E70" s="3"/>
-      <c r="F70" s="3" t="s">
-        <v>218</v>
-      </c>
+      <c r="F70" s="3"/>
       <c r="G70" s="5" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>220</v>
+        <v>36</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="9"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
@@ -3821,7 +3884,7 @@
         <v>219</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>220</v>
@@ -3831,82 +3894,84 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>36</v>
+        <v>223</v>
       </c>
       <c r="J72" s="2"/>
       <c r="K72" s="9"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>36</v>
+        <v>223</v>
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="9"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D74" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
       <c r="G74" s="5" t="s">
         <v>229</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>36</v>
+        <v>230</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>230</v>
@@ -3916,10 +3981,10 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>21</v>
@@ -3928,12 +3993,14 @@
         <v>231</v>
       </c>
       <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
+      <c r="F75" s="3" t="s">
+        <v>228</v>
+      </c>
       <c r="G75" s="5" t="s">
         <v>229</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>36</v>
+        <v>230</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>230</v>
@@ -3943,46 +4010,50 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
+      <c r="F76" s="3" t="s">
+        <v>234</v>
+      </c>
       <c r="G76" s="5" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>230</v>
+        <v>36</v>
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="9"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D77" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
       <c r="G77" s="5" t="s">
         <v>235</v>
       </c>
@@ -3990,50 +4061,50 @@
         <v>36</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="J77" s="2"/>
       <c r="K77" s="9"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>75</v>
+        <v>240</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="9"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="C79" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
@@ -4051,16 +4122,16 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="C80" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
@@ -4071,47 +4142,47 @@
         <v>36</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="9"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>237</v>
+        <v>155</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>53</v>
+        <v>243</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>245</v>
+        <v>75</v>
       </c>
       <c r="J81" s="2"/>
       <c r="K81" s="9"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>237</v>
+        <v>155</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>53</v>
+        <v>243</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>246</v>
@@ -4119,288 +4190,310 @@
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>248</v>
+        <v>75</v>
       </c>
       <c r="J82" s="2"/>
       <c r="K82" s="9"/>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B83" s="6" t="s">
+      <c r="A83" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="C83" s="6" t="s">
+      <c r="H83" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J83" s="2"/>
+      <c r="K83" s="9"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J84" s="2"/>
+      <c r="K84" s="9"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D83" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="G83" s="7" t="s">
+      <c r="D85" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="J85" s="2"/>
+      <c r="K85" s="9"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="H83" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="I83" s="6" t="s">
+      <c r="B86" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="5" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="C84" s="6" t="s">
+      <c r="H86" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J86" s="2"/>
+      <c r="K86" s="9"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="J87" s="2"/>
+      <c r="K87" s="9"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="J88" s="2"/>
+      <c r="K88" s="9"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C90" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D84" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="I84" s="6" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="F85" s="6"/>
-      <c r="G85" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="I85" s="6" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="G86" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="I86" s="6" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="G87" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I87" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="G88" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I88" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="F89" s="6"/>
-      <c r="G89" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="I89" s="6" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="D90" s="6" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>36</v>
+        <v>266</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>75</v>
+        <v>267</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D91" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F91" s="6"/>
+      <c r="G91" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="G92" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="G91" s="7" t="s">
+      <c r="H92" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="H91" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I91" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D92" s="6" t="s">
+      <c r="I92" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="G92" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I92" s="6" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="F93" s="6"/>
+        <v>274</v>
+      </c>
       <c r="G93" s="7" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>256</v>
+        <v>36</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>257</v>
+        <v>75</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>36</v>
@@ -4411,421 +4504,413 @@
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F95" s="6"/>
+      <c r="G95" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="B95" s="6" t="s">
+      <c r="H95" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="C95" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D95" s="6" t="s">
+      <c r="I95" s="6" t="s">
         <v>271</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="H95" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I95" s="6" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="6" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H96" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="F97" s="6"/>
+        <v>279</v>
+      </c>
       <c r="G97" s="7" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>256</v>
+        <v>36</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>257</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="6" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="H98" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>277</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="F99" s="6"/>
       <c r="G99" s="7" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>36</v>
+        <v>270</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H100" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="6" t="s">
-        <v>237</v>
+        <v>283</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="F101" s="6"/>
+        <v>285</v>
+      </c>
       <c r="G101" s="7" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>256</v>
+        <v>36</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="6" t="s">
-        <v>237</v>
+        <v>283</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="H102" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>282</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="F103" s="6"/>
       <c r="G103" s="7" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>36</v>
+        <v>270</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>75</v>
+        <v>271</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="6" t="s">
-        <v>237</v>
+        <v>283</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="H104" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>75</v>
+        <v>287</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="F105" s="6"/>
+        <v>291</v>
+      </c>
       <c r="G105" s="7" t="s">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>256</v>
+        <v>36</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="H106" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>75</v>
+        <v>287</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="F107" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="G107" s="16"/>
+        <v>257</v>
+      </c>
+      <c r="F107" s="6"/>
+      <c r="G107" s="7" t="s">
+        <v>269</v>
+      </c>
       <c r="H107" s="6" t="s">
-        <v>5</v>
+        <v>270</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="F108" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="G108" s="16"/>
+        <v>294</v>
+      </c>
+      <c r="G108" s="7" t="s">
+        <v>292</v>
+      </c>
       <c r="H108" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="F109" s="6"/>
+        <v>296</v>
+      </c>
       <c r="G109" s="7" t="s">
-        <v>255</v>
+        <v>297</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>256</v>
+        <v>36</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>257</v>
+        <v>75</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="F110" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="G110" s="16"/>
+        <v>298</v>
+      </c>
+      <c r="G110" s="7" t="s">
+        <v>297</v>
+      </c>
       <c r="H110" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>293</v>
+        <v>75</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="F111" s="6" t="s">
-        <v>296</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="F111" s="6"/>
       <c r="G111" s="7" t="s">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>36</v>
+        <v>270</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>298</v>
+        <v>271</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="F112" s="6" t="s">
-        <v>296</v>
-      </c>
       <c r="G112" s="7" t="s">
         <v>297</v>
       </c>
@@ -4833,549 +4918,542 @@
         <v>36</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>298</v>
+        <v>75</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="G113" s="7" t="s">
-        <v>297</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="G113" s="15"/>
       <c r="H113" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="G114" s="7" t="s">
-        <v>297</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="G114" s="15"/>
       <c r="H114" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="E115" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F115" s="6" t="s">
-        <v>304</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="F115" s="6"/>
       <c r="G115" s="7" t="s">
-        <v>305</v>
+        <v>269</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>36</v>
+        <v>270</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>306</v>
+        <v>271</v>
       </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D116" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="G116" s="15"/>
+      <c r="H116" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I116" s="6" t="s">
         <v>307</v>
-      </c>
-      <c r="E116" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="G116" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I116" s="6" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="E117" s="6" t="s">
-        <v>15</v>
+        <v>309</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="H117" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="E118" s="6" t="s">
-        <v>15</v>
+        <v>313</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="H118" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B119" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="F119" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="C119" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D119" s="6" t="s">
+      <c r="G119" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="E119" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F119" s="6" t="s">
+      <c r="H119" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I119" s="6" t="s">
         <v>312</v>
-      </c>
-      <c r="G119" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="H119" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I119" s="6" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B120" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="F120" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="C120" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D120" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="E120" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F120" s="6" t="s">
+      <c r="G120" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I120" s="6" t="s">
         <v>312</v>
-      </c>
-      <c r="G120" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I120" s="6" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E121" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="H121" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="H122" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D123" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F123" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="E123" s="6" t="s">
+      <c r="G123" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="F123" s="6" t="s">
+      <c r="H123" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I123" s="6" t="s">
         <v>320</v>
-      </c>
-      <c r="G123" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="H123" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I123" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>323</v>
       </c>
       <c r="E124" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="G124" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="F124" s="6" t="s">
+      <c r="H124" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I124" s="6" t="s">
         <v>320</v>
-      </c>
-      <c r="G124" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I124" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="E125" s="6"/>
-      <c r="F125" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="G125" s="16"/>
+        <v>325</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="G125" s="7" t="s">
+        <v>327</v>
+      </c>
       <c r="H125" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="6" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>319</v>
+        <v>15</v>
       </c>
       <c r="F126" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="G126" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I126" s="6" t="s">
         <v>320</v>
-      </c>
-      <c r="G126" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I126" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="6" t="s">
-        <v>325</v>
+        <v>251</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>53</v>
+        <v>324</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D127" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F127" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="E127" s="6" t="s">
+      <c r="G127" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="F127" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="G127" s="16"/>
       <c r="H127" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="6" t="s">
-        <v>325</v>
+        <v>251</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>53</v>
+        <v>324</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E128" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="G128" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="F128" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="G128" s="16"/>
       <c r="H128" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="129" ht="16.5" customHeight="1">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="6" t="s">
-        <v>325</v>
+        <v>251</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>53</v>
+        <v>331</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="E129" s="6"/>
+        <v>332</v>
+      </c>
+      <c r="E129" s="6" t="s">
+        <v>333</v>
+      </c>
       <c r="F129" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="G129" s="16"/>
+        <v>334</v>
+      </c>
+      <c r="G129" s="7" t="s">
+        <v>335</v>
+      </c>
       <c r="H129" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>5</v>
+        <v>336</v>
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="6" t="s">
-        <v>325</v>
+        <v>251</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>53</v>
+        <v>331</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="G130" s="16"/>
+        <v>334</v>
+      </c>
+      <c r="G130" s="7" t="s">
+        <v>335</v>
+      </c>
       <c r="H130" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>5</v>
+        <v>336</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="6" t="s">
-        <v>325</v>
+        <v>251</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="G131" s="7" t="s">
-        <v>335</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="E131" s="6"/>
+      <c r="F131" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G131" s="15"/>
       <c r="H131" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I131" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="J131" s="6" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="6" t="s">
-        <v>325</v>
+        <v>251</v>
       </c>
       <c r="B132" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="E132" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="C132" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D132" s="6" t="s">
-        <v>337</v>
+      <c r="F132" s="6" t="s">
+        <v>334</v>
       </c>
       <c r="G132" s="7" t="s">
         <v>335</v>
@@ -5386,1031 +5464,1368 @@
       <c r="I132" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="J132" s="6" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="6" t="s">
-        <v>325</v>
+        <v>251</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>338</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="E133" s="6"/>
+      <c r="F133" s="6"/>
       <c r="G133" s="7" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="H133" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="J133" s="6" t="s">
-        <v>19</v>
+        <v>287</v>
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="6" t="s">
-        <v>325</v>
+        <v>251</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>339</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="E134" s="6"/>
+      <c r="F134" s="6"/>
       <c r="G134" s="7" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="H134" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="J134" s="6" t="s">
-        <v>19</v>
+        <v>287</v>
       </c>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="6" t="s">
-        <v>340</v>
+        <v>251</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>53</v>
+        <v>339</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="F135" s="6" t="s">
-        <v>342</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="E135" s="6"/>
+      <c r="F135" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G135" s="15"/>
       <c r="H135" s="6" t="s">
-        <v>343</v>
+        <v>36</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D136" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="B136" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C136" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D136" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="F136" s="6" t="s">
-        <v>342</v>
+      <c r="E136" s="6"/>
+      <c r="F136" s="6"/>
+      <c r="G136" s="7" t="s">
+        <v>341</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>343</v>
+        <v>36</v>
       </c>
       <c r="I136" s="6" t="s">
-        <v>5</v>
+        <v>287</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="6" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D137" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="F137" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="F137" s="6" t="s">
-        <v>347</v>
-      </c>
+      <c r="G137" s="15"/>
       <c r="H137" s="6" t="s">
-        <v>348</v>
+        <v>5</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>349</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="6" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>350</v>
+        <v>347</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>345</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>342</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="G138" s="15"/>
       <c r="H138" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I138" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" ht="16.5" customHeight="1">
+      <c r="A139" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="I138" s="6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="6" t="s">
-        <v>351</v>
-      </c>
       <c r="B139" s="6" t="s">
-        <v>352</v>
+        <v>53</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="E139" s="6" t="s">
-        <v>354</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="E139" s="6"/>
       <c r="F139" s="6" t="s">
-        <v>355</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="G139" s="15"/>
       <c r="H139" s="6" t="s">
-        <v>343</v>
+        <v>5</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>356</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="6" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>352</v>
+        <v>53</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>355</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="G140" s="15"/>
       <c r="H140" s="6" t="s">
-        <v>343</v>
+        <v>5</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>356</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="B141" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="B141" s="6" t="s">
+      <c r="C141" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D141" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="C141" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D141" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E141" s="6" t="s">
+      <c r="G141" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="H141" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I141" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="F141" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="H141" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="I141" s="6" t="s">
-        <v>356</v>
+      <c r="J141" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="B142" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="B142" s="6" t="s">
-        <v>352</v>
-      </c>
       <c r="C142" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="E142" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="G142" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="H142" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I142" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="F142" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="I142" s="6" t="s">
-        <v>356</v>
+      <c r="J142" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="B143" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="B143" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="C143" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="G143" s="8" t="s">
-        <v>361</v>
+        <v>356</v>
+      </c>
+      <c r="G143" s="7" t="s">
+        <v>353</v>
       </c>
       <c r="H143" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>273</v>
+        <v>354</v>
+      </c>
+      <c r="J143" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="B144" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="B144" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="C144" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="G144" s="8" t="s">
-        <v>361</v>
+        <v>357</v>
+      </c>
+      <c r="G144" s="7" t="s">
+        <v>353</v>
       </c>
       <c r="H144" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>273</v>
+        <v>354</v>
+      </c>
+      <c r="J144" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="6" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>53</v>
+        <v>358</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="G145" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="G145" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="H145" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I145" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="H145" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I145" s="6" t="s">
-        <v>273</v>
-      </c>
+      <c r="J145" s="6"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="6" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>53</v>
+        <v>358</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="G146" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="G146" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="H146" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I146" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="H146" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I146" s="6" t="s">
-        <v>273</v>
-      </c>
+      <c r="J146" s="6"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="6" t="s">
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>53</v>
+        <v>358</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="G147" s="7" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="H147" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="I147" s="7" t="s">
-        <v>369</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="I147" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="J147" s="6"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="G148" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="H148" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I148" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="B148" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C148" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D148" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="G148" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I148" s="6" t="s">
-        <v>273</v>
-      </c>
+      <c r="J148" s="6"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="G149" s="7" t="s">
-        <v>371</v>
+        <v>367</v>
+      </c>
+      <c r="F149" s="6" t="s">
+        <v>368</v>
       </c>
       <c r="H149" s="6" t="s">
-        <v>36</v>
+        <v>369</v>
       </c>
       <c r="I149" s="6" t="s">
-        <v>273</v>
+        <v>370</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="G150" s="7" t="s">
         <v>371</v>
       </c>
+      <c r="F150" s="6" t="s">
+        <v>368</v>
+      </c>
       <c r="H150" s="6" t="s">
-        <v>36</v>
+        <v>369</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>273</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="6" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D151" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="F151" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="H151" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="I151" s="6" t="s">
         <v>375</v>
-      </c>
-      <c r="E151" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="F151" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="G151" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="H151" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I151" s="6" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="6" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="E152" s="6" t="s">
         <v>376</v>
       </c>
       <c r="F152" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="G152" s="8" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>36</v>
+        <v>369</v>
       </c>
       <c r="I152" s="6" t="s">
-        <v>273</v>
+        <v>130</v>
       </c>
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>53</v>
+        <v>378</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D153" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="E153" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="E153" s="6" t="s">
-        <v>376</v>
-      </c>
       <c r="F153" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="G153" s="8" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="H153" s="6" t="s">
-        <v>36</v>
+        <v>369</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>273</v>
+        <v>382</v>
       </c>
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>53</v>
+        <v>378</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D154" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="F154" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="E154" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="F154" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="G154" s="8" t="s">
-        <v>378</v>
-      </c>
       <c r="H154" s="6" t="s">
-        <v>36</v>
+        <v>369</v>
       </c>
       <c r="I154" s="6" t="s">
-        <v>273</v>
+        <v>382</v>
       </c>
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="6" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D155" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="G155" s="8" t="s">
-        <v>385</v>
+      <c r="E155" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="F155" s="6" t="s">
+        <v>381</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>36</v>
+        <v>369</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>273</v>
+        <v>382</v>
       </c>
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="H156" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="I156" s="6" t="s">
         <v>382</v>
-      </c>
-      <c r="B156" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="C156" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D156" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="G156" s="8" t="s">
-        <v>385</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I156" s="6" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="6" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>383</v>
+        <v>53</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D157" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="G157" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="G157" s="8" t="s">
-        <v>385</v>
-      </c>
       <c r="H157" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="6" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>383</v>
+        <v>53</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D158" s="6" t="s">
         <v>388</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H158" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D159" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="B159" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="C159" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D159" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="G159" s="7" t="s">
-        <v>392</v>
+      <c r="G159" s="8" t="s">
+        <v>387</v>
       </c>
       <c r="H159" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="6" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="B160" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D160" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="C160" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D160" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="G160" s="7" t="s">
-        <v>392</v>
+      <c r="G160" s="8" t="s">
+        <v>387</v>
       </c>
       <c r="H160" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I160" s="6" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>390</v>
+        <v>53</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D161" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="G161" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="H161" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="G161" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="H161" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I161" s="6" t="s">
-        <v>273</v>
+      <c r="I161" s="7" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>390</v>
+        <v>53</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G162" s="7" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="H162" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I162" s="6" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="6" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>397</v>
+        <v>53</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D163" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="G163" s="8" t="s">
-        <v>399</v>
+      <c r="G163" s="7" t="s">
+        <v>397</v>
       </c>
       <c r="H163" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I163" s="6" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="6" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B164" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="G164" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="C164" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D164" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="G164" s="8" t="s">
-        <v>399</v>
-      </c>
       <c r="H164" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I164" s="6" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="6" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>397</v>
+        <v>53</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D165" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="G165" s="8" t="s">
-        <v>399</v>
+      <c r="E165" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="F165" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="G165" s="7" t="s">
+        <v>404</v>
       </c>
       <c r="H165" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I165" s="6" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="6" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>397</v>
+        <v>53</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D166" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="E166" s="6" t="s">
         <v>402</v>
       </c>
+      <c r="F166" s="6" t="s">
+        <v>403</v>
+      </c>
       <c r="G166" s="8" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="H166" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I166" s="6" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="E167" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="F167" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="B167" s="6" t="s">
+      <c r="G167" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="C167" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D167" s="6" t="s">
-        <v>405</v>
-      </c>
-      <c r="G167" s="8" t="s">
-        <v>406</v>
-      </c>
       <c r="H167" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I167" s="6" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="6" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>404</v>
+        <v>53</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D168" s="6" t="s">
         <v>407</v>
       </c>
+      <c r="E168" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="F168" s="6" t="s">
+        <v>403</v>
+      </c>
       <c r="G168" s="8" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H168" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I168" s="6" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="6" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G169" s="8" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="H169" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I169" s="6" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="6" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="H170" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I170" s="6" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>53</v>
+        <v>409</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D171" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="G171" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="G171" s="7" t="s">
-        <v>412</v>
-      </c>
       <c r="H171" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I171" s="6" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>53</v>
+        <v>409</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="G172" s="7" t="s">
-        <v>412</v>
+        <v>414</v>
+      </c>
+      <c r="G172" s="8" t="s">
+        <v>411</v>
       </c>
       <c r="H172" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I172" s="6" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="6" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>53</v>
+        <v>416</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="G173" s="7" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="H173" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I173" s="6" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="6" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B174" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="G174" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="H174" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I174" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="175" ht="15.75" customHeight="1">
+      <c r="A175" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="G175" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="H175" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I175" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="176" ht="15.75" customHeight="1">
+      <c r="A176" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D176" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="G176" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="H176" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I176" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="177" ht="15.75" customHeight="1">
+      <c r="A177" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D177" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="G177" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="H177" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I177" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="178" ht="15.75" customHeight="1">
+      <c r="A178" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="G178" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="H178" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I178" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="179" ht="15.75" customHeight="1">
+      <c r="A179" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="G179" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="H179" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I179" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="180" ht="15.75" customHeight="1">
+      <c r="A180" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D180" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="G180" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="H180" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I180" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="181" ht="15.75" customHeight="1">
+      <c r="A181" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D181" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="G181" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="H181" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I181" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="182" ht="15.75" customHeight="1">
+      <c r="A182" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="G182" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="H182" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I182" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="183" ht="15.75" customHeight="1">
+      <c r="A183" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="G183" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="H183" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I183" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="184" ht="15.75" customHeight="1">
+      <c r="A184" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="G184" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="H184" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I184" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="185" ht="15.75" customHeight="1">
+      <c r="A185" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="B185" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C174" s="6" t="s">
+      <c r="C185" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="G185" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="H185" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I185" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="186" ht="15.75" customHeight="1">
+      <c r="A186" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="G186" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="H186" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I186" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="187" ht="15.75" customHeight="1">
+      <c r="A187" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C187" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D187" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="G187" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="H187" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I187" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="188" ht="15.75" customHeight="1">
+      <c r="A188" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C188" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D174" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="F174" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G174" s="16"/>
-      <c r="H174" s="6"/>
-      <c r="I174" s="6" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
+      <c r="D188" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="F188" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="G188" s="15"/>
+      <c r="H188" s="6"/>
+      <c r="I188" s="6" t="s">
+        <v>443</v>
+      </c>
+    </row>
     <row r="189" ht="15.75" customHeight="1"/>
     <row r="190" ht="15.75" customHeight="1"/>
     <row r="191" ht="15.75" customHeight="1"/>
@@ -7329,6 +7744,20 @@
     <row r="1104" ht="15.75" customHeight="1"/>
     <row r="1105" ht="15.75" customHeight="1"/>
     <row r="1106" ht="15.75" customHeight="1"/>
+    <row r="1107" ht="15.75" customHeight="1"/>
+    <row r="1108" ht="15.75" customHeight="1"/>
+    <row r="1109" ht="15.75" customHeight="1"/>
+    <row r="1110" ht="15.75" customHeight="1"/>
+    <row r="1111" ht="15.75" customHeight="1"/>
+    <row r="1112" ht="15.75" customHeight="1"/>
+    <row r="1113" ht="15.75" customHeight="1"/>
+    <row r="1114" ht="15.75" customHeight="1"/>
+    <row r="1115" ht="15.75" customHeight="1"/>
+    <row r="1116" ht="15.75" customHeight="1"/>
+    <row r="1117" ht="15.75" customHeight="1"/>
+    <row r="1118" ht="15.75" customHeight="1"/>
+    <row r="1119" ht="15.75" customHeight="1"/>
+    <row r="1120" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" location="/home" ref="G2"/>
@@ -7366,11 +7795,11 @@
     <hyperlink r:id="rId33" ref="G35"/>
     <hyperlink r:id="rId34" ref="G36"/>
     <hyperlink r:id="rId35" ref="G37"/>
-    <hyperlink r:id="rId36" location="/home" ref="G38"/>
-    <hyperlink r:id="rId37" ref="G42"/>
-    <hyperlink r:id="rId38" ref="G43"/>
-    <hyperlink r:id="rId39" ref="G44"/>
-    <hyperlink r:id="rId40" ref="G45"/>
+    <hyperlink r:id="rId36" ref="G38"/>
+    <hyperlink r:id="rId37" ref="G39"/>
+    <hyperlink r:id="rId38" ref="G40"/>
+    <hyperlink r:id="rId39" ref="G41"/>
+    <hyperlink r:id="rId40" location="/home" ref="G42"/>
     <hyperlink r:id="rId41" ref="G46"/>
     <hyperlink r:id="rId42" ref="G47"/>
     <hyperlink r:id="rId43" ref="G48"/>
@@ -7380,21 +7809,21 @@
     <hyperlink r:id="rId47" ref="G52"/>
     <hyperlink r:id="rId48" ref="G53"/>
     <hyperlink r:id="rId49" ref="G54"/>
-    <hyperlink r:id="rId50" ref="I54"/>
-    <hyperlink r:id="rId51" ref="G55"/>
-    <hyperlink r:id="rId52" ref="G56"/>
-    <hyperlink r:id="rId53" ref="G57"/>
-    <hyperlink r:id="rId54" ref="G58"/>
-    <hyperlink r:id="rId55" ref="G60"/>
-    <hyperlink r:id="rId56" ref="G61"/>
-    <hyperlink r:id="rId57" ref="G62"/>
-    <hyperlink r:id="rId58" ref="G63"/>
+    <hyperlink r:id="rId50" ref="G55"/>
+    <hyperlink r:id="rId51" ref="G56"/>
+    <hyperlink r:id="rId52" ref="G57"/>
+    <hyperlink r:id="rId53" ref="G58"/>
+    <hyperlink r:id="rId54" ref="I58"/>
+    <hyperlink r:id="rId55" ref="G59"/>
+    <hyperlink r:id="rId56" ref="G60"/>
+    <hyperlink r:id="rId57" ref="G61"/>
+    <hyperlink r:id="rId58" ref="G62"/>
     <hyperlink r:id="rId59" ref="G64"/>
-    <hyperlink r:id="rId60" location="/home" ref="G65"/>
+    <hyperlink r:id="rId60" ref="G65"/>
     <hyperlink r:id="rId61" ref="G66"/>
     <hyperlink r:id="rId62" ref="G67"/>
     <hyperlink r:id="rId63" ref="G68"/>
-    <hyperlink r:id="rId64" ref="G69"/>
+    <hyperlink r:id="rId64" location="/home" ref="G69"/>
     <hyperlink r:id="rId65" ref="G70"/>
     <hyperlink r:id="rId66" ref="G71"/>
     <hyperlink r:id="rId67" ref="G72"/>
@@ -7432,13 +7861,13 @@
     <hyperlink r:id="rId99" ref="G104"/>
     <hyperlink r:id="rId100" ref="G105"/>
     <hyperlink r:id="rId101" ref="G106"/>
-    <hyperlink r:id="rId102" ref="G109"/>
-    <hyperlink r:id="rId103" ref="G111"/>
-    <hyperlink r:id="rId104" ref="G112"/>
-    <hyperlink r:id="rId105" ref="G113"/>
-    <hyperlink r:id="rId106" ref="G114"/>
-    <hyperlink r:id="rId107" ref="G115"/>
-    <hyperlink r:id="rId108" ref="G116"/>
+    <hyperlink r:id="rId102" ref="G107"/>
+    <hyperlink r:id="rId103" ref="G108"/>
+    <hyperlink r:id="rId104" ref="G109"/>
+    <hyperlink r:id="rId105" ref="G110"/>
+    <hyperlink r:id="rId106" ref="G111"/>
+    <hyperlink r:id="rId107" ref="G112"/>
+    <hyperlink r:id="rId108" ref="G115"/>
     <hyperlink r:id="rId109" ref="G117"/>
     <hyperlink r:id="rId110" ref="G118"/>
     <hyperlink r:id="rId111" ref="G119"/>
@@ -7447,32 +7876,32 @@
     <hyperlink r:id="rId114" ref="G122"/>
     <hyperlink r:id="rId115" ref="G123"/>
     <hyperlink r:id="rId116" ref="G124"/>
-    <hyperlink r:id="rId117" ref="F125"/>
+    <hyperlink r:id="rId117" ref="G125"/>
     <hyperlink r:id="rId118" ref="G126"/>
-    <hyperlink r:id="rId119" ref="G131"/>
-    <hyperlink r:id="rId120" ref="G132"/>
-    <hyperlink r:id="rId121" ref="G133"/>
-    <hyperlink r:id="rId122" ref="G134"/>
-    <hyperlink r:id="rId123" ref="G143"/>
-    <hyperlink r:id="rId124" ref="G144"/>
-    <hyperlink r:id="rId125" ref="G145"/>
-    <hyperlink r:id="rId126" ref="G146"/>
-    <hyperlink r:id="rId127" ref="G147"/>
-    <hyperlink r:id="rId128" ref="I147"/>
-    <hyperlink r:id="rId129" ref="G148"/>
-    <hyperlink r:id="rId130" ref="G149"/>
-    <hyperlink r:id="rId131" ref="G150"/>
-    <hyperlink r:id="rId132" ref="G151"/>
-    <hyperlink r:id="rId133" ref="G152"/>
-    <hyperlink r:id="rId134" ref="G153"/>
-    <hyperlink r:id="rId135" ref="G154"/>
-    <hyperlink r:id="rId136" ref="G155"/>
-    <hyperlink r:id="rId137" ref="G156"/>
-    <hyperlink r:id="rId138" ref="G157"/>
-    <hyperlink r:id="rId139" ref="G158"/>
-    <hyperlink r:id="rId140" ref="G159"/>
-    <hyperlink r:id="rId141" ref="G160"/>
-    <hyperlink r:id="rId142" ref="G161"/>
+    <hyperlink r:id="rId119" ref="G127"/>
+    <hyperlink r:id="rId120" ref="G128"/>
+    <hyperlink r:id="rId121" ref="G129"/>
+    <hyperlink r:id="rId122" ref="G130"/>
+    <hyperlink r:id="rId123" ref="F131"/>
+    <hyperlink r:id="rId124" ref="G132"/>
+    <hyperlink r:id="rId125" ref="G133"/>
+    <hyperlink r:id="rId126" ref="G134"/>
+    <hyperlink r:id="rId127" ref="F135"/>
+    <hyperlink r:id="rId128" ref="G136"/>
+    <hyperlink r:id="rId129" ref="G141"/>
+    <hyperlink r:id="rId130" ref="G142"/>
+    <hyperlink r:id="rId131" ref="G143"/>
+    <hyperlink r:id="rId132" ref="G144"/>
+    <hyperlink r:id="rId133" ref="G145"/>
+    <hyperlink r:id="rId134" ref="G146"/>
+    <hyperlink r:id="rId135" ref="G147"/>
+    <hyperlink r:id="rId136" ref="G148"/>
+    <hyperlink r:id="rId137" ref="G157"/>
+    <hyperlink r:id="rId138" ref="G158"/>
+    <hyperlink r:id="rId139" ref="G159"/>
+    <hyperlink r:id="rId140" ref="G160"/>
+    <hyperlink r:id="rId141" ref="G161"/>
+    <hyperlink r:id="rId142" ref="I161"/>
     <hyperlink r:id="rId143" ref="G162"/>
     <hyperlink r:id="rId144" ref="G163"/>
     <hyperlink r:id="rId145" ref="G164"/>
@@ -7485,10 +7914,24 @@
     <hyperlink r:id="rId152" ref="G171"/>
     <hyperlink r:id="rId153" ref="G172"/>
     <hyperlink r:id="rId154" ref="G173"/>
+    <hyperlink r:id="rId155" ref="G174"/>
+    <hyperlink r:id="rId156" ref="G175"/>
+    <hyperlink r:id="rId157" ref="G176"/>
+    <hyperlink r:id="rId158" ref="G177"/>
+    <hyperlink r:id="rId159" ref="G178"/>
+    <hyperlink r:id="rId160" ref="G179"/>
+    <hyperlink r:id="rId161" ref="G180"/>
+    <hyperlink r:id="rId162" ref="G181"/>
+    <hyperlink r:id="rId163" ref="G182"/>
+    <hyperlink r:id="rId164" ref="G183"/>
+    <hyperlink r:id="rId165" ref="G184"/>
+    <hyperlink r:id="rId166" ref="G185"/>
+    <hyperlink r:id="rId167" ref="G186"/>
+    <hyperlink r:id="rId168" ref="G187"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId155"/>
+  <drawing r:id="rId169"/>
 </worksheet>
 </file>
--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="hTdZ7I96eXHJnVfcwaMWkA7VgWkCNcK3pFzfESiTqIw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="p6f/Q5o9orb+l4OeoNuzEflHzvG0oTkDE1MyGJSZy4s="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="429">
   <si>
     <t>County</t>
   </si>
@@ -314,6 +314,39 @@
   </si>
   <si>
     <t>Town of Mangonia Park Fire Department</t>
+  </si>
+  <si>
+    <t>Boca Raton</t>
+  </si>
+  <si>
+    <t>City of Boca Raton Building Department</t>
+  </si>
+  <si>
+    <t>https://bocaratonfl.justfoia.com/Forms/Launch/a30f7991-2d31-4550-baf7-888e0928ae17</t>
+  </si>
+  <si>
+    <t>Building/Code Request</t>
+  </si>
+  <si>
+    <t>City of Boca Raton Planning Department</t>
+  </si>
+  <si>
+    <t>https://bocaratonfl.justfoia.com/Forms/Launch/d705cbd6-1396-49b7-939e-8d86c5a87deb</t>
+  </si>
+  <si>
+    <t>General Request Form</t>
+  </si>
+  <si>
+    <t>City of Boca Raton Environmental Department</t>
+  </si>
+  <si>
+    <t>City of Boca Raton Fire Department</t>
+  </si>
+  <si>
+    <t>https://bocaratonfl.justfoia.com/Forms/Launch/8d829d17-13e7-4cc4-8c00-ed5bdb9a23d5</t>
+  </si>
+  <si>
+    <t>Fire Services Request</t>
   </si>
   <si>
     <t>Lee</t>
@@ -2624,476 +2657,456 @@
       <c r="K33" s="9"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="J34" s="2"/>
+      <c r="K34" s="9"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="J35" s="2"/>
+      <c r="K35" s="9"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="J36" s="2"/>
+      <c r="K36" s="9"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J37" s="2"/>
+      <c r="K37" s="9"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="J34" s="2" t="s">
+      <c r="D38" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J38" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="K38" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B35" s="2" t="s">
+    <row r="39">
+      <c r="A39" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J35" s="2" t="s">
+      <c r="D39" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J39" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K35" s="2" t="s">
+      <c r="K39" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B36" s="2" t="s">
+    <row r="40">
+      <c r="A40" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D40" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B37" s="2" t="s">
+      <c r="B41" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E37" s="2" t="s">
+      <c r="D41" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G37" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I37" s="2" t="s">
+      <c r="G41" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="H41" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="I41" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J41" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K37" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J38" s="2"/>
-      <c r="K38" s="9"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E39" s="2"/>
-      <c r="F39" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="G39" s="11"/>
-      <c r="H39" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J39" s="2"/>
-      <c r="K39" s="9"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E40" s="2"/>
-      <c r="F40" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="G40" s="11"/>
-      <c r="H40" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J40" s="2"/>
-      <c r="K40" s="9"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="G41" s="11"/>
-      <c r="H41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J41" s="2"/>
-      <c r="K41" s="9"/>
+      <c r="K41" s="9" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="s">
-        <v>95</v>
+      <c r="A42" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D42" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J42" s="2"/>
+      <c r="K42" s="9"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K42" s="9" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>125</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G43" s="11"/>
       <c r="H43" s="3" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K43" s="9" t="s">
-        <v>129</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="J43" s="2"/>
+      <c r="K43" s="9"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="s">
-        <v>95</v>
+      <c r="A44" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>125</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G44" s="11"/>
       <c r="H44" s="3" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K44" s="9" t="s">
         <v>131</v>
       </c>
+      <c r="J44" s="2"/>
+      <c r="K44" s="9"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="s">
-        <v>95</v>
+      <c r="A45" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>125</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G45" s="11"/>
       <c r="H45" s="3" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K45" s="9" t="s">
-        <v>133</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="J45" s="2"/>
+      <c r="K45" s="9"/>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D46" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="H46" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G46" s="5" t="s">
+      <c r="J46" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K46" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K46" s="9" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D47" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K47" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K47" s="9" t="s">
-        <v>141</v>
-      </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D48" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K48" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K48" s="9" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>28</v>
@@ -3101,19 +3114,19 @@
       <c r="D49" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G49" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J49" s="3" t="s">
+      <c r="J49" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K49" s="9" t="s">
@@ -3122,92 +3135,92 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>53</v>
+        <v>146</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E50" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>53</v>
+        <v>146</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="E51" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>53</v>
+        <v>146</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="E52" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>19</v>
@@ -3218,104 +3231,98 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>53</v>
+        <v>146</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="E53" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K53" s="9" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E54" s="2" t="s">
+      <c r="D54" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="E54" s="3" t="s">
         <v>148</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>149</v>
       </c>
       <c r="H54" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K54" s="9" t="s">
         <v>150</v>
-      </c>
-      <c r="I54" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K55" s="9" t="s">
         <v>152</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="56">
@@ -3323,573 +3330,591 @@
         <v>145</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="J56" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="J56" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K56" s="2" t="s">
-        <v>112</v>
+      <c r="K56" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>164</v>
+      <c r="B57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>168</v>
+        <v>36</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J57" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="J57" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K57" s="2" t="s">
-        <v>112</v>
+      <c r="K57" s="9" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G58" s="13" t="s">
-        <v>172</v>
+        <v>157</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>160</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>174</v>
+        <v>161</v>
+      </c>
+      <c r="I58" s="12" t="s">
+        <v>162</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="B59" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C59" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D59" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="E59" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="F59" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="I59" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="J59" s="15" t="s">
+      <c r="A59" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J59" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K59" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="L59" s="15"/>
-      <c r="M59" s="15"/>
-      <c r="N59" s="15"/>
-      <c r="O59" s="15"/>
-      <c r="P59" s="15"/>
-      <c r="Q59" s="15"/>
-      <c r="R59" s="15"/>
-      <c r="S59" s="15"/>
-      <c r="T59" s="15"/>
-      <c r="U59" s="15"/>
-      <c r="V59" s="15"/>
-      <c r="W59" s="15"/>
-      <c r="X59" s="15"/>
-      <c r="Y59" s="15"/>
-      <c r="Z59" s="15"/>
+      <c r="K59" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>13</v>
+        <v>168</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K60" s="9" t="s">
-        <v>38</v>
+      <c r="K60" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B61" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H61" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="I61" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K61" s="9" t="s">
-        <v>38</v>
+      <c r="K61" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B62" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G62" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="E63" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D62" s="3" t="s">
+      <c r="F63" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3" t="s">
+      <c r="G63" s="14"/>
+      <c r="H63" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="G62" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="J62" s="2"/>
-      <c r="K62" s="9"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3" t="s">
+      <c r="I63" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="G63" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="J63" s="2"/>
-      <c r="K63" s="9"/>
+      <c r="J63" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="K63" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="L63" s="15"/>
+      <c r="M63" s="15"/>
+      <c r="N63" s="15"/>
+      <c r="O63" s="15"/>
+      <c r="P63" s="15"/>
+      <c r="Q63" s="15"/>
+      <c r="R63" s="15"/>
+      <c r="S63" s="15"/>
+      <c r="T63" s="15"/>
+      <c r="U63" s="15"/>
+      <c r="V63" s="15"/>
+      <c r="W63" s="15"/>
+      <c r="X63" s="15"/>
+      <c r="Y63" s="15"/>
+      <c r="Z63" s="15"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>28</v>
+        <v>190</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="D64" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I64" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="G64" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J64" s="2"/>
-      <c r="K64" s="9"/>
+      <c r="J64" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K64" s="9" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>13</v>
+        <v>190</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E65" s="3"/>
+        <v>196</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="F65" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>201</v>
+        <v>193</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>202</v>
+        <v>36</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="J65" s="2"/>
-      <c r="K65" s="9"/>
+        <v>197</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K65" s="9" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
+      <c r="F66" s="3" t="s">
+        <v>200</v>
+      </c>
       <c r="G66" s="5" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="9"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="9"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I68" s="3" t="s">
         <v>208</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>213</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="9"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G69" s="5" t="s">
         <v>212</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>36</v>
+        <v>213</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="9"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B70" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C70" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="G70" s="5" t="s">
-        <v>219</v>
-      </c>
       <c r="H70" s="3" t="s">
-        <v>220</v>
+        <v>36</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="9"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="9"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>223</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I72" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="G72" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="J72" s="2"/>
       <c r="K72" s="9"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I73" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="G73" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="9"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>227</v>
@@ -3901,22 +3926,24 @@
         <v>228</v>
       </c>
       <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
+      <c r="F74" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="G74" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>36</v>
+        <v>231</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="9"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>227</v>
@@ -3925,412 +3952,433 @@
         <v>21</v>
       </c>
       <c r="D75" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="H75" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="I75" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="9"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
+      <c r="F76" s="3" t="s">
+        <v>235</v>
+      </c>
       <c r="G76" s="5" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>230</v>
+        <v>36</v>
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="9"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>233</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
+      <c r="F77" s="3" t="s">
+        <v>235</v>
+      </c>
       <c r="G77" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="J77" s="2"/>
       <c r="K77" s="9"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="5" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="9"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>237</v>
+        <v>156</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>53</v>
+        <v>238</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="9"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>237</v>
+        <v>156</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>53</v>
+        <v>238</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="9"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>237</v>
+        <v>156</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>53</v>
+        <v>244</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>245</v>
+        <v>75</v>
       </c>
       <c r="J81" s="2"/>
       <c r="K81" s="9"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>237</v>
+        <v>156</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>53</v>
+        <v>244</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>248</v>
+        <v>75</v>
       </c>
       <c r="J82" s="2"/>
       <c r="K82" s="9"/>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B83" s="6" t="s">
+      <c r="A83" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="C83" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D83" s="6" t="s">
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="G83" s="7" t="s">
+      <c r="H83" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I83" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="H83" s="6" t="s">
+      <c r="J83" s="2"/>
+      <c r="K83" s="9"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="I83" s="6" t="s">
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I84" s="3" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D84" s="6" t="s">
+      <c r="J84" s="2"/>
+      <c r="K84" s="9"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="G84" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="I84" s="6" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="F85" s="6"/>
-      <c r="G85" s="7" t="s">
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="H85" s="6" t="s">
+      <c r="H85" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I85" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="I85" s="6" t="s">
+      <c r="J85" s="2"/>
+      <c r="K85" s="9"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D86" s="3" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D86" s="6" t="s">
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="G86" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="I86" s="6" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="87" ht="15.75" customHeight="1">
+      <c r="H86" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="J86" s="2"/>
+      <c r="K86" s="9"/>
+    </row>
+    <row r="87">
       <c r="A87" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D87" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B88" s="6" t="s">
         <v>260</v>
-      </c>
-      <c r="G87" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I87" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>259</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D88" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="G88" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="G88" s="7" t="s">
-        <v>261</v>
-      </c>
       <c r="H88" s="6" t="s">
-        <v>36</v>
+        <v>263</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>75</v>
+        <v>264</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F89" s="6"/>
       <c r="G89" s="7" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="90" ht="15.75" customHeight="1">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="90">
       <c r="A90" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D90" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="G90" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>36</v>
-      </c>
       <c r="I90" s="6" t="s">
-        <v>75</v>
+        <v>264</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>36</v>
@@ -4341,19 +4389,19 @@
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>36</v>
@@ -4364,43 +4412,43 @@
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F93" s="6"/>
       <c r="G93" s="7" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>36</v>
@@ -4411,1112 +4459,1110 @@
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="6" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H95" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="6" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H96" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F97" s="6"/>
       <c r="G97" s="7" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="6" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H98" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="6" t="s">
-        <v>237</v>
+        <v>280</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="H99" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="6" t="s">
-        <v>237</v>
+        <v>280</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="H100" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F101" s="6"/>
       <c r="G101" s="7" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="6" t="s">
-        <v>237</v>
+        <v>280</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="H102" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="H103" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>75</v>
+        <v>284</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D104" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I104" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="G104" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I104" s="6" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F105" s="6"/>
       <c r="G105" s="7" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="H106" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>75</v>
+        <v>284</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="F107" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="G107" s="16"/>
+        <v>293</v>
+      </c>
+      <c r="G107" s="7" t="s">
+        <v>294</v>
+      </c>
       <c r="H107" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>289</v>
+        <v>75</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="F108" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="G108" s="16"/>
+        <v>295</v>
+      </c>
+      <c r="G108" s="7" t="s">
+        <v>294</v>
+      </c>
       <c r="H108" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>289</v>
+        <v>75</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F109" s="6"/>
       <c r="G109" s="7" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="F110" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="G110" s="16"/>
+        <v>296</v>
+      </c>
+      <c r="G110" s="7" t="s">
+        <v>294</v>
+      </c>
       <c r="H110" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>293</v>
+        <v>75</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="G111" s="7" t="s">
-        <v>297</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="G111" s="16"/>
       <c r="H111" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D112" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="F112" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="F112" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="G112" s="7" t="s">
-        <v>297</v>
-      </c>
+      <c r="G112" s="16"/>
       <c r="H112" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="F113" s="6" t="s">
-        <v>296</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="F113" s="6"/>
       <c r="G113" s="7" t="s">
-        <v>297</v>
+        <v>266</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>36</v>
+        <v>267</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>298</v>
+        <v>268</v>
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="G114" s="7" t="s">
-        <v>297</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="G114" s="16"/>
       <c r="H114" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="E115" s="6" t="s">
-        <v>15</v>
+        <v>306</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="H115" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D116" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="F116" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="E116" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>304</v>
-      </c>
       <c r="G116" s="7" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="H116" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D117" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="G117" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="E117" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F117" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="G117" s="7" t="s">
-        <v>305</v>
-      </c>
       <c r="H117" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D118" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="G118" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I118" s="6" t="s">
         <v>309</v>
-      </c>
-      <c r="E118" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F118" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="G118" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I118" s="6" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E119" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="H119" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G120" s="7" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="H120" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E121" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="H121" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="H122" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>319</v>
+        <v>15</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G123" s="7" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H123" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D124" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="E124" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F124" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="E124" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="F124" s="6" t="s">
-        <v>320</v>
-      </c>
       <c r="G124" s="7" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H124" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="E125" s="6"/>
-      <c r="F125" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="G125" s="16"/>
+        <v>326</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="G125" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="H125" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="6" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D126" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="G126" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="E126" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="F126" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="G126" s="7" t="s">
-        <v>321</v>
-      </c>
       <c r="H126" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="6" t="s">
-        <v>325</v>
+        <v>248</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>53</v>
+        <v>328</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="G127" s="16"/>
+        <v>331</v>
+      </c>
+      <c r="G127" s="7" t="s">
+        <v>332</v>
+      </c>
       <c r="H127" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>5</v>
+        <v>333</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="6" t="s">
-        <v>325</v>
+        <v>248</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>53</v>
+        <v>328</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F128" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="G128" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="H128" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I128" s="6" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="129" ht="15.75" customHeight="1">
+      <c r="A129" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B129" s="6" t="s">
         <v>328</v>
-      </c>
-      <c r="G128" s="16"/>
-      <c r="H128" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I128" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="129" ht="16.5" customHeight="1">
-      <c r="A129" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="B129" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>330</v>
+        <v>254</v>
       </c>
       <c r="E129" s="6"/>
-      <c r="F129" s="6" t="s">
-        <v>331</v>
+      <c r="F129" s="7" t="s">
+        <v>266</v>
       </c>
       <c r="G129" s="16"/>
       <c r="H129" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>5</v>
+        <v>333</v>
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="6" t="s">
-        <v>325</v>
+        <v>248</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>53</v>
+        <v>328</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D130" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="F130" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="G130" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="E130" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="F130" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="G130" s="16"/>
       <c r="H130" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>5</v>
+        <v>333</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="6" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>333</v>
+        <v>53</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="G131" s="7" t="s">
-        <v>335</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="F131" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G131" s="16"/>
       <c r="H131" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I131" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="J131" s="6" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="6" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>333</v>
+        <v>53</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="G132" s="7" t="s">
-        <v>335</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="F132" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G132" s="16"/>
       <c r="H132" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I132" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" ht="16.5" customHeight="1">
+      <c r="A133" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="J132" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="6" t="s">
-        <v>325</v>
-      </c>
       <c r="B133" s="6" t="s">
-        <v>333</v>
+        <v>53</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="G133" s="7" t="s">
-        <v>335</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="E133" s="6"/>
+      <c r="F133" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="G133" s="16"/>
       <c r="H133" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="J133" s="6" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="6" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>333</v>
+        <v>53</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D134" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="F134" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="G134" s="7" t="s">
-        <v>335</v>
-      </c>
+      <c r="G134" s="16"/>
       <c r="H134" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="J134" s="6" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>53</v>
+        <v>344</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="F135" s="6" t="s">
-        <v>342</v>
+        <v>345</v>
+      </c>
+      <c r="G135" s="7" t="s">
+        <v>346</v>
       </c>
       <c r="H135" s="6" t="s">
-        <v>343</v>
+        <v>36</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>344</v>
+        <v>347</v>
+      </c>
+      <c r="J135" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>53</v>
+        <v>344</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="F136" s="6" t="s">
-        <v>342</v>
+        <v>348</v>
+      </c>
+      <c r="G136" s="7" t="s">
+        <v>346</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>343</v>
+        <v>36</v>
       </c>
       <c r="I136" s="6" t="s">
-        <v>5</v>
+        <v>347</v>
+      </c>
+      <c r="J136" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>53</v>
+        <v>344</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D137" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="G137" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="F137" s="6" t="s">
+      <c r="H137" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I137" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="H137" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="I137" s="6" t="s">
-        <v>349</v>
+      <c r="J137" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>53</v>
+        <v>344</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>28</v>
@@ -5524,14 +5570,17 @@
       <c r="D138" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="F138" s="6" t="s">
-        <v>342</v>
+      <c r="G138" s="7" t="s">
+        <v>346</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>343</v>
+        <v>36</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>120</v>
+        <v>347</v>
+      </c>
+      <c r="J138" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1">
@@ -5539,25 +5588,22 @@
         <v>351</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>352</v>
+        <v>53</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D139" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="F139" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="E139" s="6" t="s">
+      <c r="H139" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="F139" s="6" t="s">
+      <c r="I139" s="6" t="s">
         <v>355</v>
-      </c>
-      <c r="H139" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="I139" s="6" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
@@ -5565,25 +5611,22 @@
         <v>351</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>352</v>
+        <v>53</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="E140" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="H140" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="F140" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>343</v>
-      </c>
       <c r="I140" s="6" t="s">
-        <v>356</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1">
@@ -5591,25 +5634,22 @@
         <v>351</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>352</v>
+        <v>53</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D141" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="F141" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="E141" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="F141" s="6" t="s">
-        <v>355</v>
-      </c>
       <c r="H141" s="6" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="I141" s="6" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1">
@@ -5617,122 +5657,131 @@
         <v>351</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>352</v>
+        <v>53</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="E142" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="F142" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="H142" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="F142" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>343</v>
-      </c>
       <c r="I142" s="6" t="s">
-        <v>356</v>
+        <v>131</v>
       </c>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="6" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>53</v>
+        <v>363</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="G143" s="8" t="s">
-        <v>361</v>
+        <v>364</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="F143" s="6" t="s">
+        <v>366</v>
       </c>
       <c r="H143" s="6" t="s">
-        <v>36</v>
+        <v>354</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>273</v>
+        <v>367</v>
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="6" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>53</v>
+        <v>363</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="G144" s="8" t="s">
-        <v>361</v>
+        <v>368</v>
+      </c>
+      <c r="E144" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="F144" s="6" t="s">
+        <v>366</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>36</v>
+        <v>354</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>273</v>
+        <v>367</v>
       </c>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="6" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>53</v>
+        <v>363</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="G145" s="8" t="s">
-        <v>361</v>
+        <v>369</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="F145" s="6" t="s">
+        <v>366</v>
       </c>
       <c r="H145" s="6" t="s">
-        <v>36</v>
+        <v>354</v>
       </c>
       <c r="I145" s="6" t="s">
-        <v>273</v>
+        <v>367</v>
       </c>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="6" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>53</v>
+        <v>363</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="G146" s="8" t="s">
-        <v>361</v>
+        <v>370</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="F146" s="6" t="s">
+        <v>366</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>36</v>
+        <v>354</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>273</v>
+        <v>367</v>
       </c>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="6" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>53</v>
@@ -5741,21 +5790,21 @@
         <v>13</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="G147" s="7" t="s">
-        <v>367</v>
+        <v>371</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>372</v>
       </c>
       <c r="H147" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="I147" s="7" t="s">
-        <v>369</v>
+        <v>36</v>
+      </c>
+      <c r="I147" s="6" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="6" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>53</v>
@@ -5764,21 +5813,21 @@
         <v>21</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="G148" s="7" t="s">
-        <v>371</v>
+        <v>373</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>372</v>
       </c>
       <c r="H148" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="6" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>53</v>
@@ -5787,21 +5836,21 @@
         <v>23</v>
       </c>
       <c r="D149" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="G149" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="G149" s="7" t="s">
-        <v>371</v>
-      </c>
       <c r="H149" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I149" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="6" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>53</v>
@@ -5810,21 +5859,21 @@
         <v>28</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="G150" s="7" t="s">
-        <v>371</v>
+        <v>375</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>372</v>
       </c>
       <c r="H150" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>53</v>
@@ -5833,27 +5882,21 @@
         <v>13</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="E151" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="F151" s="6" t="s">
         <v>377</v>
       </c>
       <c r="G151" s="7" t="s">
         <v>378</v>
       </c>
       <c r="H151" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I151" s="6" t="s">
-        <v>273</v>
+        <v>379</v>
+      </c>
+      <c r="I151" s="7" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>53</v>
@@ -5862,27 +5905,21 @@
         <v>21</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="E152" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="F152" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="G152" s="8" t="s">
-        <v>378</v>
+        <v>381</v>
+      </c>
+      <c r="G152" s="7" t="s">
+        <v>382</v>
       </c>
       <c r="H152" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I152" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>53</v>
@@ -5891,27 +5928,21 @@
         <v>23</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="E153" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="F153" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="G153" s="8" t="s">
-        <v>378</v>
+        <v>383</v>
+      </c>
+      <c r="G153" s="7" t="s">
+        <v>382</v>
       </c>
       <c r="H153" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>53</v>
@@ -5920,487 +5951,593 @@
         <v>28</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="E154" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="F154" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="G154" s="8" t="s">
-        <v>378</v>
+        <v>384</v>
+      </c>
+      <c r="G154" s="7" t="s">
+        <v>382</v>
       </c>
       <c r="H154" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I154" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="6" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>383</v>
+        <v>53</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="G155" s="8" t="s">
-        <v>385</v>
+        <v>386</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="F155" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="G155" s="7" t="s">
+        <v>389</v>
       </c>
       <c r="H155" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="6" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>383</v>
+        <v>53</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>386</v>
+        <v>390</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>388</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="H156" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I156" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="6" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>383</v>
+        <v>53</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D157" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="E157" s="6" t="s">
         <v>387</v>
       </c>
+      <c r="F157" s="6" t="s">
+        <v>388</v>
+      </c>
       <c r="G157" s="8" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="H157" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="6" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>383</v>
+        <v>53</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D158" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="F158" s="6" t="s">
         <v>388</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="H158" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="6" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="G159" s="7" t="s">
-        <v>392</v>
+        <v>395</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>396</v>
       </c>
       <c r="H159" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="6" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="G160" s="7" t="s">
-        <v>392</v>
+        <v>397</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>396</v>
       </c>
       <c r="H160" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I160" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="6" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="G161" s="7" t="s">
-        <v>392</v>
+        <v>398</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>396</v>
       </c>
       <c r="H161" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I161" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="6" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="G162" s="7" t="s">
-        <v>392</v>
+        <v>399</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>396</v>
       </c>
       <c r="H162" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I162" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="6" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>398</v>
-      </c>
-      <c r="G163" s="8" t="s">
-        <v>399</v>
+        <v>402</v>
+      </c>
+      <c r="G163" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="H163" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I163" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="6" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="G164" s="8" t="s">
-        <v>399</v>
+        <v>404</v>
+      </c>
+      <c r="G164" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="H164" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I164" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="6" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="G165" s="8" t="s">
-        <v>399</v>
+        <v>405</v>
+      </c>
+      <c r="G165" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="H165" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I165" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="6" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="G166" s="8" t="s">
-        <v>399</v>
+        <v>406</v>
+      </c>
+      <c r="G166" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="H166" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I166" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="6" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="G167" s="8" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="H167" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I167" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="6" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="G168" s="8" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="H168" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I168" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="6" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="G169" s="8" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="H169" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I169" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="6" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="H170" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I170" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="6" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>53</v>
+        <v>415</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="G171" s="7" t="s">
-        <v>412</v>
+        <v>416</v>
+      </c>
+      <c r="G171" s="8" t="s">
+        <v>417</v>
       </c>
       <c r="H171" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I171" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="6" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>53</v>
+        <v>415</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="G172" s="7" t="s">
-        <v>412</v>
+        <v>418</v>
+      </c>
+      <c r="G172" s="8" t="s">
+        <v>417</v>
       </c>
       <c r="H172" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I172" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="6" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>53</v>
+        <v>415</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>414</v>
-      </c>
-      <c r="G173" s="7" t="s">
-        <v>412</v>
+        <v>419</v>
+      </c>
+      <c r="G173" s="8" t="s">
+        <v>417</v>
       </c>
       <c r="H173" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I173" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="6" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>53</v>
+        <v>415</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="F174" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G174" s="16"/>
-      <c r="H174" s="6"/>
+        <v>420</v>
+      </c>
+      <c r="G174" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="H174" s="6" t="s">
+        <v>36</v>
+      </c>
       <c r="I174" s="6" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
+        <v>284</v>
+      </c>
+    </row>
+    <row r="175" ht="15.75" customHeight="1">
+      <c r="A175" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="G175" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="H175" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I175" s="6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="176" ht="15.75" customHeight="1">
+      <c r="A176" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D176" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="G176" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="H176" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I176" s="6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="177" ht="15.75" customHeight="1">
+      <c r="A177" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D177" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="G177" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="H177" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I177" s="6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="178" ht="15.75" customHeight="1">
+      <c r="A178" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="F178" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="G178" s="16"/>
+      <c r="H178" s="6"/>
+      <c r="I178" s="6" t="s">
+        <v>428</v>
+      </c>
+    </row>
     <row r="179" ht="15.75" customHeight="1"/>
     <row r="180" ht="15.75" customHeight="1"/>
     <row r="181" ht="15.75" customHeight="1"/>
@@ -7329,6 +7466,10 @@
     <row r="1104" ht="15.75" customHeight="1"/>
     <row r="1105" ht="15.75" customHeight="1"/>
     <row r="1106" ht="15.75" customHeight="1"/>
+    <row r="1107" ht="15.75" customHeight="1"/>
+    <row r="1108" ht="15.75" customHeight="1"/>
+    <row r="1109" ht="15.75" customHeight="1"/>
+    <row r="1110" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" location="/home" ref="G2"/>
@@ -7366,11 +7507,11 @@
     <hyperlink r:id="rId33" ref="G35"/>
     <hyperlink r:id="rId34" ref="G36"/>
     <hyperlink r:id="rId35" ref="G37"/>
-    <hyperlink r:id="rId36" location="/home" ref="G38"/>
-    <hyperlink r:id="rId37" ref="G42"/>
-    <hyperlink r:id="rId38" ref="G43"/>
-    <hyperlink r:id="rId39" ref="G44"/>
-    <hyperlink r:id="rId40" ref="G45"/>
+    <hyperlink r:id="rId36" ref="G38"/>
+    <hyperlink r:id="rId37" ref="G39"/>
+    <hyperlink r:id="rId38" ref="G40"/>
+    <hyperlink r:id="rId39" ref="G41"/>
+    <hyperlink r:id="rId40" location="/home" ref="G42"/>
     <hyperlink r:id="rId41" ref="G46"/>
     <hyperlink r:id="rId42" ref="G47"/>
     <hyperlink r:id="rId43" ref="G48"/>
@@ -7380,21 +7521,21 @@
     <hyperlink r:id="rId47" ref="G52"/>
     <hyperlink r:id="rId48" ref="G53"/>
     <hyperlink r:id="rId49" ref="G54"/>
-    <hyperlink r:id="rId50" ref="I54"/>
-    <hyperlink r:id="rId51" ref="G55"/>
-    <hyperlink r:id="rId52" ref="G56"/>
-    <hyperlink r:id="rId53" ref="G57"/>
-    <hyperlink r:id="rId54" ref="G58"/>
-    <hyperlink r:id="rId55" ref="G60"/>
-    <hyperlink r:id="rId56" ref="G61"/>
-    <hyperlink r:id="rId57" ref="G62"/>
-    <hyperlink r:id="rId58" ref="G63"/>
+    <hyperlink r:id="rId50" ref="G55"/>
+    <hyperlink r:id="rId51" ref="G56"/>
+    <hyperlink r:id="rId52" ref="G57"/>
+    <hyperlink r:id="rId53" ref="G58"/>
+    <hyperlink r:id="rId54" ref="I58"/>
+    <hyperlink r:id="rId55" ref="G59"/>
+    <hyperlink r:id="rId56" ref="G60"/>
+    <hyperlink r:id="rId57" ref="G61"/>
+    <hyperlink r:id="rId58" ref="G62"/>
     <hyperlink r:id="rId59" ref="G64"/>
-    <hyperlink r:id="rId60" location="/home" ref="G65"/>
+    <hyperlink r:id="rId60" ref="G65"/>
     <hyperlink r:id="rId61" ref="G66"/>
     <hyperlink r:id="rId62" ref="G67"/>
     <hyperlink r:id="rId63" ref="G68"/>
-    <hyperlink r:id="rId64" ref="G69"/>
+    <hyperlink r:id="rId64" location="/home" ref="G69"/>
     <hyperlink r:id="rId65" ref="G70"/>
     <hyperlink r:id="rId66" ref="G71"/>
     <hyperlink r:id="rId67" ref="G72"/>
@@ -7432,11 +7573,11 @@
     <hyperlink r:id="rId99" ref="G104"/>
     <hyperlink r:id="rId100" ref="G105"/>
     <hyperlink r:id="rId101" ref="G106"/>
-    <hyperlink r:id="rId102" ref="G109"/>
-    <hyperlink r:id="rId103" ref="G111"/>
-    <hyperlink r:id="rId104" ref="G112"/>
-    <hyperlink r:id="rId105" ref="G113"/>
-    <hyperlink r:id="rId106" ref="G114"/>
+    <hyperlink r:id="rId102" ref="G107"/>
+    <hyperlink r:id="rId103" ref="G108"/>
+    <hyperlink r:id="rId104" ref="G109"/>
+    <hyperlink r:id="rId105" ref="G110"/>
+    <hyperlink r:id="rId106" ref="G113"/>
     <hyperlink r:id="rId107" ref="G115"/>
     <hyperlink r:id="rId108" ref="G116"/>
     <hyperlink r:id="rId109" ref="G117"/>
@@ -7447,22 +7588,22 @@
     <hyperlink r:id="rId114" ref="G122"/>
     <hyperlink r:id="rId115" ref="G123"/>
     <hyperlink r:id="rId116" ref="G124"/>
-    <hyperlink r:id="rId117" ref="F125"/>
+    <hyperlink r:id="rId117" ref="G125"/>
     <hyperlink r:id="rId118" ref="G126"/>
-    <hyperlink r:id="rId119" ref="G131"/>
-    <hyperlink r:id="rId120" ref="G132"/>
-    <hyperlink r:id="rId121" ref="G133"/>
-    <hyperlink r:id="rId122" ref="G134"/>
-    <hyperlink r:id="rId123" ref="G143"/>
-    <hyperlink r:id="rId124" ref="G144"/>
-    <hyperlink r:id="rId125" ref="G145"/>
-    <hyperlink r:id="rId126" ref="G146"/>
+    <hyperlink r:id="rId119" ref="G127"/>
+    <hyperlink r:id="rId120" ref="G128"/>
+    <hyperlink r:id="rId121" ref="F129"/>
+    <hyperlink r:id="rId122" ref="G130"/>
+    <hyperlink r:id="rId123" ref="G135"/>
+    <hyperlink r:id="rId124" ref="G136"/>
+    <hyperlink r:id="rId125" ref="G137"/>
+    <hyperlink r:id="rId126" ref="G138"/>
     <hyperlink r:id="rId127" ref="G147"/>
-    <hyperlink r:id="rId128" ref="I147"/>
-    <hyperlink r:id="rId129" ref="G148"/>
-    <hyperlink r:id="rId130" ref="G149"/>
-    <hyperlink r:id="rId131" ref="G150"/>
-    <hyperlink r:id="rId132" ref="G151"/>
+    <hyperlink r:id="rId128" ref="G148"/>
+    <hyperlink r:id="rId129" ref="G149"/>
+    <hyperlink r:id="rId130" ref="G150"/>
+    <hyperlink r:id="rId131" ref="G151"/>
+    <hyperlink r:id="rId132" ref="I151"/>
     <hyperlink r:id="rId133" ref="G152"/>
     <hyperlink r:id="rId134" ref="G153"/>
     <hyperlink r:id="rId135" ref="G154"/>
@@ -7485,10 +7626,14 @@
     <hyperlink r:id="rId152" ref="G171"/>
     <hyperlink r:id="rId153" ref="G172"/>
     <hyperlink r:id="rId154" ref="G173"/>
+    <hyperlink r:id="rId155" ref="G174"/>
+    <hyperlink r:id="rId156" ref="G175"/>
+    <hyperlink r:id="rId157" ref="G176"/>
+    <hyperlink r:id="rId158" ref="G177"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId155"/>
+  <drawing r:id="rId159"/>
 </worksheet>
 </file>
--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="p6f/Q5o9orb+l4OeoNuzEflHzvG0oTkDE1MyGJSZy4s="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="xm8+n929/seUvR1Ytz18XQ6KL6RjdSHCEneI7sc9JzA="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1480" uniqueCount="448">
   <si>
     <t>County</t>
   </si>
@@ -379,7 +379,7 @@
     <t>DCDRecords@leegov.com</t>
   </si>
   <si>
-    <t>https://leecountyfl.mycusthelp.com/webapp/_rs/(S(uzjtk0pwrrfwwzgtjo2t1b5f))/supporthome.aspx</t>
+    <t>https://leecountyfl.nextrequest.com/</t>
   </si>
   <si>
     <t>FL DOH — Lee (Env. Health)</t>
@@ -392,9 +392,6 @@
   </si>
   <si>
     <t>Lee County Fire Department</t>
-  </si>
-  <si>
-    <t>https://www.leegov.com/publicrecords</t>
   </si>
   <si>
     <t>Use portal or email clerk</t>
@@ -789,6 +786,18 @@
     <t>City of North Bay Village Planning Department</t>
   </si>
   <si>
+    <t>North Miami</t>
+  </si>
+  <si>
+    <t>City of North Miami Building Department</t>
+  </si>
+  <si>
+    <t>https://northmiamifl.justfoia.com/Forms/Launch/ad7531dc-11a3-4ec9-b579-b6ba88a811bd</t>
+  </si>
+  <si>
+    <t>City of North Miami Planning Department</t>
+  </si>
+  <si>
     <t>Broward</t>
   </si>
   <si>
@@ -1053,6 +1062,30 @@
     <t>City of Lauderhill Fire Department</t>
   </si>
   <si>
+    <t>Dania Beach</t>
+  </si>
+  <si>
+    <t>City of Dania Beach Building Department</t>
+  </si>
+  <si>
+    <t>CDRecords@daniabeachfl.gov</t>
+  </si>
+  <si>
+    <t>https://daniabeachfl.justfoia.com/publicportal/home/newrequest</t>
+  </si>
+  <si>
+    <t>City of Dania Beach Planning Department</t>
+  </si>
+  <si>
+    <t>Broward County Sherrif Office Fire Department</t>
+  </si>
+  <si>
+    <t>https://browardcountysheriff.govqa.us/WEBAPP/_rs/(S(mrbbdqpuwczglbwadl2mqznz))/RequestOpen.aspx?sSessionID=7301152WIYWHCWZWBVKQTSBMLZDNURKIFYIMRTHP&amp;rqst=14</t>
+  </si>
+  <si>
+    <t>Use portal for BSO</t>
+  </si>
+  <si>
     <t>Collier</t>
   </si>
   <si>
@@ -1096,6 +1129,30 @@
   </si>
   <si>
     <t>City of Marco Island Fire Department</t>
+  </si>
+  <si>
+    <t>Naples</t>
+  </si>
+  <si>
+    <t>City of Naples Building Department</t>
+  </si>
+  <si>
+    <t>https://www.naplesgov.com/cityclerk/page/public-records-requests</t>
+  </si>
+  <si>
+    <t>Use portal for building, click building</t>
+  </si>
+  <si>
+    <t>City of Naples Planning Department</t>
+  </si>
+  <si>
+    <t>City of Naples Environmental Department</t>
+  </si>
+  <si>
+    <t>City of Naples Fire Department</t>
+  </si>
+  <si>
+    <t>Use portal for Fire, click Fire</t>
   </si>
   <si>
     <t>Orange</t>
@@ -1393,12 +1450,6 @@
       <color rgb="FF0000FF"/>
     </font>
     <font>
-      <u/>
-      <sz val="11.0"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1413,6 +1464,12 @@
       <sz val="11.0"/>
       <color theme="10"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1472,21 +1529,23 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -2879,20 +2938,20 @@
       <c r="E41" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G41" s="10" t="s">
-        <v>121</v>
+      <c r="G41" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>111</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42">
@@ -2900,26 +2959,26 @@
         <v>106</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="G42" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="G42" s="5" t="s">
+      <c r="H42" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="I42" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="9"/>
@@ -2929,24 +2988,24 @@
         <v>106</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="G43" s="11"/>
+        <v>125</v>
+      </c>
+      <c r="G43" s="10"/>
       <c r="H43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J43" s="2"/>
       <c r="K43" s="9"/>
@@ -2956,24 +3015,24 @@
         <v>106</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="G44" s="11"/>
+        <v>125</v>
+      </c>
+      <c r="G44" s="10"/>
       <c r="H44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="9"/>
@@ -2983,24 +3042,24 @@
         <v>106</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="G45" s="11"/>
+        <v>125</v>
+      </c>
+      <c r="G45" s="10"/>
       <c r="H45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J45" s="2"/>
       <c r="K45" s="9"/>
@@ -3010,31 +3069,31 @@
         <v>106</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G46" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K46" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47">
@@ -3042,31 +3101,31 @@
         <v>106</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G47" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K47" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48">
@@ -3074,31 +3133,31 @@
         <v>106</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G48" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49">
@@ -3106,121 +3165,121 @@
         <v>106</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G49" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D50" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="G50" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G50" s="5" t="s">
-        <v>149</v>
-      </c>
       <c r="H50" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E51" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G51" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G51" s="5" t="s">
-        <v>149</v>
-      </c>
       <c r="H51" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E52" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G52" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G52" s="5" t="s">
-        <v>149</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>19</v>
@@ -3231,39 +3290,39 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E53" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G53" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G53" s="5" t="s">
-        <v>149</v>
-      </c>
       <c r="H53" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K53" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>53</v>
@@ -3272,30 +3331,30 @@
         <v>13</v>
       </c>
       <c r="D54" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="G54" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G54" s="5" t="s">
-        <v>149</v>
-      </c>
       <c r="H54" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K54" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>53</v>
@@ -3304,30 +3363,30 @@
         <v>21</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E55" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G55" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G55" s="5" t="s">
-        <v>149</v>
-      </c>
       <c r="H55" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K55" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>53</v>
@@ -3336,19 +3395,19 @@
         <v>23</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E56" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G56" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G56" s="5" t="s">
-        <v>149</v>
-      </c>
       <c r="H56" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J56" s="3" t="s">
         <v>19</v>
@@ -3359,7 +3418,7 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>53</v>
@@ -3368,30 +3427,30 @@
         <v>28</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E57" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G57" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G57" s="5" t="s">
-        <v>149</v>
-      </c>
       <c r="H57" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K57" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>53</v>
@@ -3400,33 +3459,33 @@
         <v>13</v>
       </c>
       <c r="D58" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="F58" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="G58" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="G58" s="5" t="s">
+      <c r="H58" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="H58" s="3" t="s">
+      <c r="I58" s="11" t="s">
         <v>161</v>
-      </c>
-      <c r="I58" s="12" t="s">
-        <v>162</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>53</v>
@@ -3435,210 +3494,210 @@
         <v>21</v>
       </c>
       <c r="D59" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="F59" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="G59" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="G59" s="5" t="s">
+      <c r="H59" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I59" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D60" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="F60" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="F60" s="3" t="s">
+      <c r="G60" s="5" t="s">
         <v>171</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>172</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D61" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E61" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="F61" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="F61" s="3" t="s">
+      <c r="G61" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="G61" s="5" t="s">
+      <c r="H61" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H61" s="3" t="s">
+      <c r="I61" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D62" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F62" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F62" s="3" t="s">
+      <c r="G62" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="G62" s="13" t="s">
+      <c r="H62" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="H62" s="3" t="s">
+      <c r="I62" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B63" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="C63" s="15" t="s">
+      <c r="A63" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C63" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D63" s="15" t="s">
+      <c r="D63" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="E63" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="E63" s="14" t="s">
+      <c r="F63" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="F63" s="14" t="s">
+      <c r="G63" s="13"/>
+      <c r="H63" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I63" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="J63" s="15" t="s">
+      <c r="I63" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="J63" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="K63" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="L63" s="15"/>
-      <c r="M63" s="15"/>
-      <c r="N63" s="15"/>
-      <c r="O63" s="15"/>
-      <c r="P63" s="15"/>
-      <c r="Q63" s="15"/>
-      <c r="R63" s="15"/>
-      <c r="S63" s="15"/>
-      <c r="T63" s="15"/>
-      <c r="U63" s="15"/>
-      <c r="V63" s="15"/>
-      <c r="W63" s="15"/>
-      <c r="X63" s="15"/>
-      <c r="Y63" s="15"/>
-      <c r="Z63" s="15"/>
+      <c r="K63" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="L63" s="14"/>
+      <c r="M63" s="14"/>
+      <c r="N63" s="14"/>
+      <c r="O63" s="14"/>
+      <c r="P63" s="14"/>
+      <c r="Q63" s="14"/>
+      <c r="R63" s="14"/>
+      <c r="S63" s="14"/>
+      <c r="T63" s="14"/>
+      <c r="U63" s="14"/>
+      <c r="V63" s="14"/>
+      <c r="W63" s="14"/>
+      <c r="X63" s="14"/>
+      <c r="Y63" s="14"/>
+      <c r="Z63" s="14"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D64" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E64" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="F64" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F64" s="3" t="s">
+      <c r="G64" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="G64" s="5" t="s">
+      <c r="H64" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I64" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>19</v>
@@ -3649,31 +3708,31 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D65" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I65" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>19</v>
@@ -3684,311 +3743,311 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G66" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>201</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="9"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G67" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I67" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="9"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H68" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="I68" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>208</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="9"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G69" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="G69" s="5" t="s">
+      <c r="H69" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="H69" s="3" t="s">
+      <c r="I69" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>214</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="9"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="9"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G71" s="5" t="s">
         <v>219</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>220</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="9"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G72" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I72" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>224</v>
       </c>
       <c r="J72" s="2"/>
       <c r="K72" s="9"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G73" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I73" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>224</v>
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="9"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G74" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="G74" s="5" t="s">
+      <c r="H74" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="H74" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="I74" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="9"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G75" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="G75" s="5" t="s">
+      <c r="H75" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="H75" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="I75" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="9"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="G76" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="G76" s="5" t="s">
-        <v>236</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>36</v>
@@ -4001,23 +4060,23 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="G77" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="G77" s="5" t="s">
-        <v>236</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>36</v>
@@ -4030,102 +4089,102 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I78" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>241</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="9"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I79" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>241</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="9"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I80" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>241</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="9"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>36</v>
@@ -4138,21 +4197,21 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>36</v>
@@ -4165,290 +4224,297 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>248</v>
+        <v>155</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>53</v>
+        <v>247</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>251</v>
+        <v>75</v>
       </c>
       <c r="J83" s="2"/>
       <c r="K83" s="9"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>248</v>
+        <v>155</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>53</v>
+        <v>247</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>253</v>
+        <v>75</v>
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="9"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="9"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="J86" s="2"/>
       <c r="K86" s="9"/>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="B87" s="6" t="s">
+      <c r="A87" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="J87" s="2"/>
+      <c r="K87" s="9"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="C87" s="6" t="s">
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="J88" s="2"/>
+      <c r="K88" s="9"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C89" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D87" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="G87" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="I87" s="6" t="s">
+      <c r="D89" s="6" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D88" s="6" t="s">
+      <c r="G89" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="G88" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="I88" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="F89" s="6"/>
-      <c r="G89" s="7" t="s">
+      <c r="H89" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="H89" s="6" t="s">
+      <c r="I89" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="I89" s="6" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B91" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F91" s="6"/>
+      <c r="G91" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="H91" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="C91" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D91" s="6" t="s">
+      <c r="I91" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="G91" s="7" t="s">
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D92" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="H91" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I91" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>273</v>
-      </c>
       <c r="G92" s="7" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>36</v>
+        <v>266</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>75</v>
+        <v>267</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="F93" s="6"/>
+        <v>274</v>
+      </c>
       <c r="G93" s="7" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>267</v>
+        <v>36</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>268</v>
+        <v>75</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>36</v>
@@ -4459,42 +4525,43 @@
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>276</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="F95" s="6"/>
       <c r="G95" s="7" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>36</v>
+        <v>270</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>75</v>
+        <v>271</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B96" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="G96" s="7" t="s">
         <v>275</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G96" s="7" t="s">
-        <v>277</v>
       </c>
       <c r="H96" s="6" t="s">
         <v>36</v>
@@ -4505,43 +4572,42 @@
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="F97" s="6"/>
+        <v>279</v>
+      </c>
       <c r="G97" s="7" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>267</v>
+        <v>36</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>268</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="H98" s="6" t="s">
         <v>36</v>
@@ -4552,275 +4618,275 @@
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="6" t="s">
-        <v>280</v>
+        <v>251</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>282</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="F99" s="6"/>
       <c r="G99" s="7" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>36</v>
+        <v>270</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="G100" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="B100" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="G100" s="7" t="s">
-        <v>283</v>
-      </c>
       <c r="H100" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>284</v>
+        <v>75</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="6" t="s">
-        <v>248</v>
+        <v>283</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="F101" s="6"/>
+        <v>285</v>
+      </c>
       <c r="G101" s="7" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>267</v>
+        <v>36</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="6" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D102" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="G102" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="G102" s="7" t="s">
-        <v>283</v>
-      </c>
       <c r="H102" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>288</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="F103" s="6"/>
       <c r="G103" s="7" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>36</v>
+        <v>270</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="6" t="s">
-        <v>248</v>
+        <v>283</v>
       </c>
       <c r="B104" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I104" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="G104" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I104" s="6" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B105" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I105" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="F105" s="6"/>
-      <c r="G105" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="H105" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="I105" s="6" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B106" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="G106" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I106" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D106" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="G106" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I106" s="6" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>293</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="F107" s="6"/>
       <c r="G107" s="7" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>36</v>
+        <v>270</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>75</v>
+        <v>271</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B108" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="G108" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="C108" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="G108" s="7" t="s">
-        <v>294</v>
-      </c>
       <c r="H108" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>75</v>
+        <v>287</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="F109" s="6"/>
+        <v>296</v>
+      </c>
       <c r="G109" s="7" t="s">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>267</v>
+        <v>36</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>268</v>
+        <v>75</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="H110" s="6" t="s">
         <v>36</v>
@@ -4831,329 +4897,318 @@
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="F111" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="G111" s="16"/>
+        <v>257</v>
+      </c>
+      <c r="F111" s="6"/>
+      <c r="G111" s="7" t="s">
+        <v>269</v>
+      </c>
       <c r="H111" s="6" t="s">
-        <v>5</v>
+        <v>270</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>300</v>
+        <v>271</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B112" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="G112" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="C112" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D112" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="F112" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="G112" s="16"/>
       <c r="H112" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>300</v>
+        <v>75</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="F113" s="6"/>
-      <c r="G113" s="7" t="s">
-        <v>266</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="F113" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="G113" s="15"/>
       <c r="H113" s="6" t="s">
-        <v>267</v>
+        <v>5</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>268</v>
+        <v>303</v>
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D114" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="F114" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="F114" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="G114" s="16"/>
+      <c r="G114" s="15"/>
       <c r="H114" s="6" t="s">
         <v>5</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="F115" s="6" t="s">
-        <v>307</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="F115" s="6"/>
       <c r="G115" s="7" t="s">
-        <v>308</v>
+        <v>269</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>36</v>
+        <v>270</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B116" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D116" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="C116" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D116" s="6" t="s">
-        <v>310</v>
-      </c>
       <c r="F116" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="G116" s="15"/>
+      <c r="H116" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I116" s="6" t="s">
         <v>307</v>
-      </c>
-      <c r="G116" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I116" s="6" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D117" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="G117" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="F117" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="G117" s="7" t="s">
-        <v>308</v>
-      </c>
       <c r="H117" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D118" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="G118" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I118" s="6" t="s">
         <v>312</v>
-      </c>
-      <c r="F118" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="G118" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I118" s="6" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="E119" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="F119" s="6" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="H119" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="E120" s="6" t="s">
-        <v>15</v>
+        <v>315</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="G120" s="7" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="H120" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E121" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="H121" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="H122" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>322</v>
@@ -5162,468 +5217,480 @@
         <v>15</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="G123" s="7" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H123" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="G124" s="7" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H124" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E125" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G125" s="7" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="H125" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G126" s="7" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="H126" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>330</v>
+        <v>15</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="G127" s="7" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="H127" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>330</v>
+        <v>15</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="G128" s="7" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="H128" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="E129" s="6"/>
-      <c r="F129" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="G129" s="16"/>
+        <v>332</v>
+      </c>
+      <c r="E129" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="G129" s="7" t="s">
+        <v>335</v>
+      </c>
       <c r="H129" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D130" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="F130" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="G130" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="E130" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="F130" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="G130" s="7" t="s">
-        <v>332</v>
-      </c>
       <c r="H130" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="E131" s="6"/>
+      <c r="F131" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G131" s="15"/>
+      <c r="H131" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I131" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="B131" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C131" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="E131" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="F131" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="G131" s="16"/>
-      <c r="H131" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I131" s="6" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="F132" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="G132" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="H132" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I132" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="B132" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C132" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D132" s="6" t="s">
+    </row>
+    <row r="133" ht="15.75" customHeight="1">
+      <c r="A133" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D133" s="6" t="s">
         <v>340</v>
-      </c>
-      <c r="E132" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="F132" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="G132" s="16"/>
-      <c r="H132" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I132" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="133" ht="16.5" customHeight="1">
-      <c r="A133" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="B133" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C133" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D133" s="6" t="s">
-        <v>341</v>
       </c>
       <c r="E133" s="6"/>
       <c r="F133" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="G133" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="G133" s="16"/>
       <c r="H133" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>5</v>
+        <v>287</v>
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="6" t="s">
-        <v>336</v>
+        <v>251</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>53</v>
+        <v>339</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="E134" s="6" t="s">
-        <v>338</v>
-      </c>
+      <c r="E134" s="6"/>
       <c r="F134" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="G134" s="16"/>
+        <v>341</v>
+      </c>
+      <c r="G134" s="7" t="s">
+        <v>342</v>
+      </c>
       <c r="H134" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>5</v>
+        <v>287</v>
       </c>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="E135" s="6"/>
+      <c r="F135" s="16"/>
+      <c r="G135" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="H135" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I135" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="C135" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D135" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="G135" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="H135" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I135" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="J135" s="6" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="6" t="s">
-        <v>336</v>
+        <v>251</v>
       </c>
       <c r="B136" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D136" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="C136" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D136" s="6" t="s">
-        <v>348</v>
-      </c>
+      <c r="E136" s="6"/>
+      <c r="F136" s="6"/>
       <c r="G136" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="H136" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I136" s="6" t="s">
         <v>346</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I136" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="J136" s="6" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="6" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>344</v>
+        <v>53</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D137" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="E137" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="G137" s="7" t="s">
-        <v>346</v>
-      </c>
+      <c r="F137" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="G137" s="15"/>
       <c r="H137" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="J137" s="6" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="6" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>344</v>
+        <v>53</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D138" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F138" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="G138" s="7" t="s">
-        <v>346</v>
-      </c>
+      <c r="G138" s="15"/>
       <c r="H138" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I138" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" ht="16.5" customHeight="1">
+      <c r="A139" s="6" t="s">
         <v>347</v>
-      </c>
-      <c r="J138" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="6" t="s">
-        <v>351</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>352</v>
       </c>
+      <c r="E139" s="6"/>
       <c r="F139" s="6" t="s">
         <v>353</v>
       </c>
+      <c r="G139" s="15"/>
       <c r="H139" s="6" t="s">
-        <v>354</v>
+        <v>5</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>355</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="6" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>356</v>
+        <v>354</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>349</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>353</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="G140" s="15"/>
       <c r="H140" s="6" t="s">
-        <v>354</v>
+        <v>5</v>
       </c>
       <c r="I140" s="6" t="s">
         <v>5</v>
@@ -5631,923 +5698,1159 @@
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="6" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>53</v>
+        <v>355</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D141" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="G141" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="F141" s="6" t="s">
+      <c r="H141" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I141" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="H141" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="I141" s="6" t="s">
-        <v>360</v>
+      <c r="J141" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="6" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>53</v>
+        <v>355</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="F142" s="6" t="s">
-        <v>353</v>
+        <v>359</v>
+      </c>
+      <c r="G142" s="7" t="s">
+        <v>357</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>354</v>
+        <v>36</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>131</v>
+        <v>358</v>
+      </c>
+      <c r="J142" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="6" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="E143" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="F143" s="6" t="s">
-        <v>366</v>
+        <v>360</v>
+      </c>
+      <c r="G143" s="7" t="s">
+        <v>357</v>
       </c>
       <c r="H143" s="6" t="s">
-        <v>354</v>
+        <v>36</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>367</v>
+        <v>358</v>
+      </c>
+      <c r="J143" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="6" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="E144" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="F144" s="6" t="s">
-        <v>366</v>
+        <v>361</v>
+      </c>
+      <c r="G144" s="7" t="s">
+        <v>357</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>354</v>
+        <v>36</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>367</v>
+        <v>358</v>
+      </c>
+      <c r="J144" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="B145" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="B145" s="6" t="s">
+      <c r="C145" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D145" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="C145" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D145" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="E145" s="6" t="s">
+      <c r="G145" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="H145" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I145" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="F145" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="H145" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="I145" s="6" t="s">
-        <v>367</v>
-      </c>
+      <c r="J145" s="6"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="B146" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="B146" s="6" t="s">
-        <v>363</v>
-      </c>
       <c r="C146" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="E146" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="G146" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="H146" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I146" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="F146" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="I146" s="6" t="s">
-        <v>367</v>
-      </c>
+      <c r="J146" s="6"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="B147" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="B147" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="C147" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="G147" s="8" t="s">
-        <v>372</v>
+        <v>367</v>
+      </c>
+      <c r="G147" s="7" t="s">
+        <v>364</v>
       </c>
       <c r="H147" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>284</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="J147" s="6"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="B148" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="B148" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="C148" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="G148" s="8" t="s">
-        <v>372</v>
+        <v>368</v>
+      </c>
+      <c r="G148" s="7" t="s">
+        <v>364</v>
       </c>
       <c r="H148" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>284</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="J148" s="6"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="6" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D149" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="F149" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="H149" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="I149" s="6" t="s">
         <v>374</v>
-      </c>
-      <c r="G149" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="H149" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I149" s="6" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="6" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="G150" s="8" t="s">
+      <c r="F150" s="6" t="s">
         <v>372</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>36</v>
+        <v>373</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>284</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="6" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D151" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F151" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="G151" s="7" t="s">
+      <c r="H151" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="H151" s="6" t="s">
+      <c r="I151" s="6" t="s">
         <v>379</v>
-      </c>
-      <c r="I151" s="7" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="6" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="G152" s="7" t="s">
-        <v>382</v>
+        <v>380</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>372</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>36</v>
+        <v>373</v>
       </c>
       <c r="I152" s="6" t="s">
-        <v>284</v>
+        <v>130</v>
       </c>
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="6" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>53</v>
+        <v>382</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D153" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="G153" s="7" t="s">
-        <v>382</v>
+      <c r="E153" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="F153" s="6" t="s">
+        <v>385</v>
       </c>
       <c r="H153" s="6" t="s">
-        <v>36</v>
+        <v>373</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>284</v>
+        <v>386</v>
       </c>
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="6" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>53</v>
+        <v>382</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D154" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="E154" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="G154" s="7" t="s">
-        <v>382</v>
+      <c r="F154" s="6" t="s">
+        <v>385</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>36</v>
+        <v>373</v>
       </c>
       <c r="I154" s="6" t="s">
-        <v>284</v>
+        <v>386</v>
       </c>
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="F155" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="B155" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C155" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D155" s="6" t="s">
+      <c r="H155" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="I155" s="6" t="s">
         <v>386</v>
-      </c>
-      <c r="E155" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="F155" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="G155" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="H155" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I155" s="6" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="F156" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="B156" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C156" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D156" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="E156" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="F156" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="G156" s="8" t="s">
-        <v>389</v>
-      </c>
       <c r="H156" s="6" t="s">
-        <v>36</v>
+        <v>373</v>
       </c>
       <c r="I156" s="6" t="s">
-        <v>284</v>
+        <v>386</v>
       </c>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="6" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D157" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="G157" s="8" t="s">
         <v>391</v>
       </c>
-      <c r="E157" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="F157" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="G157" s="8" t="s">
-        <v>389</v>
-      </c>
       <c r="H157" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="6" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D158" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="E158" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="F158" s="6" t="s">
-        <v>388</v>
-      </c>
       <c r="G158" s="8" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="H158" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D159" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="B159" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="C159" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D159" s="6" t="s">
-        <v>395</v>
-      </c>
       <c r="G159" s="8" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="H159" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="6" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="B160" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D160" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="C160" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D160" s="6" t="s">
-        <v>397</v>
-      </c>
       <c r="G160" s="8" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="H160" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I160" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>394</v>
+        <v>53</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D161" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="G161" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="H161" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="G161" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="H161" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I161" s="6" t="s">
-        <v>284</v>
+      <c r="I161" s="7" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>394</v>
+        <v>53</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="G162" s="8" t="s">
-        <v>396</v>
+        <v>400</v>
+      </c>
+      <c r="G162" s="7" t="s">
+        <v>401</v>
       </c>
       <c r="H162" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I162" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="6" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>401</v>
+        <v>53</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D163" s="6" t="s">
         <v>402</v>
       </c>
       <c r="G163" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H163" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I163" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="6" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B164" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="G164" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="C164" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D164" s="6" t="s">
-        <v>404</v>
-      </c>
-      <c r="G164" s="7" t="s">
-        <v>403</v>
-      </c>
       <c r="H164" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I164" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="6" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>401</v>
+        <v>53</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D165" s="6" t="s">
         <v>405</v>
       </c>
+      <c r="E165" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="F165" s="6" t="s">
+        <v>407</v>
+      </c>
       <c r="G165" s="7" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="H165" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I165" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="6" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>401</v>
+        <v>53</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D166" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="E166" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="G166" s="7" t="s">
-        <v>403</v>
+      <c r="F166" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="G166" s="8" t="s">
+        <v>408</v>
       </c>
       <c r="H166" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I166" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="E167" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="F167" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="B167" s="6" t="s">
+      <c r="G167" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="C167" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D167" s="6" t="s">
-        <v>409</v>
-      </c>
-      <c r="G167" s="8" t="s">
-        <v>410</v>
-      </c>
       <c r="H167" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I167" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="6" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>408</v>
+        <v>53</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D168" s="6" t="s">
         <v>411</v>
       </c>
+      <c r="E168" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="F168" s="6" t="s">
+        <v>407</v>
+      </c>
       <c r="G168" s="8" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H168" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I168" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="6" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G169" s="8" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="H169" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I169" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="6" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="H170" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I170" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B171" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="G171" s="8" t="s">
         <v>415</v>
       </c>
-      <c r="C171" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D171" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G171" s="8" t="s">
-        <v>417</v>
-      </c>
       <c r="H171" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I171" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D172" s="6" t="s">
         <v>418</v>
       </c>
       <c r="G172" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H172" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I172" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="6" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>419</v>
-      </c>
-      <c r="G173" s="8" t="s">
-        <v>417</v>
+        <v>421</v>
+      </c>
+      <c r="G173" s="7" t="s">
+        <v>422</v>
       </c>
       <c r="H173" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I173" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="6" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>420</v>
-      </c>
-      <c r="G174" s="8" t="s">
-        <v>417</v>
+        <v>423</v>
+      </c>
+      <c r="G174" s="7" t="s">
+        <v>422</v>
       </c>
       <c r="H174" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I174" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>53</v>
+        <v>420</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D175" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="G175" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="G175" s="7" t="s">
-        <v>423</v>
-      </c>
       <c r="H175" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I175" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>53</v>
+        <v>420</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G176" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H176" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I176" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="6" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>53</v>
+        <v>427</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="G177" s="7" t="s">
-        <v>423</v>
+        <v>428</v>
+      </c>
+      <c r="G177" s="8" t="s">
+        <v>429</v>
       </c>
       <c r="H177" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I177" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="6" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B178" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="G178" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="H178" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I178" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="179" ht="15.75" customHeight="1">
+      <c r="A179" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="G179" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="H179" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I179" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="180" ht="15.75" customHeight="1">
+      <c r="A180" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D180" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="G180" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="H180" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I180" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="181" ht="15.75" customHeight="1">
+      <c r="A181" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D181" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="G181" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="H181" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I181" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="182" ht="15.75" customHeight="1">
+      <c r="A182" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="G182" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="H182" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I182" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="183" ht="15.75" customHeight="1">
+      <c r="A183" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="G183" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="H183" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I183" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="184" ht="15.75" customHeight="1">
+      <c r="A184" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="G184" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="H184" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I184" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="185" ht="15.75" customHeight="1">
+      <c r="A185" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="B185" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C178" s="6" t="s">
+      <c r="C185" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="G185" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="H185" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I185" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="186" ht="15.75" customHeight="1">
+      <c r="A186" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="G186" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="H186" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I186" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="187" ht="15.75" customHeight="1">
+      <c r="A187" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C187" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D187" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="G187" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="H187" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I187" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="188" ht="15.75" customHeight="1">
+      <c r="A188" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C188" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D178" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="F178" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="G178" s="16"/>
-      <c r="H178" s="6"/>
-      <c r="I178" s="6" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
+      <c r="D188" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="F188" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="G188" s="15"/>
+      <c r="H188" s="6"/>
+      <c r="I188" s="6" t="s">
+        <v>447</v>
+      </c>
+    </row>
     <row r="189" ht="15.75" customHeight="1"/>
     <row r="190" ht="15.75" customHeight="1"/>
     <row r="191" ht="15.75" customHeight="1"/>
@@ -7470,6 +7773,16 @@
     <row r="1108" ht="15.75" customHeight="1"/>
     <row r="1109" ht="15.75" customHeight="1"/>
     <row r="1110" ht="15.75" customHeight="1"/>
+    <row r="1111" ht="15.75" customHeight="1"/>
+    <row r="1112" ht="15.75" customHeight="1"/>
+    <row r="1113" ht="15.75" customHeight="1"/>
+    <row r="1114" ht="15.75" customHeight="1"/>
+    <row r="1115" ht="15.75" customHeight="1"/>
+    <row r="1116" ht="15.75" customHeight="1"/>
+    <row r="1117" ht="15.75" customHeight="1"/>
+    <row r="1118" ht="15.75" customHeight="1"/>
+    <row r="1119" ht="15.75" customHeight="1"/>
+    <row r="1120" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" location="/home" ref="G2"/>
@@ -7577,9 +7890,9 @@
     <hyperlink r:id="rId103" ref="G108"/>
     <hyperlink r:id="rId104" ref="G109"/>
     <hyperlink r:id="rId105" ref="G110"/>
-    <hyperlink r:id="rId106" ref="G113"/>
-    <hyperlink r:id="rId107" ref="G115"/>
-    <hyperlink r:id="rId108" ref="G116"/>
+    <hyperlink r:id="rId106" ref="G111"/>
+    <hyperlink r:id="rId107" ref="G112"/>
+    <hyperlink r:id="rId108" ref="G115"/>
     <hyperlink r:id="rId109" ref="G117"/>
     <hyperlink r:id="rId110" ref="G118"/>
     <hyperlink r:id="rId111" ref="G119"/>
@@ -7592,28 +7905,28 @@
     <hyperlink r:id="rId118" ref="G126"/>
     <hyperlink r:id="rId119" ref="G127"/>
     <hyperlink r:id="rId120" ref="G128"/>
-    <hyperlink r:id="rId121" ref="F129"/>
+    <hyperlink r:id="rId121" ref="G129"/>
     <hyperlink r:id="rId122" ref="G130"/>
-    <hyperlink r:id="rId123" ref="G135"/>
-    <hyperlink r:id="rId124" ref="G136"/>
-    <hyperlink r:id="rId125" ref="G137"/>
-    <hyperlink r:id="rId126" ref="G138"/>
-    <hyperlink r:id="rId127" ref="G147"/>
-    <hyperlink r:id="rId128" ref="G148"/>
-    <hyperlink r:id="rId129" ref="G149"/>
-    <hyperlink r:id="rId130" ref="G150"/>
-    <hyperlink r:id="rId131" ref="G151"/>
-    <hyperlink r:id="rId132" ref="I151"/>
-    <hyperlink r:id="rId133" ref="G152"/>
-    <hyperlink r:id="rId134" ref="G153"/>
-    <hyperlink r:id="rId135" ref="G154"/>
-    <hyperlink r:id="rId136" ref="G155"/>
-    <hyperlink r:id="rId137" ref="G156"/>
-    <hyperlink r:id="rId138" ref="G157"/>
-    <hyperlink r:id="rId139" ref="G158"/>
-    <hyperlink r:id="rId140" ref="G159"/>
-    <hyperlink r:id="rId141" ref="G160"/>
-    <hyperlink r:id="rId142" ref="G161"/>
+    <hyperlink r:id="rId123" ref="F131"/>
+    <hyperlink r:id="rId124" ref="G132"/>
+    <hyperlink r:id="rId125" ref="G133"/>
+    <hyperlink r:id="rId126" ref="G134"/>
+    <hyperlink r:id="rId127" ref="G135"/>
+    <hyperlink r:id="rId128" ref="G136"/>
+    <hyperlink r:id="rId129" ref="G141"/>
+    <hyperlink r:id="rId130" ref="G142"/>
+    <hyperlink r:id="rId131" ref="G143"/>
+    <hyperlink r:id="rId132" ref="G144"/>
+    <hyperlink r:id="rId133" ref="G145"/>
+    <hyperlink r:id="rId134" ref="G146"/>
+    <hyperlink r:id="rId135" ref="G147"/>
+    <hyperlink r:id="rId136" ref="G148"/>
+    <hyperlink r:id="rId137" ref="G157"/>
+    <hyperlink r:id="rId138" ref="G158"/>
+    <hyperlink r:id="rId139" ref="G159"/>
+    <hyperlink r:id="rId140" ref="G160"/>
+    <hyperlink r:id="rId141" ref="G161"/>
+    <hyperlink r:id="rId142" ref="I161"/>
     <hyperlink r:id="rId143" ref="G162"/>
     <hyperlink r:id="rId144" ref="G163"/>
     <hyperlink r:id="rId145" ref="G164"/>
@@ -7630,10 +7943,20 @@
     <hyperlink r:id="rId156" ref="G175"/>
     <hyperlink r:id="rId157" ref="G176"/>
     <hyperlink r:id="rId158" ref="G177"/>
+    <hyperlink r:id="rId159" ref="G178"/>
+    <hyperlink r:id="rId160" ref="G179"/>
+    <hyperlink r:id="rId161" ref="G180"/>
+    <hyperlink r:id="rId162" ref="G181"/>
+    <hyperlink r:id="rId163" ref="G182"/>
+    <hyperlink r:id="rId164" ref="G183"/>
+    <hyperlink r:id="rId165" ref="G184"/>
+    <hyperlink r:id="rId166" ref="G185"/>
+    <hyperlink r:id="rId167" ref="G186"/>
+    <hyperlink r:id="rId168" ref="G187"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId159"/>
+  <drawing r:id="rId169"/>
 </worksheet>
 </file>